--- a/fact_inventario/outputs/01_pesos_finales.xlsx
+++ b/fact_inventario/outputs/01_pesos_finales.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F444"/>
+  <dimension ref="A1:F457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,13 +465,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.01720205134254952</v>
+        <v>-0.01720205134254953</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01720205134254952</v>
+        <v>0.01720205134254953</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01134909034064964</v>
+        <v>0.01134909034064965</v>
       </c>
     </row>
     <row r="3">
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.4351649251456696</v>
+        <v>-0.4351649251456693</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4351649251456696</v>
+        <v>0.4351649251456693</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2871009945391939</v>
+        <v>0.2871009945391936</v>
       </c>
     </row>
     <row r="5">
@@ -549,7 +549,7 @@
         <v>0.2210375970584088</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1458300296715775</v>
+        <v>0.1458300296715774</v>
       </c>
     </row>
     <row r="6">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.2153487431213609</v>
+        <v>0.215348743121361</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2153487431213609</v>
+        <v>0.215348743121361</v>
       </c>
       <c r="F7" t="n">
         <v>0.1420767960611987</v>
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.2382837104419929</v>
+        <v>0.238283710441993</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2382837104419929</v>
+        <v>0.238283710441993</v>
       </c>
       <c r="F8" t="n">
         <v>0.1572081900384895</v>
@@ -673,13 +673,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.02413040390074436</v>
+        <v>0.0241304039007444</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02413040390074436</v>
+        <v>0.0241304039007444</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01592008583002658</v>
+        <v>0.0159200858300266</v>
       </c>
     </row>
     <row r="11">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.4984185467830454</v>
+        <v>-0.4984185467830455</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4984185467830454</v>
+        <v>0.4984185467830455</v>
       </c>
       <c r="F11" t="n">
         <v>0.3288327073471999</v>
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.3918480332147748</v>
+        <v>-0.3918480332147747</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3918480332147748</v>
+        <v>0.3918480332147747</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2585225819992962</v>
+        <v>0.2585225819992961</v>
       </c>
     </row>
     <row r="13">
@@ -757,7 +757,7 @@
         <v>0.6214263994842752</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4099874025121008</v>
+        <v>0.4099874025121007</v>
       </c>
     </row>
     <row r="14">
@@ -803,13 +803,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.2823871307507416</v>
+        <v>-0.2823871307507417</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2823871307507416</v>
+        <v>0.2823871307507417</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1863055163659347</v>
+        <v>0.1863055163659348</v>
       </c>
     </row>
     <row r="16">
@@ -829,13 +829,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.031187215461716</v>
+        <v>0.03118721546171591</v>
       </c>
       <c r="E16" t="n">
-        <v>0.031187215461716</v>
+        <v>0.03118721546171591</v>
       </c>
       <c r="F16" t="n">
-        <v>0.02057583242254536</v>
+        <v>0.02057583242254529</v>
       </c>
     </row>
     <row r="17">
@@ -855,13 +855,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.7544636701196982</v>
+        <v>0.7544636701196979</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7544636701196982</v>
+        <v>0.7544636701196979</v>
       </c>
       <c r="F17" t="n">
-        <v>0.497759027712418</v>
+        <v>0.4977590277124178</v>
       </c>
     </row>
     <row r="18">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.3120404355066063</v>
+        <v>-0.3120404355066062</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3120404355066063</v>
+        <v>0.3120404355066062</v>
       </c>
       <c r="F19" t="n">
         <v>0.2058693479039032</v>
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.1030165900234799</v>
+        <v>0.1030165900234798</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1030165900234799</v>
+        <v>0.1030165900234798</v>
       </c>
       <c r="F20" t="n">
-        <v>0.06796541665180618</v>
+        <v>0.06796541665180612</v>
       </c>
     </row>
     <row r="21">
@@ -959,13 +959,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.07094451355466765</v>
+        <v>0.07094451355466762</v>
       </c>
       <c r="E21" t="n">
-        <v>0.07094451355466765</v>
+        <v>0.07094451355466762</v>
       </c>
       <c r="F21" t="n">
-        <v>0.04680579527825277</v>
+        <v>0.04680579527825275</v>
       </c>
     </row>
     <row r="22">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.09489948024889666</v>
+        <v>0.09489948024889669</v>
       </c>
       <c r="E22" t="n">
-        <v>0.09489948024889666</v>
+        <v>0.09489948024889669</v>
       </c>
       <c r="F22" t="n">
         <v>0.06261013603426432</v>
@@ -1069,7 +1069,7 @@
         <v>0.08293224211623104</v>
       </c>
       <c r="F25" t="n">
-        <v>0.05471472495850829</v>
+        <v>0.05471472495850827</v>
       </c>
     </row>
     <row r="26">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-0.01031521888564041</v>
+        <v>-0.01031521888564037</v>
       </c>
       <c r="E27" t="n">
-        <v>0.01031521888564041</v>
+        <v>0.01031521888564037</v>
       </c>
       <c r="F27" t="n">
-        <v>0.006805487827323137</v>
+        <v>0.006805487827323107</v>
       </c>
     </row>
     <row r="28">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-0.003733207688397675</v>
+        <v>-0.003733207688397674</v>
       </c>
       <c r="E28" t="n">
-        <v>0.003733207688397675</v>
+        <v>0.003733207688397674</v>
       </c>
       <c r="F28" t="n">
         <v>0.002462991795125847</v>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-0.4329768894859886</v>
+        <v>-0.4329768894859887</v>
       </c>
       <c r="E29" t="n">
-        <v>0.4329768894859886</v>
+        <v>0.4329768894859887</v>
       </c>
       <c r="F29" t="n">
         <v>0.285657433310606</v>
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-0.2560725127730248</v>
+        <v>-0.2560725127730249</v>
       </c>
       <c r="E30" t="n">
-        <v>0.2560725127730248</v>
+        <v>0.2560725127730249</v>
       </c>
       <c r="F30" t="n">
         <v>0.1689443906047249</v>
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.1040280552947547</v>
+        <v>0.1040280552947548</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1040280552947547</v>
+        <v>0.1040280552947548</v>
       </c>
       <c r="F31" t="n">
         <v>0.06863273303818004</v>
@@ -1271,13 +1271,13 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-0.3467715154270991</v>
+        <v>-0.346771515427099</v>
       </c>
       <c r="E33" t="n">
-        <v>0.3467715154270991</v>
+        <v>0.346771515427099</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2287832525189313</v>
+        <v>0.2287832525189312</v>
       </c>
     </row>
     <row r="34">
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>-0.2232199533740552</v>
+        <v>-0.2232199533740553</v>
       </c>
       <c r="E34" t="n">
-        <v>0.2232199533740552</v>
+        <v>0.2232199533740553</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1472698439407335</v>
+        <v>0.1472698439407336</v>
       </c>
     </row>
     <row r="35">
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.01778206734325326</v>
+        <v>0.01778206734325321</v>
       </c>
       <c r="E35" t="n">
-        <v>0.01778206734325326</v>
+        <v>0.01778206734325321</v>
       </c>
       <c r="F35" t="n">
-        <v>0.01173175714357487</v>
+        <v>0.01173175714357483</v>
       </c>
     </row>
     <row r="36">
@@ -1349,13 +1349,13 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-0.2215534215993231</v>
+        <v>-0.221553421599323</v>
       </c>
       <c r="E36" t="n">
-        <v>0.2215534215993231</v>
+        <v>0.221553421599323</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1461703460209584</v>
+        <v>0.1461703460209583</v>
       </c>
     </row>
     <row r="37">
@@ -1381,7 +1381,7 @@
         <v>0.3868583956063532</v>
       </c>
       <c r="F37" t="n">
-        <v>0.2552306578643525</v>
+        <v>0.2552306578643524</v>
       </c>
     </row>
     <row r="38">
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.0002523875681593416</v>
+        <v>0.0002523875681593033</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0002523875681593416</v>
+        <v>0.0002523875681593033</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0001665132404768598</v>
+        <v>0.0001665132404768345</v>
       </c>
     </row>
     <row r="39">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.600146799657663</v>
+        <v>0.6001467996576632</v>
       </c>
       <c r="E39" t="n">
-        <v>0.600146799657663</v>
+        <v>0.6001467996576632</v>
       </c>
       <c r="F39" t="n">
         <v>0.3959481407963931</v>
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.2259264396334941</v>
+        <v>0.2259264396334942</v>
       </c>
       <c r="E40" t="n">
-        <v>0.2259264396334941</v>
+        <v>0.2259264396334942</v>
       </c>
       <c r="F40" t="n">
         <v>0.1490554540666679</v>
@@ -1485,7 +1485,7 @@
         <v>0.105882477842336</v>
       </c>
       <c r="F41" t="n">
-        <v>0.06985619229912181</v>
+        <v>0.06985619229912178</v>
       </c>
     </row>
     <row r="42">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>-0.3792990207095799</v>
+        <v>-0.3792990207095798</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3792990207095799</v>
+        <v>0.3792990207095798</v>
       </c>
       <c r="F44" t="n">
         <v>0.2502433440310242</v>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.2660680004636836</v>
+        <v>0.2660680004636837</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2660680004636836</v>
+        <v>0.2660680004636837</v>
       </c>
       <c r="F45" t="n">
         <v>0.1755389350890529</v>
@@ -1615,7 +1615,7 @@
         <v>0.5630356570138377</v>
       </c>
       <c r="F46" t="n">
-        <v>0.3714639846848647</v>
+        <v>0.3714639846848646</v>
       </c>
     </row>
     <row r="47">
@@ -1635,13 +1635,13 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-0.1316561839127881</v>
+        <v>-0.1316561839127882</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1316561839127881</v>
+        <v>0.1316561839127882</v>
       </c>
       <c r="F47" t="n">
-        <v>0.08686045026708798</v>
+        <v>0.08686045026708802</v>
       </c>
     </row>
     <row r="48">
@@ -1661,13 +1661,13 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.08322207419077769</v>
+        <v>0.08322207419077757</v>
       </c>
       <c r="E48" t="n">
-        <v>0.08322207419077769</v>
+        <v>0.08322207419077757</v>
       </c>
       <c r="F48" t="n">
-        <v>0.05490594229254284</v>
+        <v>0.05490594229254274</v>
       </c>
     </row>
     <row r="49">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.8811770867208216</v>
+        <v>0.8811770867208217</v>
       </c>
       <c r="E49" t="n">
-        <v>0.8811770867208216</v>
+        <v>0.8811770867208217</v>
       </c>
       <c r="F49" t="n">
         <v>0.5813584766235724</v>
@@ -1713,13 +1713,13 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.03281472281817769</v>
+        <v>0.03281472281817768</v>
       </c>
       <c r="E50" t="n">
-        <v>0.03281472281817769</v>
+        <v>0.03281472281817768</v>
       </c>
       <c r="F50" t="n">
-        <v>0.02164958389850264</v>
+        <v>0.02164958389850263</v>
       </c>
     </row>
     <row r="51">
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>-0.3331047480840261</v>
+        <v>-0.3331047480840262</v>
       </c>
       <c r="E52" t="n">
-        <v>0.3331047480840261</v>
+        <v>0.3331047480840262</v>
       </c>
       <c r="F52" t="n">
         <v>0.2197665733943016</v>
@@ -1791,10 +1791,10 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.3059996470163239</v>
+        <v>0.305999647016324</v>
       </c>
       <c r="E53" t="n">
-        <v>0.3059996470163239</v>
+        <v>0.305999647016324</v>
       </c>
       <c r="F53" t="n">
         <v>0.2018839247157168</v>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.01988359986406832</v>
+        <v>0.01988359986406831</v>
       </c>
       <c r="E54" t="n">
-        <v>0.01988359986406832</v>
+        <v>0.01988359986406831</v>
       </c>
       <c r="F54" t="n">
         <v>0.01311824774039972</v>
@@ -1843,13 +1843,13 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>-0.03384198667782843</v>
+        <v>-0.03384198667782844</v>
       </c>
       <c r="E55" t="n">
-        <v>0.03384198667782843</v>
+        <v>0.03384198667782844</v>
       </c>
       <c r="F55" t="n">
-        <v>0.02232732343750885</v>
+        <v>0.02232732343750886</v>
       </c>
     </row>
     <row r="56">
@@ -1869,13 +1869,13 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>-0.1485936887322683</v>
+        <v>-0.1485936887322684</v>
       </c>
       <c r="E56" t="n">
-        <v>0.1485936887322683</v>
+        <v>0.1485936887322684</v>
       </c>
       <c r="F56" t="n">
-        <v>0.09803500547062914</v>
+        <v>0.09803500547062917</v>
       </c>
     </row>
     <row r="57">
@@ -1927,7 +1927,7 @@
         <v>0.1076931080503719</v>
       </c>
       <c r="F58" t="n">
-        <v>0.07105075946993825</v>
+        <v>0.07105075946993823</v>
       </c>
     </row>
     <row r="59">
@@ -1953,7 +1953,7 @@
         <v>0.2083750233268926</v>
       </c>
       <c r="F59" t="n">
-        <v>0.1374758694401957</v>
+        <v>0.1374758694401956</v>
       </c>
     </row>
     <row r="60">
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.3088525780538262</v>
+        <v>0.3088525780538263</v>
       </c>
       <c r="E60" t="n">
-        <v>0.3088525780538262</v>
+        <v>0.3088525780538263</v>
       </c>
       <c r="F60" t="n">
         <v>0.2037661520986899</v>
@@ -1999,13 +1999,13 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>-0.007620815319650663</v>
+        <v>-0.007620815319650634</v>
       </c>
       <c r="E61" t="n">
-        <v>0.007620815319650663</v>
+        <v>0.007620815319650634</v>
       </c>
       <c r="F61" t="n">
-        <v>0.005027849284357708</v>
+        <v>0.005027849284357688</v>
       </c>
     </row>
     <row r="62">
@@ -2031,7 +2031,7 @@
         <v>0.1483634676876706</v>
       </c>
       <c r="F62" t="n">
-        <v>0.09788311664170821</v>
+        <v>0.09788311664170818</v>
       </c>
     </row>
     <row r="63">
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.02765391919337824</v>
+        <v>0.02765391919337822</v>
       </c>
       <c r="E63" t="n">
-        <v>0.02765391919337824</v>
+        <v>0.02765391919337822</v>
       </c>
       <c r="F63" t="n">
-        <v>0.01824473261641594</v>
+        <v>0.01824473261641592</v>
       </c>
     </row>
     <row r="64">
@@ -2077,13 +2077,13 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.04417187916363712</v>
+        <v>0.04417187916363711</v>
       </c>
       <c r="E64" t="n">
-        <v>0.04417187916363712</v>
+        <v>0.04417187916363711</v>
       </c>
       <c r="F64" t="n">
-        <v>0.02914249220407674</v>
+        <v>0.02914249220407673</v>
       </c>
     </row>
     <row r="65">
@@ -2109,7 +2109,7 @@
         <v>0.1498424929507562</v>
       </c>
       <c r="F65" t="n">
-        <v>0.09885890673747089</v>
+        <v>0.09885890673747087</v>
       </c>
     </row>
     <row r="66">
@@ -2187,7 +2187,7 @@
         <v>0.3119235106596341</v>
       </c>
       <c r="F68" t="n">
-        <v>0.2057922064848406</v>
+        <v>0.2057922064848405</v>
       </c>
     </row>
     <row r="69">
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>-0.2068401964467618</v>
+        <v>-0.2068401964467619</v>
       </c>
       <c r="E69" t="n">
-        <v>0.2068401964467618</v>
+        <v>0.2068401964467619</v>
       </c>
       <c r="F69" t="n">
         <v>0.1364632641076691</v>
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>-0.07000533736934132</v>
+        <v>-0.07000533736934135</v>
       </c>
       <c r="E71" t="n">
-        <v>0.07000533736934132</v>
+        <v>0.07000533736934135</v>
       </c>
       <c r="F71" t="n">
         <v>0.04618617177168351</v>
@@ -2291,7 +2291,7 @@
         <v>0.2684404434199759</v>
       </c>
       <c r="F72" t="n">
-        <v>0.1771041594278735</v>
+        <v>0.1771041594278734</v>
       </c>
     </row>
     <row r="73">
@@ -2337,13 +2337,13 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.111299334707123</v>
+        <v>0.1112993347071229</v>
       </c>
       <c r="E74" t="n">
-        <v>0.111299334707123</v>
+        <v>0.1112993347071229</v>
       </c>
       <c r="F74" t="n">
-        <v>0.07342997525655154</v>
+        <v>0.07342997525655152</v>
       </c>
     </row>
     <row r="75">
@@ -2363,10 +2363,10 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.3595356312478757</v>
+        <v>0.3595356312478758</v>
       </c>
       <c r="E75" t="n">
-        <v>0.3595356312478757</v>
+        <v>0.3595356312478758</v>
       </c>
       <c r="F75" t="n">
         <v>0.2372044053619178</v>
@@ -2389,10 +2389,10 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>-0.2956577858396832</v>
+        <v>-0.2956577858396833</v>
       </c>
       <c r="E76" t="n">
-        <v>0.2956577858396832</v>
+        <v>0.2956577858396833</v>
       </c>
       <c r="F76" t="n">
         <v>0.1950608595796516</v>
@@ -2421,7 +2421,7 @@
         <v>0.2394151921092406</v>
       </c>
       <c r="F77" t="n">
-        <v>0.157954687500023</v>
+        <v>0.1579546875000229</v>
       </c>
     </row>
     <row r="78">
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>-0.2640915362424739</v>
+        <v>-0.2640915362424738</v>
       </c>
       <c r="E81" t="n">
-        <v>0.2640915362424739</v>
+        <v>0.2640915362424738</v>
       </c>
       <c r="F81" t="n">
-        <v>0.1742349585716659</v>
+        <v>0.1742349585716658</v>
       </c>
     </row>
     <row r="82">
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>-0.2908239202239662</v>
+        <v>-0.2908239202239663</v>
       </c>
       <c r="E82" t="n">
-        <v>0.2908239202239662</v>
+        <v>0.2908239202239663</v>
       </c>
       <c r="F82" t="n">
         <v>0.1918717063516505</v>
@@ -2577,7 +2577,7 @@
         <v>0.1825353590884093</v>
       </c>
       <c r="F83" t="n">
-        <v>0.1204280954291261</v>
+        <v>0.120428095429126</v>
       </c>
     </row>
     <row r="84">
@@ -2597,13 +2597,13 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>-0.08024786201111699</v>
+        <v>-0.08024786201111687</v>
       </c>
       <c r="E84" t="n">
-        <v>0.08024786201111699</v>
+        <v>0.08024786201111687</v>
       </c>
       <c r="F84" t="n">
-        <v>0.05294369941539612</v>
+        <v>0.05294369941539604</v>
       </c>
     </row>
     <row r="85">
@@ -2629,7 +2629,7 @@
         <v>0.3214604661168977</v>
       </c>
       <c r="F85" t="n">
-        <v>0.2120842333427952</v>
+        <v>0.2120842333427951</v>
       </c>
     </row>
     <row r="86">
@@ -2681,7 +2681,7 @@
         <v>0.4785528407944308</v>
       </c>
       <c r="F87" t="n">
-        <v>0.3157262651295848</v>
+        <v>0.3157262651295847</v>
       </c>
     </row>
     <row r="88">
@@ -2727,10 +2727,10 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>-0.2728701254506481</v>
+        <v>-0.2728701254506482</v>
       </c>
       <c r="E89" t="n">
-        <v>0.2728701254506481</v>
+        <v>0.2728701254506482</v>
       </c>
       <c r="F89" t="n">
         <v>0.1800266516670462</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>-0.3436245415470213</v>
+        <v>-0.3436245415470214</v>
       </c>
       <c r="E91" t="n">
-        <v>0.3436245415470213</v>
+        <v>0.3436245415470214</v>
       </c>
       <c r="F91" t="n">
         <v>0.2267070297386676</v>
@@ -2805,13 +2805,13 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.06100052785126204</v>
+        <v>0.06100052785126208</v>
       </c>
       <c r="E92" t="n">
-        <v>0.06100052785126204</v>
+        <v>0.06100052785126208</v>
       </c>
       <c r="F92" t="n">
-        <v>0.04024522934069336</v>
+        <v>0.04024522934069338</v>
       </c>
     </row>
     <row r="93">
@@ -2831,13 +2831,13 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0.6124514152590662</v>
+        <v>0.612451415259066</v>
       </c>
       <c r="E93" t="n">
-        <v>0.6124514152590662</v>
+        <v>0.612451415259066</v>
       </c>
       <c r="F93" t="n">
-        <v>0.4040661373821767</v>
+        <v>0.4040661373821764</v>
       </c>
     </row>
     <row r="94">
@@ -2857,13 +2857,13 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0.0863418224897991</v>
+        <v>0.08634182248979913</v>
       </c>
       <c r="E94" t="n">
-        <v>0.0863418224897991</v>
+        <v>0.08634182248979913</v>
       </c>
       <c r="F94" t="n">
-        <v>0.05696420293719653</v>
+        <v>0.05696420293719655</v>
       </c>
     </row>
     <row r="95">
@@ -2889,7 +2889,7 @@
         <v>0.3574406206475763</v>
       </c>
       <c r="F95" t="n">
-        <v>0.2358222176161688</v>
+        <v>0.2358222176161687</v>
       </c>
     </row>
     <row r="96">
@@ -2909,13 +2909,13 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.2083441282725199</v>
+        <v>0.2083441282725198</v>
       </c>
       <c r="E96" t="n">
-        <v>0.2083441282725199</v>
+        <v>0.2083441282725198</v>
       </c>
       <c r="F96" t="n">
-        <v>0.1374554863616795</v>
+        <v>0.1374554863616794</v>
       </c>
     </row>
     <row r="97">
@@ -2987,13 +2987,13 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>-0.07226624911840762</v>
+        <v>-0.0722662491184077</v>
       </c>
       <c r="E99" t="n">
-        <v>0.07226624911840762</v>
+        <v>0.0722662491184077</v>
       </c>
       <c r="F99" t="n">
-        <v>0.04767781315685488</v>
+        <v>0.04767781315685492</v>
       </c>
     </row>
     <row r="100">
@@ -3019,7 +3019,7 @@
         <v>0.2627912214334839</v>
       </c>
       <c r="F100" t="n">
-        <v>0.1733770730820436</v>
+        <v>0.1733770730820435</v>
       </c>
     </row>
     <row r="101">
@@ -3065,10 +3065,10 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.07358052296812424</v>
+        <v>0.07358052296812426</v>
       </c>
       <c r="E102" t="n">
-        <v>0.07358052296812424</v>
+        <v>0.07358052296812426</v>
       </c>
       <c r="F102" t="n">
         <v>0.04854490815359477</v>
@@ -3117,10 +3117,10 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>-0.4117658492051711</v>
+        <v>-0.4117658492051712</v>
       </c>
       <c r="E104" t="n">
-        <v>0.4117658492051711</v>
+        <v>0.4117658492051712</v>
       </c>
       <c r="F104" t="n">
         <v>0.2716634039025716</v>
@@ -3175,7 +3175,7 @@
         <v>0.1469458685259343</v>
       </c>
       <c r="F106" t="n">
-        <v>0.09694785254831609</v>
+        <v>0.09694785254831606</v>
       </c>
     </row>
     <row r="107">
@@ -3195,10 +3195,10 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0.02957639128356524</v>
+        <v>0.02957639128356525</v>
       </c>
       <c r="E107" t="n">
-        <v>0.02957639128356524</v>
+        <v>0.02957639128356525</v>
       </c>
       <c r="F107" t="n">
         <v>0.01951308770933104</v>
@@ -3279,7 +3279,7 @@
         <v>0.3392202591308543</v>
       </c>
       <c r="F110" t="n">
-        <v>0.2238012949497488</v>
+        <v>0.2238012949497487</v>
       </c>
     </row>
     <row r="111">
@@ -3299,13 +3299,13 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>-0.06175104805696557</v>
+        <v>-0.06175104805696559</v>
       </c>
       <c r="E111" t="n">
-        <v>0.06175104805696557</v>
+        <v>0.06175104805696559</v>
       </c>
       <c r="F111" t="n">
-        <v>0.04074038665928265</v>
+        <v>0.04074038665928267</v>
       </c>
     </row>
     <row r="112">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>-0.1391549418787721</v>
+        <v>-0.1391549418787722</v>
       </c>
       <c r="E112" t="n">
-        <v>0.1391549418787721</v>
+        <v>0.1391549418787722</v>
       </c>
       <c r="F112" t="n">
         <v>0.09180777195006148</v>
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0.02677083471440831</v>
+        <v>0.02677083471440832</v>
       </c>
       <c r="E113" t="n">
-        <v>0.02677083471440831</v>
+        <v>0.02677083471440832</v>
       </c>
       <c r="F113" t="n">
         <v>0.01766211573365701</v>
@@ -3383,7 +3383,7 @@
         <v>0.1282887699375677</v>
       </c>
       <c r="F114" t="n">
-        <v>0.08463879166032566</v>
+        <v>0.08463879166032562</v>
       </c>
     </row>
     <row r="115">
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.3485336964355675</v>
+        <v>0.3485336964355674</v>
       </c>
       <c r="E115" t="n">
-        <v>0.3485336964355675</v>
+        <v>0.3485336964355674</v>
       </c>
       <c r="F115" t="n">
         <v>0.2299458552262152</v>
@@ -3429,13 +3429,13 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.04312474956893262</v>
+        <v>0.04312474956893264</v>
       </c>
       <c r="E116" t="n">
-        <v>0.04312474956893262</v>
+        <v>0.04312474956893264</v>
       </c>
       <c r="F116" t="n">
-        <v>0.02845164620367712</v>
+        <v>0.02845164620367713</v>
       </c>
     </row>
     <row r="117">
@@ -3461,7 +3461,7 @@
         <v>0.262898038425264</v>
       </c>
       <c r="F117" t="n">
-        <v>0.1734475458219214</v>
+        <v>0.1734475458219213</v>
       </c>
     </row>
     <row r="118">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>0.2270766956747885</v>
+        <v>0.2270766956747884</v>
       </c>
       <c r="E119" t="n">
-        <v>0.2270766956747885</v>
+        <v>0.2270766956747884</v>
       </c>
       <c r="F119" t="n">
-        <v>0.1498143379618251</v>
+        <v>0.1498143379618249</v>
       </c>
     </row>
     <row r="120">
@@ -3565,7 +3565,7 @@
         <v>0.5214397614291514</v>
       </c>
       <c r="F121" t="n">
-        <v>0.3440210031828185</v>
+        <v>0.3440210031828184</v>
       </c>
     </row>
     <row r="122">
@@ -3611,13 +3611,13 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>-0.1975116599540623</v>
+        <v>-0.1975116599540619</v>
       </c>
       <c r="E123" t="n">
-        <v>0.1975116599540623</v>
+        <v>0.1975116599540619</v>
       </c>
       <c r="F123" t="n">
-        <v>0.1303087421094803</v>
+        <v>0.13030874210948</v>
       </c>
     </row>
     <row r="124">
@@ -3637,13 +3637,13 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>-0.06195984287419792</v>
+        <v>-0.06195984287419787</v>
       </c>
       <c r="E124" t="n">
-        <v>0.06195984287419792</v>
+        <v>0.06195984287419787</v>
       </c>
       <c r="F124" t="n">
-        <v>0.04087813948865412</v>
+        <v>0.04087813948865408</v>
       </c>
     </row>
     <row r="125">
@@ -3663,13 +3663,13 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>-0.09217726763235914</v>
+        <v>-0.09217726763235919</v>
       </c>
       <c r="E125" t="n">
-        <v>0.09217726763235914</v>
+        <v>0.09217726763235919</v>
       </c>
       <c r="F125" t="n">
-        <v>0.06081415041043804</v>
+        <v>0.06081415041043805</v>
       </c>
     </row>
     <row r="126">
@@ -3689,13 +3689,13 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>-0.03833778901507949</v>
+        <v>-0.03833778901507943</v>
       </c>
       <c r="E126" t="n">
-        <v>0.03833778901507949</v>
+        <v>0.03833778901507943</v>
       </c>
       <c r="F126" t="n">
-        <v>0.02529343869104023</v>
+        <v>0.02529343869104019</v>
       </c>
     </row>
     <row r="127">
@@ -3721,7 +3721,7 @@
         <v>0.5170222960934284</v>
       </c>
       <c r="F127" t="n">
-        <v>0.3411065709343924</v>
+        <v>0.3411065709343923</v>
       </c>
     </row>
     <row r="128">
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>-0.290068504127602</v>
+        <v>-0.2900685041276017</v>
       </c>
       <c r="E128" t="n">
-        <v>0.290068504127602</v>
+        <v>0.2900685041276017</v>
       </c>
       <c r="F128" t="n">
-        <v>0.1913733189586765</v>
+        <v>0.1913733189586763</v>
       </c>
     </row>
     <row r="129">
@@ -3773,7 +3773,7 @@
         <v>0.1369732064754696</v>
       </c>
       <c r="F129" t="n">
-        <v>0.09036836732915862</v>
+        <v>0.09036836732915858</v>
       </c>
     </row>
     <row r="130">
@@ -3793,13 +3793,13 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0.2776067594993098</v>
+        <v>0.2776067594993097</v>
       </c>
       <c r="E130" t="n">
-        <v>0.2776067594993098</v>
+        <v>0.2776067594993097</v>
       </c>
       <c r="F130" t="n">
-        <v>0.1831516561597308</v>
+        <v>0.1831516561597307</v>
       </c>
     </row>
     <row r="131">
@@ -3819,13 +3819,13 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>-0.0349005760040867</v>
+        <v>-0.03490057600408691</v>
       </c>
       <c r="E131" t="n">
-        <v>0.0349005760040867</v>
+        <v>0.03490057600408691</v>
       </c>
       <c r="F131" t="n">
-        <v>0.02302573002042816</v>
+        <v>0.0230257300204283</v>
       </c>
     </row>
     <row r="132">
@@ -3845,13 +3845,13 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>0.1439443037425318</v>
+        <v>0.1439443037425319</v>
       </c>
       <c r="E132" t="n">
-        <v>0.1439443037425318</v>
+        <v>0.1439443037425319</v>
       </c>
       <c r="F132" t="n">
-        <v>0.09496756373206965</v>
+        <v>0.09496756373206967</v>
       </c>
     </row>
     <row r="133">
@@ -3871,13 +3871,13 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>-0.1596479044383413</v>
+        <v>-0.1596479044383414</v>
       </c>
       <c r="E133" t="n">
-        <v>0.1596479044383413</v>
+        <v>0.1596479044383414</v>
       </c>
       <c r="F133" t="n">
-        <v>0.1053280480383452</v>
+        <v>0.1053280480383453</v>
       </c>
     </row>
     <row r="134">
@@ -3903,7 +3903,7 @@
         <v>0.2647468936334678</v>
       </c>
       <c r="F134" t="n">
-        <v>0.1746673320187446</v>
+        <v>0.1746673320187445</v>
       </c>
     </row>
     <row r="135">
@@ -3923,10 +3923,10 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>0.4233439067965398</v>
+        <v>0.4233439067965399</v>
       </c>
       <c r="E135" t="n">
-        <v>0.4233439067965398</v>
+        <v>0.4233439067965399</v>
       </c>
       <c r="F135" t="n">
         <v>0.2793020522798537</v>
@@ -3949,10 +3949,10 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>0.3339157546823793</v>
+        <v>0.3339157546823794</v>
       </c>
       <c r="E136" t="n">
-        <v>0.3339157546823793</v>
+        <v>0.3339157546823794</v>
       </c>
       <c r="F136" t="n">
         <v>0.2203016367404274</v>
@@ -3981,7 +3981,7 @@
         <v>0.2858083788561387</v>
       </c>
       <c r="F137" t="n">
-        <v>0.1885626921557713</v>
+        <v>0.1885626921557712</v>
       </c>
     </row>
     <row r="138">
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>-0.1191672382391928</v>
+        <v>-0.1191672382391929</v>
       </c>
       <c r="E138" t="n">
-        <v>0.1191672382391928</v>
+        <v>0.1191672382391929</v>
       </c>
       <c r="F138" t="n">
         <v>0.0786208415200482</v>
@@ -4027,13 +4027,13 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>-0.1980165995948732</v>
+        <v>-0.1980165995948731</v>
       </c>
       <c r="E139" t="n">
-        <v>0.1980165995948732</v>
+        <v>0.1980165995948731</v>
       </c>
       <c r="F139" t="n">
-        <v>0.1306418771226263</v>
+        <v>0.1306418771226262</v>
       </c>
     </row>
     <row r="140">
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>-0.1071797840745197</v>
+        <v>-0.1071797840745198</v>
       </c>
       <c r="E140" t="n">
-        <v>0.1071797840745197</v>
+        <v>0.1071797840745198</v>
       </c>
       <c r="F140" t="n">
         <v>0.07071209287373074</v>
@@ -4079,13 +4079,13 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>0.03483248353244399</v>
+        <v>0.03483248353244396</v>
       </c>
       <c r="E141" t="n">
-        <v>0.03483248353244399</v>
+        <v>0.03483248353244396</v>
       </c>
       <c r="F141" t="n">
-        <v>0.02298080586593039</v>
+        <v>0.02298080586593037</v>
       </c>
     </row>
     <row r="142">
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>-0.4826886402231794</v>
+        <v>-0.4826886402231795</v>
       </c>
       <c r="E142" t="n">
-        <v>0.4826886402231794</v>
+        <v>0.4826886402231795</v>
       </c>
       <c r="F142" t="n">
         <v>0.3184548676905814</v>
@@ -4131,13 +4131,13 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>-0.142283207124409</v>
+        <v>-0.1422832071244089</v>
       </c>
       <c r="E143" t="n">
-        <v>0.142283207124409</v>
+        <v>0.1422832071244089</v>
       </c>
       <c r="F143" t="n">
-        <v>0.09387165166854772</v>
+        <v>0.09387165166854763</v>
       </c>
     </row>
     <row r="144">
@@ -4157,10 +4157,10 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>0.5135248448984391</v>
+        <v>0.5135248448984392</v>
       </c>
       <c r="E144" t="n">
-        <v>0.5135248448984391</v>
+        <v>0.5135248448984392</v>
       </c>
       <c r="F144" t="n">
         <v>0.3387991199924361</v>
@@ -4183,13 +4183,13 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>-0.02927052199977992</v>
+        <v>-0.02927052199977994</v>
       </c>
       <c r="E145" t="n">
-        <v>0.02927052199977992</v>
+        <v>0.02927052199977994</v>
       </c>
       <c r="F145" t="n">
-        <v>0.01931128979203713</v>
+        <v>0.01931128979203714</v>
       </c>
     </row>
     <row r="146">
@@ -4209,13 +4209,13 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>-0.07867275643710447</v>
+        <v>-0.07867275643710443</v>
       </c>
       <c r="E146" t="n">
-        <v>0.07867275643710447</v>
+        <v>0.07867275643710443</v>
       </c>
       <c r="F146" t="n">
-        <v>0.0519045201280217</v>
+        <v>0.05190452012802167</v>
       </c>
     </row>
     <row r="147">
@@ -4261,10 +4261,10 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>0.2192438041588357</v>
+        <v>0.2192438041588358</v>
       </c>
       <c r="E148" t="n">
-        <v>0.2192438041588357</v>
+        <v>0.2192438041588358</v>
       </c>
       <c r="F148" t="n">
         <v>0.1446465709512029</v>
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>-0.4451527170254869</v>
+        <v>-0.445152717025487</v>
       </c>
       <c r="E149" t="n">
-        <v>0.4451527170254869</v>
+        <v>0.445152717025487</v>
       </c>
       <c r="F149" t="n">
         <v>0.2936904616957809</v>
@@ -4313,13 +4313,13 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>0.3468526708583281</v>
+        <v>0.346852670858328</v>
       </c>
       <c r="E150" t="n">
-        <v>0.3468526708583281</v>
+        <v>0.346852670858328</v>
       </c>
       <c r="F150" t="n">
-        <v>0.2288367949890886</v>
+        <v>0.2288367949890885</v>
       </c>
     </row>
     <row r="151">
@@ -4417,13 +4417,13 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>-0.01976679893959481</v>
+        <v>-0.01976679893959477</v>
       </c>
       <c r="E154" t="n">
-        <v>0.01976679893959481</v>
+        <v>0.01976679893959477</v>
       </c>
       <c r="F154" t="n">
-        <v>0.01304118807947182</v>
+        <v>0.01304118807947179</v>
       </c>
     </row>
     <row r="155">
@@ -4443,13 +4443,13 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>-0.2180870442213675</v>
+        <v>-0.2180870442213674</v>
       </c>
       <c r="E155" t="n">
-        <v>0.2180870442213675</v>
+        <v>0.2180870442213674</v>
       </c>
       <c r="F155" t="n">
-        <v>0.1438833960965681</v>
+        <v>0.143883396096568</v>
       </c>
     </row>
     <row r="156">
@@ -4469,13 +4469,13 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>0.1178799029148214</v>
+        <v>0.1178799029148213</v>
       </c>
       <c r="E156" t="n">
-        <v>0.1178799029148214</v>
+        <v>0.1178799029148213</v>
       </c>
       <c r="F156" t="n">
-        <v>0.07777151927329597</v>
+        <v>0.07777151927329592</v>
       </c>
     </row>
     <row r="157">
@@ -4521,10 +4521,10 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>0.1766380826345331</v>
+        <v>0.1766380826345332</v>
       </c>
       <c r="E158" t="n">
-        <v>0.1766380826345331</v>
+        <v>0.1766380826345332</v>
       </c>
       <c r="F158" t="n">
         <v>0.1165373546153676</v>
@@ -4579,7 +4579,7 @@
         <v>0.4017484266877598</v>
       </c>
       <c r="F160" t="n">
-        <v>0.2650543878691554</v>
+        <v>0.2650543878691553</v>
       </c>
     </row>
     <row r="161">
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>0.09334636272745356</v>
+        <v>0.09334636272745357</v>
       </c>
       <c r="E161" t="n">
-        <v>0.09334636272745356</v>
+        <v>0.09334636272745357</v>
       </c>
       <c r="F161" t="n">
         <v>0.06158546341182514</v>
@@ -4625,13 +4625,13 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>0.108472994454547</v>
+        <v>0.1084729944545469</v>
       </c>
       <c r="E162" t="n">
-        <v>0.108472994454547</v>
+        <v>0.1084729944545469</v>
       </c>
       <c r="F162" t="n">
-        <v>0.07156529120107745</v>
+        <v>0.07156529120107738</v>
       </c>
     </row>
     <row r="163">
@@ -4651,13 +4651,13 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>0.1593988864140463</v>
+        <v>0.1593988864140461</v>
       </c>
       <c r="E163" t="n">
-        <v>0.1593988864140463</v>
+        <v>0.1593988864140461</v>
       </c>
       <c r="F163" t="n">
-        <v>0.105163757861674</v>
+        <v>0.1051637578616739</v>
       </c>
     </row>
     <row r="164">
@@ -4677,13 +4677,13 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>0.04491353994748729</v>
+        <v>0.04491353994748734</v>
       </c>
       <c r="E164" t="n">
-        <v>0.04491353994748729</v>
+        <v>0.04491353994748734</v>
       </c>
       <c r="F164" t="n">
-        <v>0.02963180450005929</v>
+        <v>0.02963180450005932</v>
       </c>
     </row>
     <row r="165">
@@ -4729,10 +4729,10 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>0.2055435686015052</v>
+        <v>0.2055435686015051</v>
       </c>
       <c r="E166" t="n">
-        <v>0.2055435686015052</v>
+        <v>0.2055435686015051</v>
       </c>
       <c r="F166" t="n">
         <v>0.1356078111002931</v>
@@ -4755,13 +4755,13 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>0.1222892155828622</v>
+        <v>0.122289215582862</v>
       </c>
       <c r="E167" t="n">
-        <v>0.1222892155828622</v>
+        <v>0.122289215582862</v>
       </c>
       <c r="F167" t="n">
-        <v>0.0806805727816986</v>
+        <v>0.08068057278169849</v>
       </c>
     </row>
     <row r="168">
@@ -4807,13 +4807,13 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>0.1630165922785031</v>
+        <v>0.1630165922785029</v>
       </c>
       <c r="E169" t="n">
-        <v>0.1630165922785031</v>
+        <v>0.1630165922785029</v>
       </c>
       <c r="F169" t="n">
-        <v>0.1075505470802401</v>
+        <v>0.10755054708024</v>
       </c>
     </row>
     <row r="170">
@@ -4833,13 +4833,13 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>0.4175375177381173</v>
+        <v>0.4175375177381172</v>
       </c>
       <c r="E170" t="n">
-        <v>0.4175375177381173</v>
+        <v>0.4175375177381172</v>
       </c>
       <c r="F170" t="n">
-        <v>0.2754712746205637</v>
+        <v>0.2754712746205636</v>
       </c>
     </row>
     <row r="171">
@@ -4865,7 +4865,7 @@
         <v>0.1289008711279852</v>
       </c>
       <c r="F171" t="n">
-        <v>0.08504262673611594</v>
+        <v>0.08504262673611596</v>
       </c>
     </row>
     <row r="172">
@@ -4891,7 +4891,7 @@
         <v>0.1241768892143308</v>
       </c>
       <c r="F172" t="n">
-        <v>0.081925969516692</v>
+        <v>0.08192596951669198</v>
       </c>
     </row>
     <row r="173">
@@ -4911,13 +4911,13 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>-0.03416981151427637</v>
+        <v>-0.03416981151427625</v>
       </c>
       <c r="E173" t="n">
-        <v>0.03416981151427637</v>
+        <v>0.03416981151427625</v>
       </c>
       <c r="F173" t="n">
-        <v>0.02254360657785465</v>
+        <v>0.02254360657785457</v>
       </c>
     </row>
     <row r="174">
@@ -4937,13 +4937,13 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>0.2376313760575365</v>
+        <v>0.2376313760575364</v>
       </c>
       <c r="E174" t="n">
-        <v>0.2376313760575365</v>
+        <v>0.2376313760575364</v>
       </c>
       <c r="F174" t="n">
-        <v>0.1567778110264704</v>
+        <v>0.1567778110264703</v>
       </c>
     </row>
     <row r="175">
@@ -4963,13 +4963,13 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>0.1155647108566096</v>
+        <v>0.1155647108566097</v>
       </c>
       <c r="E175" t="n">
-        <v>0.1155647108566096</v>
+        <v>0.1155647108566097</v>
       </c>
       <c r="F175" t="n">
-        <v>0.07624406633751689</v>
+        <v>0.07624406633751694</v>
       </c>
     </row>
     <row r="176">
@@ -4989,13 +4989,13 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>0.2788639021465562</v>
+        <v>0.2788639021465563</v>
       </c>
       <c r="E176" t="n">
-        <v>0.2788639021465562</v>
+        <v>0.2788639021465563</v>
       </c>
       <c r="F176" t="n">
-        <v>0.1839810587228653</v>
+        <v>0.1839810587228654</v>
       </c>
     </row>
     <row r="177">
@@ -5015,13 +5015,13 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>0.02225171357804165</v>
+        <v>0.0222517135780417</v>
       </c>
       <c r="E177" t="n">
-        <v>0.02225171357804165</v>
+        <v>0.0222517135780417</v>
       </c>
       <c r="F177" t="n">
-        <v>0.01468061585229674</v>
+        <v>0.01468061585229678</v>
       </c>
     </row>
     <row r="178">
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>-0.5295871836104394</v>
+        <v>-0.5295871836104395</v>
       </c>
       <c r="E178" t="n">
-        <v>0.5295871836104394</v>
+        <v>0.5295871836104395</v>
       </c>
       <c r="F178" t="n">
         <v>0.3493962824758256</v>
@@ -5067,13 +5067,13 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>-0.2576344514532181</v>
+        <v>-0.2576344514532183</v>
       </c>
       <c r="E179" t="n">
-        <v>0.2576344514532181</v>
+        <v>0.2576344514532183</v>
       </c>
       <c r="F179" t="n">
-        <v>0.1699748830056063</v>
+        <v>0.1699748830056064</v>
       </c>
     </row>
     <row r="180">
@@ -5099,7 +5099,7 @@
         <v>0.3901617193819207</v>
       </c>
       <c r="F180" t="n">
-        <v>0.2574100328241632</v>
+        <v>0.2574100328241631</v>
       </c>
     </row>
     <row r="181">
@@ -5119,13 +5119,13 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>-0.2500141122253303</v>
+        <v>-0.2500141122253302</v>
       </c>
       <c r="E181" t="n">
-        <v>0.2500141122253303</v>
+        <v>0.2500141122253302</v>
       </c>
       <c r="F181" t="n">
-        <v>0.1649473478238122</v>
+        <v>0.1649473478238121</v>
       </c>
     </row>
     <row r="182">
@@ -5171,13 +5171,13 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>-0.06634882451767586</v>
+        <v>-0.06634882451767576</v>
       </c>
       <c r="E183" t="n">
-        <v>0.06634882451767586</v>
+        <v>0.06634882451767576</v>
       </c>
       <c r="F183" t="n">
-        <v>0.04377377955990981</v>
+        <v>0.04377377955990974</v>
       </c>
     </row>
     <row r="184">
@@ -5203,7 +5203,7 @@
         <v>0.8156719097497791</v>
       </c>
       <c r="F184" t="n">
-        <v>0.5381412953455621</v>
+        <v>0.538141295345562</v>
       </c>
     </row>
     <row r="185">
@@ -5223,13 +5223,13 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>0.4428150813781883</v>
+        <v>0.4428150813781882</v>
       </c>
       <c r="E185" t="n">
-        <v>0.4428150813781883</v>
+        <v>0.4428150813781882</v>
       </c>
       <c r="F185" t="n">
-        <v>0.2921482015538703</v>
+        <v>0.2921482015538701</v>
       </c>
     </row>
     <row r="186">
@@ -5275,13 +5275,13 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>-0.09531441779033277</v>
+        <v>-0.09531441779033291</v>
       </c>
       <c r="E187" t="n">
-        <v>0.09531441779033277</v>
+        <v>0.09531441779033291</v>
       </c>
       <c r="F187" t="n">
-        <v>0.06288389196893225</v>
+        <v>0.06288389196893233</v>
       </c>
     </row>
     <row r="188">
@@ -5301,13 +5301,13 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>-0.9127330151836273</v>
+        <v>-0.9127330151836275</v>
       </c>
       <c r="E188" t="n">
-        <v>0.9127330151836273</v>
+        <v>0.9127330151836275</v>
       </c>
       <c r="F188" t="n">
-        <v>0.602177568240955</v>
+        <v>0.6021775682409551</v>
       </c>
     </row>
     <row r="189">
@@ -5405,13 +5405,13 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>-0.4637260065706525</v>
+        <v>-0.4637260065706528</v>
       </c>
       <c r="E192" t="n">
-        <v>0.4637260065706525</v>
+        <v>0.4637260065706528</v>
       </c>
       <c r="F192" t="n">
-        <v>0.3059442293874129</v>
+        <v>0.3059442293874131</v>
       </c>
     </row>
     <row r="193">
@@ -5431,13 +5431,13 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>0.4785102086747804</v>
+        <v>0.4785102086747803</v>
       </c>
       <c r="E193" t="n">
-        <v>0.4785102086747804</v>
+        <v>0.4785102086747803</v>
       </c>
       <c r="F193" t="n">
-        <v>0.3156981384970286</v>
+        <v>0.3156981384970284</v>
       </c>
     </row>
     <row r="194">
@@ -5463,7 +5463,7 @@
         <v>0.1027545573495628</v>
       </c>
       <c r="F194" t="n">
-        <v>0.06779254003207821</v>
+        <v>0.0677925400320782</v>
       </c>
     </row>
     <row r="195">
@@ -5483,13 +5483,13 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>0.2339641274629752</v>
+        <v>0.2339641274629753</v>
       </c>
       <c r="E195" t="n">
-        <v>0.2339641274629752</v>
+        <v>0.2339641274629753</v>
       </c>
       <c r="F195" t="n">
-        <v>0.1543583358852499</v>
+        <v>0.15435833588525</v>
       </c>
     </row>
     <row r="196">
@@ -5515,7 +5515,7 @@
         <v>0.2605529485852828</v>
       </c>
       <c r="F196" t="n">
-        <v>0.1719003677603693</v>
+        <v>0.1719003677603692</v>
       </c>
     </row>
     <row r="197">
@@ -5535,10 +5535,10 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>0.257974013919511</v>
+        <v>0.2579740139195111</v>
       </c>
       <c r="E197" t="n">
-        <v>0.257974013919511</v>
+        <v>0.2579740139195111</v>
       </c>
       <c r="F197" t="n">
         <v>0.1701989100724666</v>
@@ -5567,7 +5567,7 @@
         <v>0.5540818398462158</v>
       </c>
       <c r="F198" t="n">
-        <v>0.3655566845666719</v>
+        <v>0.3655566845666718</v>
       </c>
     </row>
     <row r="199">
@@ -5593,7 +5593,7 @@
         <v>0.5391986065954352</v>
       </c>
       <c r="F199" t="n">
-        <v>0.3557374394452331</v>
+        <v>0.355737439445233</v>
       </c>
     </row>
     <row r="200">
@@ -5619,7 +5619,7 @@
         <v>0.1121477602507695</v>
       </c>
       <c r="F200" t="n">
-        <v>0.07398972583224844</v>
+        <v>0.07398972583224843</v>
       </c>
     </row>
     <row r="201">
@@ -5639,13 +5639,13 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>-0.4749388789002536</v>
+        <v>-0.4749388789002535</v>
       </c>
       <c r="E201" t="n">
-        <v>0.4749388789002536</v>
+        <v>0.4749388789002535</v>
       </c>
       <c r="F201" t="n">
-        <v>0.3133419460034566</v>
+        <v>0.3133419460034564</v>
       </c>
     </row>
     <row r="202">
@@ -5665,13 +5665,13 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>0.02568030225822885</v>
+        <v>0.02568030225822884</v>
       </c>
       <c r="E202" t="n">
-        <v>0.02568030225822885</v>
+        <v>0.02568030225822884</v>
       </c>
       <c r="F202" t="n">
-        <v>0.01694263460212605</v>
+        <v>0.01694263460212603</v>
       </c>
     </row>
     <row r="203">
@@ -5691,13 +5691,13 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>-0.4284835228123414</v>
+        <v>-0.4284835228123413</v>
       </c>
       <c r="E203" t="n">
-        <v>0.4284835228123414</v>
+        <v>0.4284835228123413</v>
       </c>
       <c r="F203" t="n">
-        <v>0.2826929249913716</v>
+        <v>0.2826929249913715</v>
       </c>
     </row>
     <row r="204">
@@ -5717,13 +5717,13 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>0.03267165655842826</v>
+        <v>0.03267165655842827</v>
       </c>
       <c r="E204" t="n">
-        <v>0.03267165655842826</v>
+        <v>0.03267165655842827</v>
       </c>
       <c r="F204" t="n">
-        <v>0.02155519562618194</v>
+        <v>0.02155519562618195</v>
       </c>
     </row>
     <row r="205">
@@ -5749,7 +5749,7 @@
         <v>0.3660767187696763</v>
       </c>
       <c r="F205" t="n">
-        <v>0.2415199019112967</v>
+        <v>0.2415199019112966</v>
       </c>
     </row>
     <row r="206">
@@ -5795,13 +5795,13 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>0.0105911745169684</v>
+        <v>0.01059117451696839</v>
       </c>
       <c r="E207" t="n">
-        <v>0.0105911745169684</v>
+        <v>0.01059117451696839</v>
       </c>
       <c r="F207" t="n">
-        <v>0.006987550148123543</v>
+        <v>0.006987550148123536</v>
       </c>
     </row>
     <row r="208">
@@ -5821,10 +5821,10 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>-0.2903426046330606</v>
+        <v>-0.2903426046330607</v>
       </c>
       <c r="E208" t="n">
-        <v>0.2903426046330606</v>
+        <v>0.2903426046330607</v>
       </c>
       <c r="F208" t="n">
         <v>0.1915541573561979</v>
@@ -5847,13 +5847,13 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>0.5282747148179203</v>
+        <v>0.5282747148179201</v>
       </c>
       <c r="E209" t="n">
-        <v>0.5282747148179203</v>
+        <v>0.5282747148179201</v>
       </c>
       <c r="F209" t="n">
-        <v>0.3485303783694508</v>
+        <v>0.3485303783694506</v>
       </c>
     </row>
     <row r="210">
@@ -5879,7 +5879,7 @@
         <v>0.138668769725259</v>
       </c>
       <c r="F210" t="n">
-        <v>0.09148701882699171</v>
+        <v>0.09148701882699173</v>
       </c>
     </row>
     <row r="211">
@@ -5905,7 +5905,7 @@
         <v>0.4866541726635998</v>
       </c>
       <c r="F211" t="n">
-        <v>0.3210711362401228</v>
+        <v>0.3210711362401227</v>
       </c>
     </row>
     <row r="212">
@@ -5931,7 +5931,7 @@
         <v>0.1010057707741057</v>
       </c>
       <c r="F212" t="n">
-        <v>0.06663877433075828</v>
+        <v>0.06663877433075827</v>
       </c>
     </row>
     <row r="213">
@@ -5977,10 +5977,10 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>0.06936591482911791</v>
+        <v>0.06936591482911793</v>
       </c>
       <c r="E214" t="n">
-        <v>0.06936591482911791</v>
+        <v>0.06936591482911793</v>
       </c>
       <c r="F214" t="n">
         <v>0.04576431137664486</v>
@@ -6003,13 +6003,13 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>-0.06250251937787414</v>
+        <v>-0.0625025193778741</v>
       </c>
       <c r="E215" t="n">
-        <v>0.06250251937787414</v>
+        <v>0.0625025193778741</v>
       </c>
       <c r="F215" t="n">
-        <v>0.04123617147817244</v>
+        <v>0.04123617147817241</v>
       </c>
     </row>
     <row r="216">
@@ -6029,13 +6029,13 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>0.008826568692098359</v>
+        <v>0.008826568692098365</v>
       </c>
       <c r="E216" t="n">
-        <v>0.008826568692098359</v>
+        <v>0.008826568692098365</v>
       </c>
       <c r="F216" t="n">
-        <v>0.005823347663007689</v>
+        <v>0.005823347663007692</v>
       </c>
     </row>
     <row r="217">
@@ -6055,13 +6055,13 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>0.1196586747961976</v>
+        <v>0.1196586747961975</v>
       </c>
       <c r="E217" t="n">
-        <v>0.1196586747961976</v>
+        <v>0.1196586747961975</v>
       </c>
       <c r="F217" t="n">
-        <v>0.07894506784463477</v>
+        <v>0.07894506784463472</v>
       </c>
     </row>
     <row r="218">
@@ -6087,7 +6087,7 @@
         <v>0.2723028916186313</v>
       </c>
       <c r="F218" t="n">
-        <v>0.1796524179273812</v>
+        <v>0.1796524179273811</v>
       </c>
     </row>
     <row r="219">
@@ -6107,13 +6107,13 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>-0.1188168835717075</v>
+        <v>-0.1188168835717077</v>
       </c>
       <c r="E219" t="n">
-        <v>0.1188168835717075</v>
+        <v>0.1188168835717077</v>
       </c>
       <c r="F219" t="n">
-        <v>0.07838969427525863</v>
+        <v>0.07838969427525873</v>
       </c>
     </row>
     <row r="220">
@@ -6185,13 +6185,13 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>0.0615242494494301</v>
+        <v>0.06152424944943009</v>
       </c>
       <c r="E222" t="n">
-        <v>0.0615242494494301</v>
+        <v>0.06152424944943009</v>
       </c>
       <c r="F222" t="n">
-        <v>0.04059075579056836</v>
+        <v>0.04059075579056835</v>
       </c>
     </row>
     <row r="223">
@@ -6211,10 +6211,10 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>0.4927950582570121</v>
+        <v>0.4927950582570122</v>
       </c>
       <c r="E223" t="n">
-        <v>0.4927950582570121</v>
+        <v>0.4927950582570122</v>
       </c>
       <c r="F223" t="n">
         <v>0.325122598707209</v>
@@ -6237,13 +6237,13 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>-0.300657525696652</v>
+        <v>-0.3006575256966522</v>
       </c>
       <c r="E224" t="n">
-        <v>0.300657525696652</v>
+        <v>0.3006575256966522</v>
       </c>
       <c r="F224" t="n">
-        <v>0.1983594486947842</v>
+        <v>0.1983594486947843</v>
       </c>
     </row>
     <row r="225">
@@ -6263,13 +6263,13 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>0.02328289865493444</v>
+        <v>0.02328289865493431</v>
       </c>
       <c r="E225" t="n">
-        <v>0.02328289865493444</v>
+        <v>0.02328289865493431</v>
       </c>
       <c r="F225" t="n">
-        <v>0.01536094242280514</v>
+        <v>0.01536094242280505</v>
       </c>
     </row>
     <row r="226">
@@ -6289,13 +6289,13 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>-0.04879525642099165</v>
+        <v>-0.04879525642099163</v>
       </c>
       <c r="E226" t="n">
-        <v>0.04879525642099165</v>
+        <v>0.04879525642099163</v>
       </c>
       <c r="F226" t="n">
-        <v>0.03219277528530633</v>
+        <v>0.03219277528530631</v>
       </c>
     </row>
     <row r="227">
@@ -6315,13 +6315,13 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>-0.01237287969440777</v>
+        <v>-0.01237287969440778</v>
       </c>
       <c r="E227" t="n">
-        <v>0.01237287969440777</v>
+        <v>0.01237287969440778</v>
       </c>
       <c r="F227" t="n">
-        <v>0.008163033967843713</v>
+        <v>0.00816303396784372</v>
       </c>
     </row>
     <row r="228">
@@ -6341,13 +6341,13 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>-0.02048615286616472</v>
+        <v>-0.02048615286616465</v>
       </c>
       <c r="E228" t="n">
-        <v>0.02048615286616472</v>
+        <v>0.02048615286616465</v>
       </c>
       <c r="F228" t="n">
-        <v>0.01351578337842603</v>
+        <v>0.01351578337842598</v>
       </c>
     </row>
     <row r="229">
@@ -6367,13 +6367,13 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>-0.05721181326401194</v>
+        <v>-0.05721181326401191</v>
       </c>
       <c r="E229" t="n">
-        <v>0.05721181326401194</v>
+        <v>0.05721181326401191</v>
       </c>
       <c r="F229" t="n">
-        <v>0.03774561674976467</v>
+        <v>0.03774561674976464</v>
       </c>
     </row>
     <row r="230">
@@ -6399,7 +6399,7 @@
         <v>0.03151746853254632</v>
       </c>
       <c r="F230" t="n">
-        <v>0.02079371759574324</v>
+        <v>0.02079371759574323</v>
       </c>
     </row>
     <row r="231">
@@ -6425,7 +6425,7 @@
         <v>0.1266419037833108</v>
       </c>
       <c r="F231" t="n">
-        <v>0.08355226817592071</v>
+        <v>0.08355226817592069</v>
       </c>
     </row>
     <row r="232">
@@ -6445,13 +6445,13 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>0.0716488354152051</v>
+        <v>0.07164883541520507</v>
       </c>
       <c r="E232" t="n">
-        <v>0.0716488354152051</v>
+        <v>0.07164883541520507</v>
       </c>
       <c r="F232" t="n">
-        <v>0.04727047313933799</v>
+        <v>0.04727047313933797</v>
       </c>
     </row>
     <row r="233">
@@ -6471,13 +6471,13 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>-0.03826042204742452</v>
+        <v>-0.0382604220474245</v>
       </c>
       <c r="E233" t="n">
-        <v>0.03826042204742452</v>
+        <v>0.0382604220474245</v>
       </c>
       <c r="F233" t="n">
-        <v>0.02524239566786738</v>
+        <v>0.02524239566786736</v>
       </c>
     </row>
     <row r="234">
@@ -6529,7 +6529,7 @@
         <v>0.1164793041784383</v>
       </c>
       <c r="F235" t="n">
-        <v>0.07684747124706476</v>
+        <v>0.07684747124706469</v>
       </c>
     </row>
     <row r="236">
@@ -6549,13 +6549,13 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>-0.003150879813793619</v>
+        <v>-0.003150879813793613</v>
       </c>
       <c r="E236" t="n">
-        <v>0.003150879813793619</v>
+        <v>0.003150879813793613</v>
       </c>
       <c r="F236" t="n">
-        <v>0.002078799728426643</v>
+        <v>0.002078799728426639</v>
       </c>
     </row>
     <row r="237">
@@ -6581,7 +6581,7 @@
         <v>0.1374551550478915</v>
       </c>
       <c r="F237" t="n">
-        <v>0.0906863339355269</v>
+        <v>0.09068633393552684</v>
       </c>
     </row>
     <row r="238">
@@ -6607,7 +6607,7 @@
         <v>0.1280855125210753</v>
       </c>
       <c r="F238" t="n">
-        <v>0.08450469214299229</v>
+        <v>0.08450469214299228</v>
       </c>
     </row>
     <row r="239">
@@ -6627,13 +6627,13 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>-0.02022698223041923</v>
+        <v>-0.02022698223041922</v>
       </c>
       <c r="E239" t="n">
-        <v>0.02022698223041923</v>
+        <v>0.02022698223041922</v>
       </c>
       <c r="F239" t="n">
-        <v>0.01334479499453232</v>
+        <v>0.01334479499453231</v>
       </c>
     </row>
     <row r="240">
@@ -6653,13 +6653,13 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>0.149586216054435</v>
+        <v>0.1495862160544351</v>
       </c>
       <c r="E240" t="n">
-        <v>0.149586216054435</v>
+        <v>0.1495862160544351</v>
       </c>
       <c r="F240" t="n">
-        <v>0.09868982750438103</v>
+        <v>0.09868982750438109</v>
       </c>
     </row>
     <row r="241">
@@ -6705,10 +6705,10 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>0.5969012193132609</v>
+        <v>0.596901219313261</v>
       </c>
       <c r="E242" t="n">
-        <v>0.5969012193132609</v>
+        <v>0.596901219313261</v>
       </c>
       <c r="F242" t="n">
         <v>0.3938068621893849</v>
@@ -6757,13 +6757,13 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>-0.6481099056235756</v>
+        <v>-0.648109905623576</v>
       </c>
       <c r="E244" t="n">
-        <v>0.6481099056235756</v>
+        <v>0.648109905623576</v>
       </c>
       <c r="F244" t="n">
-        <v>0.4275919030306602</v>
+        <v>0.4275919030306604</v>
       </c>
     </row>
     <row r="245">
@@ -6783,13 +6783,13 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>0.03473298502174575</v>
+        <v>0.03473298502174572</v>
       </c>
       <c r="E245" t="n">
-        <v>0.03473298502174575</v>
+        <v>0.03473298502174572</v>
       </c>
       <c r="F245" t="n">
-        <v>0.0229151615096738</v>
+        <v>0.02291516150967379</v>
       </c>
     </row>
     <row r="246">
@@ -6809,13 +6809,13 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>-0.2971287808760877</v>
+        <v>-0.2971287808760879</v>
       </c>
       <c r="E246" t="n">
-        <v>0.2971287808760877</v>
+        <v>0.2971287808760879</v>
       </c>
       <c r="F246" t="n">
-        <v>0.1960313517161044</v>
+        <v>0.1960313517161045</v>
       </c>
     </row>
     <row r="247">
@@ -6835,13 +6835,13 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>-0.01927420782052992</v>
+        <v>-0.01927420782052985</v>
       </c>
       <c r="E247" t="n">
-        <v>0.01927420782052992</v>
+        <v>0.01927420782052985</v>
       </c>
       <c r="F247" t="n">
-        <v>0.01271620003008488</v>
+        <v>0.01271620003008483</v>
       </c>
     </row>
     <row r="248">
@@ -6861,10 +6861,10 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>-0.6068467813513776</v>
+        <v>-0.6068467813513777</v>
       </c>
       <c r="E248" t="n">
-        <v>0.6068467813513776</v>
+        <v>0.6068467813513777</v>
       </c>
       <c r="F248" t="n">
         <v>0.4003684681171575</v>
@@ -6887,13 +6887,13 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>-0.6750526378191113</v>
+        <v>-0.6750526378191108</v>
       </c>
       <c r="E249" t="n">
-        <v>0.6750526378191113</v>
+        <v>0.6750526378191108</v>
       </c>
       <c r="F249" t="n">
-        <v>0.4453674284969006</v>
+        <v>0.4453674284969003</v>
       </c>
     </row>
     <row r="250">
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>-0.05672152269405888</v>
+        <v>-0.05672152269405895</v>
       </c>
       <c r="E250" t="n">
-        <v>0.05672152269405888</v>
+        <v>0.05672152269405895</v>
       </c>
       <c r="F250" t="n">
-        <v>0.03742214649259817</v>
+        <v>0.0374221464925982</v>
       </c>
     </row>
     <row r="251">
@@ -6997,7 +6997,7 @@
         <v>0.6287469941713977</v>
       </c>
       <c r="F253" t="n">
-        <v>0.4148171805889705</v>
+        <v>0.4148171805889704</v>
       </c>
     </row>
     <row r="254">
@@ -7017,13 +7017,13 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>0.05632998825695373</v>
+        <v>0.05632998825695371</v>
       </c>
       <c r="E254" t="n">
-        <v>0.05632998825695373</v>
+        <v>0.05632998825695371</v>
       </c>
       <c r="F254" t="n">
-        <v>0.03716383080630611</v>
+        <v>0.0371638308063061</v>
       </c>
     </row>
     <row r="255">
@@ -7095,13 +7095,13 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>-0.04018276324358007</v>
+        <v>-0.0401827632435801</v>
       </c>
       <c r="E257" t="n">
-        <v>0.04018276324358007</v>
+        <v>0.0401827632435801</v>
       </c>
       <c r="F257" t="n">
-        <v>0.02651066440316394</v>
+        <v>0.02651066440316395</v>
       </c>
     </row>
     <row r="258">
@@ -7121,13 +7121,13 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>-0.4201588294544529</v>
+        <v>-0.4201588294544533</v>
       </c>
       <c r="E258" t="n">
-        <v>0.4201588294544529</v>
+        <v>0.4201588294544533</v>
       </c>
       <c r="F258" t="n">
-        <v>0.2772006906586446</v>
+        <v>0.2772006906586448</v>
       </c>
     </row>
     <row r="259">
@@ -7147,10 +7147,10 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>0.2556082340748426</v>
+        <v>0.2556082340748427</v>
       </c>
       <c r="E259" t="n">
-        <v>0.2556082340748426</v>
+        <v>0.2556082340748427</v>
       </c>
       <c r="F259" t="n">
         <v>0.168638081735859</v>
@@ -7199,13 +7199,13 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>-0.01351161612359387</v>
+        <v>-0.01351161612359391</v>
       </c>
       <c r="E261" t="n">
-        <v>0.01351161612359387</v>
+        <v>0.01351161612359391</v>
       </c>
       <c r="F261" t="n">
-        <v>0.00891431777415669</v>
+        <v>0.008914317774156714</v>
       </c>
     </row>
     <row r="262">
@@ -7225,13 +7225,13 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>-0.1662052243159495</v>
+        <v>-0.1662052243159494</v>
       </c>
       <c r="E262" t="n">
-        <v>0.1662052243159495</v>
+        <v>0.1662052243159494</v>
       </c>
       <c r="F262" t="n">
-        <v>0.1096542539193517</v>
+        <v>0.1096542539193516</v>
       </c>
     </row>
     <row r="263">
@@ -7251,13 +7251,13 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>0.3889513860037945</v>
+        <v>0.3889513860037943</v>
       </c>
       <c r="E263" t="n">
-        <v>0.3889513860037945</v>
+        <v>0.3889513860037943</v>
       </c>
       <c r="F263" t="n">
-        <v>0.2566115127769243</v>
+        <v>0.2566115127769241</v>
       </c>
     </row>
     <row r="264">
@@ -7277,13 +7277,13 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>-0.0265527091382971</v>
+        <v>-0.02655270913829695</v>
       </c>
       <c r="E264" t="n">
-        <v>0.0265527091382971</v>
+        <v>0.02655270913829695</v>
       </c>
       <c r="F264" t="n">
-        <v>0.01751820691606331</v>
+        <v>0.01751820691606321</v>
       </c>
     </row>
     <row r="265">
@@ -7329,10 +7329,10 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>0.2105769503360434</v>
+        <v>0.2105769503360435</v>
       </c>
       <c r="E266" t="n">
-        <v>0.2105769503360434</v>
+        <v>0.2105769503360435</v>
       </c>
       <c r="F266" t="n">
         <v>0.138928595516449</v>
@@ -7361,7 +7361,7 @@
         <v>0.6033472643699221</v>
       </c>
       <c r="F267" t="n">
-        <v>0.3980596542681408</v>
+        <v>0.3980596542681407</v>
       </c>
     </row>
     <row r="268">
@@ -7381,13 +7381,13 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>-0.4305478822354779</v>
+        <v>-0.4305478822354777</v>
       </c>
       <c r="E268" t="n">
-        <v>0.4305478822354779</v>
+        <v>0.4305478822354777</v>
       </c>
       <c r="F268" t="n">
-        <v>0.2840548905571176</v>
+        <v>0.2840548905571174</v>
       </c>
     </row>
     <row r="269">
@@ -7407,10 +7407,10 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>-0.295970026144987</v>
+        <v>-0.2959700261449871</v>
       </c>
       <c r="E269" t="n">
-        <v>0.295970026144987</v>
+        <v>0.2959700261449871</v>
       </c>
       <c r="F269" t="n">
         <v>0.1952668607920837</v>
@@ -7459,13 +7459,13 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>-0.1735701668459846</v>
+        <v>-0.1735701668459845</v>
       </c>
       <c r="E271" t="n">
-        <v>0.1735701668459846</v>
+        <v>0.1735701668459845</v>
       </c>
       <c r="F271" t="n">
-        <v>0.114513290580887</v>
+        <v>0.1145132905808869</v>
       </c>
     </row>
     <row r="272">
@@ -7485,13 +7485,13 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>0.1727376103873829</v>
+        <v>0.172737610387383</v>
       </c>
       <c r="E272" t="n">
-        <v>0.1727376103873829</v>
+        <v>0.172737610387383</v>
       </c>
       <c r="F272" t="n">
-        <v>0.1139640096681513</v>
+        <v>0.1139640096681514</v>
       </c>
     </row>
     <row r="273">
@@ -7511,13 +7511,13 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>0.6948675141852831</v>
+        <v>0.6948675141852829</v>
       </c>
       <c r="E273" t="n">
-        <v>0.6948675141852831</v>
+        <v>0.6948675141852829</v>
       </c>
       <c r="F273" t="n">
-        <v>0.4584403357618756</v>
+        <v>0.4584403357618754</v>
       </c>
     </row>
     <row r="274">
@@ -7537,10 +7537,10 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>-0.1569353361802209</v>
+        <v>-0.156935336180221</v>
       </c>
       <c r="E274" t="n">
-        <v>0.1569353361802209</v>
+        <v>0.156935336180221</v>
       </c>
       <c r="F274" t="n">
         <v>0.1035384253007105</v>
@@ -7569,7 +7569,7 @@
         <v>0.6783215979269961</v>
       </c>
       <c r="F275" t="n">
-        <v>0.4475241319531098</v>
+        <v>0.4475241319531097</v>
       </c>
     </row>
     <row r="276">
@@ -7595,7 +7595,7 @@
         <v>0.7927724821450397</v>
       </c>
       <c r="F276" t="n">
-        <v>0.5230333487722068</v>
+        <v>0.5230333487722066</v>
       </c>
     </row>
     <row r="277">
@@ -7615,13 +7615,13 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>0.07527126862799963</v>
+        <v>0.07527126862799974</v>
       </c>
       <c r="E277" t="n">
-        <v>0.07527126862799963</v>
+        <v>0.07527126862799974</v>
       </c>
       <c r="F277" t="n">
-        <v>0.04966038123612906</v>
+        <v>0.04966038123612913</v>
       </c>
     </row>
     <row r="278">
@@ -7641,13 +7641,13 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>0.1249537637231952</v>
+        <v>0.1249537637231955</v>
       </c>
       <c r="E278" t="n">
-        <v>0.1249537637231952</v>
+        <v>0.1249537637231955</v>
       </c>
       <c r="F278" t="n">
-        <v>0.08243851414342737</v>
+        <v>0.08243851414342751</v>
       </c>
     </row>
     <row r="279">
@@ -7673,7 +7673,7 @@
         <v>1.04921845099177</v>
       </c>
       <c r="F279" t="n">
-        <v>0.6922241278241199</v>
+        <v>0.6922241278241198</v>
       </c>
     </row>
     <row r="280">
@@ -7693,13 +7693,13 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>0.919494431960751</v>
+        <v>0.9194944319607509</v>
       </c>
       <c r="E280" t="n">
-        <v>0.919494431960751</v>
+        <v>0.9194944319607509</v>
       </c>
       <c r="F280" t="n">
-        <v>0.6066384274900235</v>
+        <v>0.6066384274900233</v>
       </c>
     </row>
     <row r="281">
@@ -7719,10 +7719,10 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>-0.8400872931227049</v>
+        <v>-0.840087293122705</v>
       </c>
       <c r="E281" t="n">
-        <v>0.8400872931227049</v>
+        <v>0.840087293122705</v>
       </c>
       <c r="F281" t="n">
         <v>0.5542493969947845</v>
@@ -7777,7 +7777,7 @@
         <v>0.3636790362227444</v>
       </c>
       <c r="F283" t="n">
-        <v>0.2399380256983115</v>
+        <v>0.2399380256983114</v>
       </c>
     </row>
     <row r="284">
@@ -7797,13 +7797,13 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>-0.2790540506783331</v>
+        <v>-0.2790540506783332</v>
       </c>
       <c r="E284" t="n">
-        <v>0.2790540506783331</v>
+        <v>0.2790540506783332</v>
       </c>
       <c r="F284" t="n">
-        <v>0.1841065096253365</v>
+        <v>0.1841065096253366</v>
       </c>
     </row>
     <row r="285">
@@ -7829,7 +7829,7 @@
         <v>0.6783062027552585</v>
       </c>
       <c r="F285" t="n">
-        <v>0.4475139749554716</v>
+        <v>0.4475139749554715</v>
       </c>
     </row>
     <row r="286">
@@ -7881,7 +7881,7 @@
         <v>0.03478134404048067</v>
       </c>
       <c r="F287" t="n">
-        <v>0.02294706647620825</v>
+        <v>0.02294706647620824</v>
       </c>
     </row>
     <row r="288">
@@ -7933,7 +7933,7 @@
         <v>0.4402773646636987</v>
       </c>
       <c r="F289" t="n">
-        <v>0.2904739374979039</v>
+        <v>0.2904739374979038</v>
       </c>
     </row>
     <row r="290">
@@ -7953,13 +7953,13 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>-0.9445347014608364</v>
+        <v>-0.9445347014608363</v>
       </c>
       <c r="E290" t="n">
-        <v>0.9445347014608364</v>
+        <v>0.9445347014608363</v>
       </c>
       <c r="F290" t="n">
-        <v>0.6231587991045268</v>
+        <v>0.6231587991045267</v>
       </c>
     </row>
     <row r="291">
@@ -7979,13 +7979,13 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>0.3569540893211799</v>
+        <v>0.3569540893211798</v>
       </c>
       <c r="E291" t="n">
-        <v>0.3569540893211799</v>
+        <v>0.3569540893211798</v>
       </c>
       <c r="F291" t="n">
-        <v>0.2355012275280174</v>
+        <v>0.2355012275280173</v>
       </c>
     </row>
     <row r="292">
@@ -8005,13 +8005,13 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>0.06049376594486176</v>
+        <v>0.06049376594486173</v>
       </c>
       <c r="E292" t="n">
-        <v>0.06049376594486176</v>
+        <v>0.06049376594486173</v>
       </c>
       <c r="F292" t="n">
-        <v>0.03991089208390871</v>
+        <v>0.03991089208390869</v>
       </c>
     </row>
     <row r="293">
@@ -8031,13 +8031,13 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>-0.758763782046549</v>
+        <v>-0.7587637820465488</v>
       </c>
       <c r="E293" t="n">
-        <v>0.758763782046549</v>
+        <v>0.7587637820465488</v>
       </c>
       <c r="F293" t="n">
-        <v>0.500596035797147</v>
+        <v>0.5005960357971467</v>
       </c>
     </row>
     <row r="294">
@@ -8057,10 +8057,10 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>0.5528492351695409</v>
+        <v>0.5528492351695411</v>
       </c>
       <c r="E294" t="n">
-        <v>0.5528492351695409</v>
+        <v>0.5528492351695411</v>
       </c>
       <c r="F294" t="n">
         <v>0.3647434709823543</v>
@@ -8135,10 +8135,10 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>-0.8173585364399651</v>
+        <v>-0.8173585364399653</v>
       </c>
       <c r="E297" t="n">
-        <v>0.8173585364399651</v>
+        <v>0.8173585364399653</v>
       </c>
       <c r="F297" t="n">
         <v>0.5392540509289921</v>
@@ -8167,7 +8167,7 @@
         <v>0.6708164475063023</v>
       </c>
       <c r="F298" t="n">
-        <v>0.4425725928344041</v>
+        <v>0.442572592834404</v>
       </c>
     </row>
     <row r="299">
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>-0.06920538030551884</v>
+        <v>-0.06920538030551886</v>
       </c>
       <c r="E299" t="n">
-        <v>0.06920538030551884</v>
+        <v>0.06920538030551886</v>
       </c>
       <c r="F299" t="n">
         <v>0.04565839837970986</v>
@@ -8219,7 +8219,7 @@
         <v>0.7402247441739621</v>
       </c>
       <c r="F300" t="n">
-        <v>0.488364865720106</v>
+        <v>0.4883648657201059</v>
       </c>
     </row>
     <row r="301">
@@ -8265,13 +8265,13 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>-0.2130734919933954</v>
+        <v>-0.2130734919933953</v>
       </c>
       <c r="E302" t="n">
-        <v>0.2130734919933954</v>
+        <v>0.2130734919933953</v>
       </c>
       <c r="F302" t="n">
-        <v>0.1405756942399831</v>
+        <v>0.140575694239983</v>
       </c>
     </row>
     <row r="303">
@@ -8291,13 +8291,13 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>0.5542097883028113</v>
+        <v>0.5542097883028112</v>
       </c>
       <c r="E303" t="n">
-        <v>0.5542097883028113</v>
+        <v>0.5542097883028112</v>
       </c>
       <c r="F303" t="n">
-        <v>0.3656410988358734</v>
+        <v>0.3656410988358733</v>
       </c>
     </row>
     <row r="304">
@@ -8317,13 +8317,13 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>0.02545232320661904</v>
+        <v>0.02545232320661906</v>
       </c>
       <c r="E304" t="n">
-        <v>0.02545232320661904</v>
+        <v>0.02545232320661906</v>
       </c>
       <c r="F304" t="n">
-        <v>0.01679222493289691</v>
+        <v>0.01679222493289692</v>
       </c>
     </row>
     <row r="305">
@@ -8349,7 +8349,7 @@
         <v>0.3521001358707782</v>
       </c>
       <c r="F305" t="n">
-        <v>0.2322988213079141</v>
+        <v>0.232298821307914</v>
       </c>
     </row>
     <row r="306">
@@ -8369,13 +8369,13 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>0.129080134205099</v>
+        <v>0.1290801342050991</v>
       </c>
       <c r="E306" t="n">
-        <v>0.129080134205099</v>
+        <v>0.1290801342050991</v>
       </c>
       <c r="F306" t="n">
-        <v>0.08516089593648014</v>
+        <v>0.08516089593648023</v>
       </c>
     </row>
     <row r="307">
@@ -8401,7 +8401,7 @@
         <v>0.7247091511131948</v>
       </c>
       <c r="F307" t="n">
-        <v>0.4781284198550801</v>
+        <v>0.47812841985508</v>
       </c>
     </row>
     <row r="308">
@@ -8421,13 +8421,13 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>-0.262846260685011</v>
+        <v>-0.2628462606850108</v>
       </c>
       <c r="E308" t="n">
-        <v>0.262846260685011</v>
+        <v>0.2628462606850108</v>
       </c>
       <c r="F308" t="n">
-        <v>0.1734133853465185</v>
+        <v>0.1734133853465183</v>
       </c>
     </row>
     <row r="309">
@@ -8447,13 +8447,13 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>0.1382104459268301</v>
+        <v>0.13821044592683</v>
       </c>
       <c r="E309" t="n">
-        <v>0.1382104459268301</v>
+        <v>0.13821044592683</v>
       </c>
       <c r="F309" t="n">
-        <v>0.09118463871603526</v>
+        <v>0.09118463871603516</v>
       </c>
     </row>
     <row r="310">
@@ -8473,13 +8473,13 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>-0.009078314708187809</v>
+        <v>-0.009078314708187719</v>
       </c>
       <c r="E310" t="n">
-        <v>0.009078314708187809</v>
+        <v>0.009078314708187719</v>
       </c>
       <c r="F310" t="n">
-        <v>0.005989437638127736</v>
+        <v>0.005989437638127675</v>
       </c>
     </row>
     <row r="311">
@@ -8525,13 +8525,13 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>-0.4825654495332908</v>
+        <v>-0.4825654495332907</v>
       </c>
       <c r="E312" t="n">
-        <v>0.4825654495332908</v>
+        <v>0.4825654495332907</v>
       </c>
       <c r="F312" t="n">
-        <v>0.3183735923681892</v>
+        <v>0.3183735923681891</v>
       </c>
     </row>
     <row r="313">
@@ -8551,13 +8551,13 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>0.3886484653123256</v>
+        <v>0.3886484653123254</v>
       </c>
       <c r="E313" t="n">
-        <v>0.3886484653123256</v>
+        <v>0.3886484653123254</v>
       </c>
       <c r="F313" t="n">
-        <v>0.2564116601997477</v>
+        <v>0.2564116601997476</v>
       </c>
     </row>
     <row r="314">
@@ -8577,13 +8577,13 @@
         </is>
       </c>
       <c r="D314" t="n">
-        <v>0.4046493965693715</v>
+        <v>0.4046493965693714</v>
       </c>
       <c r="E314" t="n">
-        <v>0.4046493965693715</v>
+        <v>0.4046493965693714</v>
       </c>
       <c r="F314" t="n">
-        <v>0.2669683089827657</v>
+        <v>0.2669683089827656</v>
       </c>
     </row>
     <row r="315">
@@ -8603,13 +8603,13 @@
         </is>
       </c>
       <c r="D315" t="n">
-        <v>-0.04244651617108216</v>
+        <v>-0.0424465161710821</v>
       </c>
       <c r="E315" t="n">
-        <v>0.04244651617108216</v>
+        <v>0.0424465161710821</v>
       </c>
       <c r="F315" t="n">
-        <v>0.02800418026191405</v>
+        <v>0.028004180261914</v>
       </c>
     </row>
     <row r="316">
@@ -8629,13 +8629,13 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>-0.05791734675943366</v>
+        <v>-0.05791734675943368</v>
       </c>
       <c r="E316" t="n">
-        <v>0.05791734675943366</v>
+        <v>0.05791734675943368</v>
       </c>
       <c r="F316" t="n">
-        <v>0.0382110939895686</v>
+        <v>0.03821109398956861</v>
       </c>
     </row>
     <row r="317">
@@ -8655,13 +8655,13 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>-0.03389240205415409</v>
+        <v>-0.03389240205415412</v>
       </c>
       <c r="E317" t="n">
-        <v>0.03389240205415409</v>
+        <v>0.03389240205415412</v>
       </c>
       <c r="F317" t="n">
-        <v>0.02236058509038292</v>
+        <v>0.02236058509038293</v>
       </c>
     </row>
     <row r="318">
@@ -8687,7 +8687,7 @@
         <v>0.5220671469701437</v>
       </c>
       <c r="F318" t="n">
-        <v>0.3444349221417468</v>
+        <v>0.3444349221417467</v>
       </c>
     </row>
     <row r="319">
@@ -8707,13 +8707,13 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>0.7280288483391875</v>
+        <v>0.7280288483391872</v>
       </c>
       <c r="E319" t="n">
-        <v>0.7280288483391875</v>
+        <v>0.7280288483391872</v>
       </c>
       <c r="F319" t="n">
-        <v>0.4803185972339956</v>
+        <v>0.4803185972339953</v>
       </c>
     </row>
     <row r="320">
@@ -8739,7 +8739,7 @@
         <v>0.9055931294549977</v>
       </c>
       <c r="F320" t="n">
-        <v>0.5974670132877967</v>
+        <v>0.5974670132877966</v>
       </c>
     </row>
     <row r="321">
@@ -8765,7 +8765,7 @@
         <v>0.06779185523031694</v>
       </c>
       <c r="F321" t="n">
-        <v>0.04472582217366406</v>
+        <v>0.04472582217366405</v>
       </c>
     </row>
     <row r="322">
@@ -8817,7 +8817,7 @@
         <v>0.2965973248175783</v>
       </c>
       <c r="F323" t="n">
-        <v>0.1956807224393978</v>
+        <v>0.1956807224393977</v>
       </c>
     </row>
     <row r="324">
@@ -8837,13 +8837,13 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>-0.02080725521193732</v>
+        <v>-0.02080725521193721</v>
       </c>
       <c r="E324" t="n">
-        <v>0.02080725521193732</v>
+        <v>0.02080725521193721</v>
       </c>
       <c r="F324" t="n">
-        <v>0.01372763134110207</v>
+        <v>0.013727631341102</v>
       </c>
     </row>
     <row r="325">
@@ -8889,10 +8889,10 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>0.3028318879010506</v>
+        <v>0.3028318879010508</v>
       </c>
       <c r="E326" t="n">
-        <v>0.3028318879010506</v>
+        <v>0.3028318879010508</v>
       </c>
       <c r="F326" t="n">
         <v>0.1997939888318651</v>
@@ -8915,10 +8915,10 @@
         </is>
       </c>
       <c r="D327" t="n">
-        <v>-0.3647476650875067</v>
+        <v>-0.3647476650875068</v>
       </c>
       <c r="E327" t="n">
-        <v>0.3647476650875067</v>
+        <v>0.3647476650875068</v>
       </c>
       <c r="F327" t="n">
         <v>0.2406430558883339</v>
@@ -8941,13 +8941,13 @@
         </is>
       </c>
       <c r="D328" t="n">
-        <v>0.05925701661677236</v>
+        <v>0.05925701661677226</v>
       </c>
       <c r="E328" t="n">
-        <v>0.05925701661677236</v>
+        <v>0.05925701661677226</v>
       </c>
       <c r="F328" t="n">
-        <v>0.03909494405691345</v>
+        <v>0.03909494405691338</v>
       </c>
     </row>
     <row r="329">
@@ -8967,13 +8967,13 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>0.5525774852001095</v>
+        <v>0.5525774852001094</v>
       </c>
       <c r="E329" t="n">
-        <v>0.5525774852001095</v>
+        <v>0.5525774852001094</v>
       </c>
       <c r="F329" t="n">
-        <v>0.3645641833560281</v>
+        <v>0.364564183356028</v>
       </c>
     </row>
     <row r="330">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="D330" t="n">
-        <v>-0.5669260583928327</v>
+        <v>-0.5669260583928329</v>
       </c>
       <c r="E330" t="n">
-        <v>0.5669260583928327</v>
+        <v>0.5669260583928329</v>
       </c>
       <c r="F330" t="n">
-        <v>0.3740306853551731</v>
+        <v>0.3740306853551732</v>
       </c>
     </row>
     <row r="331">
@@ -9077,7 +9077,7 @@
         <v>1.025888495582351</v>
       </c>
       <c r="F333" t="n">
-        <v>0.6768321396064184</v>
+        <v>0.6768321396064182</v>
       </c>
     </row>
     <row r="334">
@@ -9103,7 +9103,7 @@
         <v>0.5558962603899275</v>
       </c>
       <c r="F334" t="n">
-        <v>0.3667537524195959</v>
+        <v>0.3667537524195958</v>
       </c>
     </row>
     <row r="335">
@@ -9129,7 +9129,7 @@
         <v>0.4547816110700643</v>
       </c>
       <c r="F335" t="n">
-        <v>0.3000431452342929</v>
+        <v>0.3000431452342928</v>
       </c>
     </row>
     <row r="336">
@@ -9149,13 +9149,13 @@
         </is>
       </c>
       <c r="D336" t="n">
-        <v>-0.05543699835018494</v>
+        <v>-0.05543699835018503</v>
       </c>
       <c r="E336" t="n">
-        <v>0.05543699835018494</v>
+        <v>0.05543699835018503</v>
       </c>
       <c r="F336" t="n">
-        <v>0.03657467879627001</v>
+        <v>0.03657467879627006</v>
       </c>
     </row>
     <row r="337">
@@ -9175,13 +9175,13 @@
         </is>
       </c>
       <c r="D337" t="n">
-        <v>0.4269660212548876</v>
+        <v>0.4269660212548875</v>
       </c>
       <c r="E337" t="n">
-        <v>0.4269660212548876</v>
+        <v>0.4269660212548875</v>
       </c>
       <c r="F337" t="n">
-        <v>0.2816917500777135</v>
+        <v>0.2816917500777134</v>
       </c>
     </row>
     <row r="338">
@@ -9201,13 +9201,13 @@
         </is>
       </c>
       <c r="D338" t="n">
-        <v>-0.8198817943707832</v>
+        <v>-0.8198817943707831</v>
       </c>
       <c r="E338" t="n">
-        <v>0.8198817943707832</v>
+        <v>0.8198817943707831</v>
       </c>
       <c r="F338" t="n">
-        <v>0.5409187757713592</v>
+        <v>0.5409187757713591</v>
       </c>
     </row>
     <row r="339">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>-0.3404707718898469</v>
+        <v>-0.340470771889847</v>
       </c>
       <c r="E339" t="n">
-        <v>0.3404707718898469</v>
+        <v>0.340470771889847</v>
       </c>
       <c r="F339" t="n">
-        <v>0.2246263234298601</v>
+        <v>0.2246263234298602</v>
       </c>
     </row>
     <row r="340">
@@ -9253,10 +9253,10 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>0.6856754240501364</v>
+        <v>0.6856754240501365</v>
       </c>
       <c r="E340" t="n">
-        <v>0.6856754240501364</v>
+        <v>0.6856754240501365</v>
       </c>
       <c r="F340" t="n">
         <v>0.452375834541307</v>
@@ -9279,13 +9279,13 @@
         </is>
       </c>
       <c r="D341" t="n">
-        <v>-0.4081382268446362</v>
+        <v>-0.4081382268446361</v>
       </c>
       <c r="E341" t="n">
-        <v>0.4081382268446362</v>
+        <v>0.4081382268446361</v>
       </c>
       <c r="F341" t="n">
-        <v>0.2692700722544074</v>
+        <v>0.2692700722544072</v>
       </c>
     </row>
     <row r="342">
@@ -9331,13 +9331,13 @@
         </is>
       </c>
       <c r="D343" t="n">
-        <v>0.6410075311730765</v>
+        <v>0.6410075311730764</v>
       </c>
       <c r="E343" t="n">
-        <v>0.6410075311730765</v>
+        <v>0.6410075311730764</v>
       </c>
       <c r="F343" t="n">
-        <v>0.4229060962238606</v>
+        <v>0.4229060962238604</v>
       </c>
     </row>
     <row r="344">
@@ -9357,13 +9357,13 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>-0.8509085555777486</v>
+        <v>-0.8509085555777485</v>
       </c>
       <c r="E344" t="n">
-        <v>0.8509085555777486</v>
+        <v>0.8509085555777485</v>
       </c>
       <c r="F344" t="n">
-        <v>0.5613887481545148</v>
+        <v>0.5613887481545147</v>
       </c>
     </row>
     <row r="345">
@@ -9415,7 +9415,7 @@
         <v>0.5201995361550551</v>
       </c>
       <c r="F346" t="n">
-        <v>0.3432027618929754</v>
+        <v>0.3432027618929753</v>
       </c>
     </row>
     <row r="347">
@@ -9435,13 +9435,13 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>0.8733135007935883</v>
+        <v>0.8733135007935882</v>
       </c>
       <c r="E347" t="n">
-        <v>0.8733135007935883</v>
+        <v>0.8733135007935882</v>
       </c>
       <c r="F347" t="n">
-        <v>0.5761704589091453</v>
+        <v>0.5761704589091451</v>
       </c>
     </row>
     <row r="348">
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>-0.400557185258987</v>
+        <v>-0.4005571852589871</v>
       </c>
       <c r="E348" t="n">
-        <v>0.400557185258987</v>
+        <v>0.4005571852589871</v>
       </c>
       <c r="F348" t="n">
         <v>0.2642684637765312</v>
@@ -9487,10 +9487,10 @@
         </is>
       </c>
       <c r="D349" t="n">
-        <v>0.2240289646621466</v>
+        <v>0.2240289646621467</v>
       </c>
       <c r="E349" t="n">
-        <v>0.2240289646621466</v>
+        <v>0.2240289646621467</v>
       </c>
       <c r="F349" t="n">
         <v>0.1478035908766263</v>
@@ -9539,13 +9539,13 @@
         </is>
       </c>
       <c r="D351" t="n">
-        <v>0.3116358400462007</v>
+        <v>0.3116358400462009</v>
       </c>
       <c r="E351" t="n">
-        <v>0.3116358400462007</v>
+        <v>0.3116358400462009</v>
       </c>
       <c r="F351" t="n">
-        <v>0.2056024151794204</v>
+        <v>0.2056024151794206</v>
       </c>
     </row>
     <row r="352">
@@ -9565,13 +9565,13 @@
         </is>
       </c>
       <c r="D352" t="n">
-        <v>-0.06633437191090533</v>
+        <v>-0.0663343719109053</v>
       </c>
       <c r="E352" t="n">
-        <v>0.06633437191090533</v>
+        <v>0.0663343719109053</v>
       </c>
       <c r="F352" t="n">
-        <v>0.04376424442153413</v>
+        <v>0.04376424442153411</v>
       </c>
     </row>
     <row r="353">
@@ -9591,13 +9591,13 @@
         </is>
       </c>
       <c r="D353" t="n">
-        <v>-0.7489897991437025</v>
+        <v>-0.7489897991437022</v>
       </c>
       <c r="E353" t="n">
-        <v>0.7489897991437025</v>
+        <v>0.7489897991437022</v>
       </c>
       <c r="F353" t="n">
-        <v>0.4941476295725943</v>
+        <v>0.4941476295725941</v>
       </c>
     </row>
     <row r="354">
@@ -9623,7 +9623,7 @@
         <v>0.4984453436306112</v>
       </c>
       <c r="F354" t="n">
-        <v>0.3288503866249681</v>
+        <v>0.328850386624968</v>
       </c>
     </row>
     <row r="355">
@@ -9643,13 +9643,13 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>0.08366186973260162</v>
+        <v>0.08366186973260149</v>
       </c>
       <c r="E355" t="n">
-        <v>0.08366186973260162</v>
+        <v>0.08366186973260149</v>
       </c>
       <c r="F355" t="n">
-        <v>0.05519609834638677</v>
+        <v>0.05519609834638667</v>
       </c>
     </row>
     <row r="356">
@@ -9669,13 +9669,13 @@
         </is>
       </c>
       <c r="D356" t="n">
-        <v>0.0675567546328804</v>
+        <v>0.06755675463288049</v>
       </c>
       <c r="E356" t="n">
-        <v>0.0675567546328804</v>
+        <v>0.06755675463288049</v>
       </c>
       <c r="F356" t="n">
-        <v>0.04457071404927146</v>
+        <v>0.04457071404927151</v>
       </c>
     </row>
     <row r="357">
@@ -9701,7 +9701,7 @@
         <v>0.674213716435348</v>
       </c>
       <c r="F357" t="n">
-        <v>0.4448139483111113</v>
+        <v>0.4448139483111112</v>
       </c>
     </row>
     <row r="358">
@@ -9721,13 +9721,13 @@
         </is>
       </c>
       <c r="D358" t="n">
-        <v>0.9106854781005789</v>
+        <v>0.9106854781005793</v>
       </c>
       <c r="E358" t="n">
-        <v>0.9106854781005789</v>
+        <v>0.9106854781005793</v>
       </c>
       <c r="F358" t="n">
-        <v>0.6008267012502336</v>
+        <v>0.6008267012502339</v>
       </c>
     </row>
     <row r="359">
@@ -9753,7 +9753,7 @@
         <v>0.7458783541380288</v>
       </c>
       <c r="F359" t="n">
-        <v>0.4920948470435706</v>
+        <v>0.4920948470435705</v>
       </c>
     </row>
     <row r="360">
@@ -9773,10 +9773,10 @@
         </is>
       </c>
       <c r="D360" t="n">
-        <v>-0.4968750054625378</v>
+        <v>-0.4968750054625379</v>
       </c>
       <c r="E360" t="n">
-        <v>0.4968750054625378</v>
+        <v>0.4968750054625379</v>
       </c>
       <c r="F360" t="n">
         <v>0.3278143526439072</v>
@@ -9799,13 +9799,13 @@
         </is>
       </c>
       <c r="D361" t="n">
-        <v>0.1677345596559755</v>
+        <v>0.1677345596559753</v>
       </c>
       <c r="E361" t="n">
-        <v>0.1677345596559755</v>
+        <v>0.1677345596559753</v>
       </c>
       <c r="F361" t="n">
-        <v>0.1106632361964927</v>
+        <v>0.1106632361964926</v>
       </c>
     </row>
     <row r="362">
@@ -9877,13 +9877,13 @@
         </is>
       </c>
       <c r="D364" t="n">
-        <v>0.3687113823677002</v>
+        <v>0.3687113823677003</v>
       </c>
       <c r="E364" t="n">
-        <v>0.3687113823677002</v>
+        <v>0.3687113823677003</v>
       </c>
       <c r="F364" t="n">
-        <v>0.2432581268820147</v>
+        <v>0.2432581268820148</v>
       </c>
     </row>
     <row r="365">
@@ -9903,13 +9903,13 @@
         </is>
       </c>
       <c r="D365" t="n">
-        <v>-0.4359928034581434</v>
+        <v>-0.4359928034581432</v>
       </c>
       <c r="E365" t="n">
-        <v>0.4359928034581434</v>
+        <v>0.4359928034581432</v>
       </c>
       <c r="F365" t="n">
-        <v>0.2876471890349683</v>
+        <v>0.2876471890349682</v>
       </c>
     </row>
     <row r="366">
@@ -9929,10 +9929,10 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>0.6277239135088098</v>
+        <v>0.62772391350881</v>
       </c>
       <c r="E366" t="n">
-        <v>0.6277239135088098</v>
+        <v>0.62772391350881</v>
       </c>
       <c r="F366" t="n">
         <v>0.4141422009232162</v>
@@ -9955,13 +9955,13 @@
         </is>
       </c>
       <c r="D367" t="n">
-        <v>-0.09436591551484874</v>
+        <v>-0.09436591551484877</v>
       </c>
       <c r="E367" t="n">
-        <v>0.09436591551484874</v>
+        <v>0.09436591551484877</v>
       </c>
       <c r="F367" t="n">
-        <v>0.06225811555433956</v>
+        <v>0.06225811555433958</v>
       </c>
     </row>
     <row r="368">
@@ -9987,7 +9987,7 @@
         <v>0.6283814711032356</v>
       </c>
       <c r="F368" t="n">
-        <v>0.4145760259592374</v>
+        <v>0.4145760259592373</v>
       </c>
     </row>
     <row r="369">
@@ -10013,7 +10013,7 @@
         <v>0.8760925574103519</v>
       </c>
       <c r="F369" t="n">
-        <v>0.5780039474842792</v>
+        <v>0.578003947484279</v>
       </c>
     </row>
     <row r="370">
@@ -10039,7 +10039,7 @@
         <v>0.4486046067141558</v>
       </c>
       <c r="F370" t="n">
-        <v>0.2959678533360302</v>
+        <v>0.2959678533360301</v>
       </c>
     </row>
     <row r="371">
@@ -10059,13 +10059,13 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>-0.02838093508102363</v>
+        <v>-0.02838093508102383</v>
       </c>
       <c r="E371" t="n">
-        <v>0.02838093508102363</v>
+        <v>0.02838093508102383</v>
       </c>
       <c r="F371" t="n">
-        <v>0.01872438291065533</v>
+        <v>0.01872438291065546</v>
       </c>
     </row>
     <row r="372">
@@ -10117,7 +10117,7 @@
         <v>0.08066789159438224</v>
       </c>
       <c r="F373" t="n">
-        <v>0.0532208148356037</v>
+        <v>0.05322081483560368</v>
       </c>
     </row>
     <row r="374">
@@ -10137,13 +10137,13 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>-0.392918880246918</v>
+        <v>-0.3929188802469179</v>
       </c>
       <c r="E374" t="n">
-        <v>0.392918880246918</v>
+        <v>0.3929188802469179</v>
       </c>
       <c r="F374" t="n">
-        <v>0.259229075630015</v>
+        <v>0.2592290756300149</v>
       </c>
     </row>
     <row r="375">
@@ -10163,10 +10163,10 @@
         </is>
       </c>
       <c r="D375" t="n">
-        <v>-0.7317906271705968</v>
+        <v>-0.731790627170597</v>
       </c>
       <c r="E375" t="n">
-        <v>0.7317906271705968</v>
+        <v>0.731790627170597</v>
       </c>
       <c r="F375" t="n">
         <v>0.482800438902123</v>
@@ -10195,7 +10195,7 @@
         <v>0.3590496919574185</v>
       </c>
       <c r="F376" t="n">
-        <v>0.2368838058707496</v>
+        <v>0.2368838058707495</v>
       </c>
     </row>
     <row r="377">
@@ -10241,13 +10241,13 @@
         </is>
       </c>
       <c r="D378" t="n">
-        <v>-0.09641165775068541</v>
+        <v>-0.09641165775068557</v>
       </c>
       <c r="E378" t="n">
-        <v>0.09641165775068541</v>
+        <v>0.09641165775068557</v>
       </c>
       <c r="F378" t="n">
-        <v>0.06360779839075598</v>
+        <v>0.06360779839075606</v>
       </c>
     </row>
     <row r="379">
@@ -10267,13 +10267,13 @@
         </is>
       </c>
       <c r="D379" t="n">
-        <v>0.1389739666384265</v>
+        <v>0.1389739666384264</v>
       </c>
       <c r="E379" t="n">
-        <v>0.1389739666384265</v>
+        <v>0.1389739666384264</v>
       </c>
       <c r="F379" t="n">
-        <v>0.09168837314632561</v>
+        <v>0.09168837314632554</v>
       </c>
     </row>
     <row r="380">
@@ -10319,10 +10319,10 @@
         </is>
       </c>
       <c r="D381" t="n">
-        <v>0.1757423327222918</v>
+        <v>0.1757423327222917</v>
       </c>
       <c r="E381" t="n">
-        <v>0.1757423327222918</v>
+        <v>0.1757423327222917</v>
       </c>
       <c r="F381" t="n">
         <v>0.1159463816857896</v>
@@ -10345,10 +10345,10 @@
         </is>
       </c>
       <c r="D382" t="n">
-        <v>-0.3768192114640507</v>
+        <v>-0.3768192114640509</v>
       </c>
       <c r="E382" t="n">
-        <v>0.3768192114640507</v>
+        <v>0.3768192114640509</v>
       </c>
       <c r="F382" t="n">
         <v>0.2486072845521483</v>
@@ -10371,10 +10371,10 @@
         </is>
       </c>
       <c r="D383" t="n">
-        <v>0.1657673544880665</v>
+        <v>0.1657673544880664</v>
       </c>
       <c r="E383" t="n">
-        <v>0.1657673544880665</v>
+        <v>0.1657673544880664</v>
       </c>
       <c r="F383" t="n">
         <v>0.1093653683594186</v>
@@ -10397,13 +10397,13 @@
         </is>
       </c>
       <c r="D384" t="n">
-        <v>0.1475834424198135</v>
+        <v>0.1475834424198134</v>
       </c>
       <c r="E384" t="n">
-        <v>0.1475834424198135</v>
+        <v>0.1475834424198134</v>
       </c>
       <c r="F384" t="n">
-        <v>0.09736849329495635</v>
+        <v>0.09736849329495631</v>
       </c>
     </row>
     <row r="385">
@@ -10423,13 +10423,13 @@
         </is>
       </c>
       <c r="D385" t="n">
-        <v>-0.5377548191126126</v>
+        <v>-0.5377548191126125</v>
       </c>
       <c r="E385" t="n">
-        <v>0.5377548191126126</v>
+        <v>0.5377548191126125</v>
       </c>
       <c r="F385" t="n">
-        <v>0.3547848975507252</v>
+        <v>0.3547848975507251</v>
       </c>
     </row>
     <row r="386">
@@ -10475,13 +10475,13 @@
         </is>
       </c>
       <c r="D387" t="n">
-        <v>0.03308343132924952</v>
+        <v>0.03308343132924955</v>
       </c>
       <c r="E387" t="n">
-        <v>0.03308343132924952</v>
+        <v>0.03308343132924955</v>
       </c>
       <c r="F387" t="n">
-        <v>0.0218268649161399</v>
+        <v>0.02182686491613992</v>
       </c>
     </row>
     <row r="388">
@@ -10501,13 +10501,13 @@
         </is>
       </c>
       <c r="D388" t="n">
-        <v>0.2853778172201072</v>
+        <v>0.2853778172201071</v>
       </c>
       <c r="E388" t="n">
-        <v>0.2853778172201072</v>
+        <v>0.2853778172201071</v>
       </c>
       <c r="F388" t="n">
-        <v>0.1882786281911177</v>
+        <v>0.1882786281911176</v>
       </c>
     </row>
     <row r="389">
@@ -10527,10 +10527,10 @@
         </is>
       </c>
       <c r="D389" t="n">
-        <v>0.6081514436725415</v>
+        <v>0.6081514436725416</v>
       </c>
       <c r="E389" t="n">
-        <v>0.6081514436725415</v>
+        <v>0.6081514436725416</v>
       </c>
       <c r="F389" t="n">
         <v>0.4012292218872794</v>
@@ -10559,7 +10559,7 @@
         <v>0.7207833387812445</v>
       </c>
       <c r="F390" t="n">
-        <v>0.4755383567324608</v>
+        <v>0.4755383567324607</v>
       </c>
     </row>
     <row r="391">
@@ -10585,7 +10585,7 @@
         <v>0.7046154400860372</v>
       </c>
       <c r="F391" t="n">
-        <v>0.4648715508233009</v>
+        <v>0.4648715508233008</v>
       </c>
     </row>
     <row r="392">
@@ -10611,7 +10611,7 @@
         <v>0.4442243582876745</v>
       </c>
       <c r="F392" t="n">
-        <v>0.2930779750234558</v>
+        <v>0.2930779750234557</v>
       </c>
     </row>
     <row r="393">
@@ -10631,13 +10631,13 @@
         </is>
       </c>
       <c r="D393" t="n">
-        <v>-1.185064531678152</v>
+        <v>-1.185064531678151</v>
       </c>
       <c r="E393" t="n">
-        <v>1.185064531678152</v>
+        <v>1.185064531678151</v>
       </c>
       <c r="F393" t="n">
-        <v>0.7818488714917219</v>
+        <v>0.7818488714917214</v>
       </c>
     </row>
     <row r="394">
@@ -10663,7 +10663,7 @@
         <v>1.122791611843444</v>
       </c>
       <c r="F394" t="n">
-        <v>0.7407641788055654</v>
+        <v>0.7407641788055653</v>
       </c>
     </row>
     <row r="395">
@@ -10709,10 +10709,10 @@
         </is>
       </c>
       <c r="D396" t="n">
-        <v>0.5021269891812098</v>
+        <v>0.5021269891812099</v>
       </c>
       <c r="E396" t="n">
-        <v>0.5021269891812098</v>
+        <v>0.5021269891812099</v>
       </c>
       <c r="F396" t="n">
         <v>0.3312793601888734</v>
@@ -10735,13 +10735,13 @@
         </is>
       </c>
       <c r="D397" t="n">
-        <v>-0.8555266877073314</v>
+        <v>-0.8555266877073319</v>
       </c>
       <c r="E397" t="n">
-        <v>0.8555266877073314</v>
+        <v>0.8555266877073319</v>
       </c>
       <c r="F397" t="n">
-        <v>0.5644355707514251</v>
+        <v>0.5644355707514254</v>
       </c>
     </row>
     <row r="398">
@@ -10761,10 +10761,10 @@
         </is>
       </c>
       <c r="D398" t="n">
-        <v>0.595628407470345</v>
+        <v>0.5956284074703451</v>
       </c>
       <c r="E398" t="n">
-        <v>0.595628407470345</v>
+        <v>0.5956284074703451</v>
       </c>
       <c r="F398" t="n">
         <v>0.3929671218407341</v>
@@ -10793,7 +10793,7 @@
         <v>0.8239792416519895</v>
       </c>
       <c r="F399" t="n">
-        <v>0.5436220754205955</v>
+        <v>0.5436220754205954</v>
       </c>
     </row>
     <row r="400">
@@ -10819,7 +10819,7 @@
         <v>0.2004715850873052</v>
       </c>
       <c r="F400" t="n">
-        <v>0.1322615590770498</v>
+        <v>0.1322615590770499</v>
       </c>
     </row>
     <row r="401">
@@ -10839,13 +10839,13 @@
         </is>
       </c>
       <c r="D401" t="n">
-        <v>0.273959292902342</v>
+        <v>0.2739592929023418</v>
       </c>
       <c r="E401" t="n">
-        <v>0.273959292902342</v>
+        <v>0.2739592929023418</v>
       </c>
       <c r="F401" t="n">
-        <v>0.1807452322339344</v>
+        <v>0.1807452322339342</v>
       </c>
     </row>
     <row r="402">
@@ -10865,13 +10865,13 @@
         </is>
       </c>
       <c r="D402" t="n">
-        <v>0.2996442891363076</v>
+        <v>0.2996442891363075</v>
       </c>
       <c r="E402" t="n">
-        <v>0.2996442891363076</v>
+        <v>0.2996442891363075</v>
       </c>
       <c r="F402" t="n">
-        <v>0.1976909636966401</v>
+        <v>0.19769096369664</v>
       </c>
     </row>
     <row r="403">
@@ -10891,13 +10891,13 @@
         </is>
       </c>
       <c r="D403" t="n">
-        <v>0.0377007414959445</v>
+        <v>0.03770074149594446</v>
       </c>
       <c r="E403" t="n">
-        <v>0.0377007414959445</v>
+        <v>0.03770074149594446</v>
       </c>
       <c r="F403" t="n">
-        <v>0.02487314522126861</v>
+        <v>0.02487314522126858</v>
       </c>
     </row>
     <row r="404">
@@ -10917,13 +10917,13 @@
         </is>
       </c>
       <c r="D404" t="n">
-        <v>-0.07000679658455136</v>
+        <v>-0.07000679658455129</v>
       </c>
       <c r="E404" t="n">
-        <v>0.07000679658455136</v>
+        <v>0.07000679658455129</v>
       </c>
       <c r="F404" t="n">
-        <v>0.0461871344920542</v>
+        <v>0.04618713449205415</v>
       </c>
     </row>
     <row r="405">
@@ -10943,13 +10943,13 @@
         </is>
       </c>
       <c r="D405" t="n">
-        <v>-0.121754747879525</v>
+        <v>-0.1217547478795251</v>
       </c>
       <c r="E405" t="n">
-        <v>0.121754747879525</v>
+        <v>0.1217547478795251</v>
       </c>
       <c r="F405" t="n">
-        <v>0.08032795656584479</v>
+        <v>0.08032795656584481</v>
       </c>
     </row>
     <row r="406">
@@ -10969,13 +10969,13 @@
         </is>
       </c>
       <c r="D406" t="n">
-        <v>0.04534502800860516</v>
+        <v>0.04534502800860517</v>
       </c>
       <c r="E406" t="n">
-        <v>0.04534502800860516</v>
+        <v>0.04534502800860517</v>
       </c>
       <c r="F406" t="n">
-        <v>0.02991647967565452</v>
+        <v>0.02991647967565453</v>
       </c>
     </row>
     <row r="407">
@@ -10995,13 +10995,13 @@
         </is>
       </c>
       <c r="D407" t="n">
-        <v>0.03615685052651094</v>
+        <v>0.03615685052651104</v>
       </c>
       <c r="E407" t="n">
-        <v>0.03615685052651094</v>
+        <v>0.03615685052651104</v>
       </c>
       <c r="F407" t="n">
-        <v>0.02385455983634569</v>
+        <v>0.02385455983634575</v>
       </c>
     </row>
     <row r="408">
@@ -11027,7 +11027,7 @@
         <v>0.1360495013009898</v>
       </c>
       <c r="F408" t="n">
-        <v>0.08975895085524269</v>
+        <v>0.08975895085524266</v>
       </c>
     </row>
     <row r="409">
@@ -11047,13 +11047,13 @@
         </is>
       </c>
       <c r="D409" t="n">
-        <v>0.01331556895149659</v>
+        <v>0.01331556895149652</v>
       </c>
       <c r="E409" t="n">
-        <v>0.01331556895149659</v>
+        <v>0.01331556895149652</v>
       </c>
       <c r="F409" t="n">
-        <v>0.008784975231057923</v>
+        <v>0.008784975231057876</v>
       </c>
     </row>
     <row r="410">
@@ -11073,13 +11073,13 @@
         </is>
       </c>
       <c r="D410" t="n">
-        <v>-0.08529699245071581</v>
+        <v>-0.08529699245071584</v>
       </c>
       <c r="E410" t="n">
-        <v>0.08529699245071581</v>
+        <v>0.08529699245071584</v>
       </c>
       <c r="F410" t="n">
-        <v>0.05627487407355978</v>
+        <v>0.05627487407355979</v>
       </c>
     </row>
     <row r="411">
@@ -11099,13 +11099,13 @@
         </is>
       </c>
       <c r="D411" t="n">
-        <v>-0.07010989165539956</v>
+        <v>-0.07010989165539959</v>
       </c>
       <c r="E411" t="n">
-        <v>0.07010989165539956</v>
+        <v>0.07010989165539959</v>
       </c>
       <c r="F411" t="n">
-        <v>0.04625515168659877</v>
+        <v>0.04625515168659878</v>
       </c>
     </row>
     <row r="412">
@@ -11121,14 +11121,14 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Clase ['Quiebre', 'Normal', 'Exceso'][0]</t>
+          <t>Clase 0</t>
         </is>
       </c>
       <c r="D412" t="n">
-        <v>0.5821548882060107</v>
+        <v>0.5821548882060108</v>
       </c>
       <c r="E412" t="n">
-        <v>0.5821548882060107</v>
+        <v>0.5821548882060108</v>
       </c>
       <c r="F412" t="n">
         <v>0.3840779385513445</v>
@@ -11147,7 +11147,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Clase ['Quiebre', 'Normal', 'Exceso'][1]</t>
+          <t>Clase 1</t>
         </is>
       </c>
       <c r="D413" t="n">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Clase ['Quiebre', 'Normal', 'Exceso'][2]</t>
+          <t>Clase 2</t>
         </is>
       </c>
       <c r="D414" t="n">
@@ -11183,7 +11183,7 @@
         <v>0.2582792660729253</v>
       </c>
       <c r="F414" t="n">
-        <v>0.170400300836672</v>
+        <v>0.1704003008366719</v>
       </c>
     </row>
     <row r="415">
@@ -11199,7 +11199,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Clase ['Quiebre', 'Normal', 'Exceso'][0]</t>
+          <t>Clase 0</t>
         </is>
       </c>
       <c r="D415" t="n">
@@ -11209,7 +11209,7 @@
         <v>1.196122946287917</v>
       </c>
       <c r="F415" t="n">
-        <v>0.7891446842951727</v>
+        <v>0.7891446842951724</v>
       </c>
     </row>
     <row r="416">
@@ -11225,7 +11225,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Clase ['Quiebre', 'Normal', 'Exceso'][1]</t>
+          <t>Clase 1</t>
         </is>
       </c>
       <c r="D416" t="n">
@@ -11235,7 +11235,7 @@
         <v>1.107341259801132</v>
       </c>
       <c r="F416" t="n">
-        <v>0.7305707758426691</v>
+        <v>0.7305707758426692</v>
       </c>
     </row>
     <row r="417">
@@ -11251,17 +11251,17 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Clase ['Quiebre', 'Normal', 'Exceso'][2]</t>
+          <t>Clase 2</t>
         </is>
       </c>
       <c r="D417" t="n">
-        <v>-2.317014863284313</v>
+        <v>-2.317014863284311</v>
       </c>
       <c r="E417" t="n">
-        <v>2.317014863284313</v>
+        <v>2.317014863284311</v>
       </c>
       <c r="F417" t="n">
-        <v>1.528655535342933</v>
+        <v>1.528655535342931</v>
       </c>
     </row>
     <row r="418">
@@ -11277,17 +11277,17 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Clase ['Quiebre', 'Normal', 'Exceso'][0]</t>
+          <t>Clase 0</t>
         </is>
       </c>
       <c r="D418" t="n">
-        <v>-1.007523780057481</v>
+        <v>-1.007523780057482</v>
       </c>
       <c r="E418" t="n">
-        <v>1.007523780057481</v>
+        <v>1.007523780057482</v>
       </c>
       <c r="F418" t="n">
-        <v>0.6647159790729043</v>
+        <v>0.6647159790729046</v>
       </c>
     </row>
     <row r="419">
@@ -11303,17 +11303,17 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Clase ['Quiebre', 'Normal', 'Exceso'][1]</t>
+          <t>Clase 1</t>
         </is>
       </c>
       <c r="D419" t="n">
-        <v>-0.862268262821469</v>
+        <v>-0.8622682628214687</v>
       </c>
       <c r="E419" t="n">
-        <v>0.862268262821469</v>
+        <v>0.8622682628214687</v>
       </c>
       <c r="F419" t="n">
-        <v>0.5688833394206985</v>
+        <v>0.5688833394206982</v>
       </c>
     </row>
     <row r="420">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Clase ['Quiebre', 'Normal', 'Exceso'][2]</t>
+          <t>Clase 2</t>
         </is>
       </c>
       <c r="D420" t="n">
@@ -11355,17 +11355,17 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Clase ['Quiebre', 'Normal', 'Exceso'][0]</t>
+          <t>Clase 0</t>
         </is>
       </c>
       <c r="D421" t="n">
-        <v>0.9249256349493459</v>
+        <v>0.9249256349493455</v>
       </c>
       <c r="E421" t="n">
-        <v>0.9249256349493459</v>
+        <v>0.9249256349493455</v>
       </c>
       <c r="F421" t="n">
-        <v>0.6102216753334656</v>
+        <v>0.6102216753334653</v>
       </c>
     </row>
     <row r="422">
@@ -11381,14 +11381,14 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Clase ['Quiebre', 'Normal', 'Exceso'][1]</t>
+          <t>Clase 1</t>
         </is>
       </c>
       <c r="D422" t="n">
-        <v>-0.8614997759163564</v>
+        <v>-0.8614997759163566</v>
       </c>
       <c r="E422" t="n">
-        <v>0.8614997759163564</v>
+        <v>0.8614997759163566</v>
       </c>
       <c r="F422" t="n">
         <v>0.5683763285335635</v>
@@ -11407,17 +11407,17 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Clase ['Quiebre', 'Normal', 'Exceso'][2]</t>
+          <t>Clase 2</t>
         </is>
       </c>
       <c r="D423" t="n">
-        <v>-0.5773062122693721</v>
+        <v>-0.5773062122693723</v>
       </c>
       <c r="E423" t="n">
-        <v>0.5773062122693721</v>
+        <v>0.5773062122693723</v>
       </c>
       <c r="F423" t="n">
-        <v>0.3808790141822878</v>
+        <v>0.3808790141822879</v>
       </c>
     </row>
     <row r="424">
@@ -11433,17 +11433,17 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Clase ['Quiebre', 'Normal', 'Exceso'][0]</t>
+          <t>Clase 0</t>
         </is>
       </c>
       <c r="D424" t="n">
-        <v>-1.328292924614142</v>
+        <v>-1.328292924614143</v>
       </c>
       <c r="E424" t="n">
-        <v>1.328292924614142</v>
+        <v>1.328292924614143</v>
       </c>
       <c r="F424" t="n">
-        <v>0.8763441115306757</v>
+        <v>0.876344111530676</v>
       </c>
     </row>
     <row r="425">
@@ -11459,17 +11459,17 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Clase ['Quiebre', 'Normal', 'Exceso'][1]</t>
+          <t>Clase 1</t>
         </is>
       </c>
       <c r="D425" t="n">
-        <v>0.0697899787286186</v>
+        <v>0.06978997872861849</v>
       </c>
       <c r="E425" t="n">
-        <v>0.0697899787286186</v>
+        <v>0.06978997872861849</v>
       </c>
       <c r="F425" t="n">
-        <v>0.04604408844565854</v>
+        <v>0.04604408844565846</v>
       </c>
     </row>
     <row r="426">
@@ -11485,14 +11485,14 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Clase ['Quiebre', 'Normal', 'Exceso'][2]</t>
+          <t>Clase 2</t>
         </is>
       </c>
       <c r="D426" t="n">
-        <v>0.3751838014685118</v>
+        <v>0.3751838014685119</v>
       </c>
       <c r="E426" t="n">
-        <v>0.3751838014685118</v>
+        <v>0.3751838014685119</v>
       </c>
       <c r="F426" t="n">
         <v>0.2475283192930769</v>
@@ -11511,7 +11511,7 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Clase ['Quiebre', 'Normal', 'Exceso'][0]</t>
+          <t>Clase 0</t>
         </is>
       </c>
       <c r="D427" t="n">
@@ -11537,14 +11537,14 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Clase ['Quiebre', 'Normal', 'Exceso'][1]</t>
+          <t>Clase 1</t>
         </is>
       </c>
       <c r="D428" t="n">
-        <v>0.640633964485523</v>
+        <v>0.6406339644855231</v>
       </c>
       <c r="E428" t="n">
-        <v>0.640633964485523</v>
+        <v>0.6406339644855231</v>
       </c>
       <c r="F428" t="n">
         <v>0.4226596347989481</v>
@@ -11563,14 +11563,14 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Clase ['Quiebre', 'Normal', 'Exceso'][2]</t>
+          <t>Clase 2</t>
         </is>
       </c>
       <c r="D429" t="n">
-        <v>-1.54970982361205</v>
+        <v>-1.549709823612051</v>
       </c>
       <c r="E429" t="n">
-        <v>1.54970982361205</v>
+        <v>1.549709823612051</v>
       </c>
       <c r="F429" t="n">
         <v>1.022424386471962</v>
@@ -11589,17 +11589,17 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Clase ['Quiebre', 'Normal', 'Exceso'][0]</t>
+          <t>Clase 0</t>
         </is>
       </c>
       <c r="D430" t="n">
-        <v>0.1012325450052862</v>
+        <v>0.1012325450052867</v>
       </c>
       <c r="E430" t="n">
-        <v>0.1012325450052862</v>
+        <v>0.1012325450052867</v>
       </c>
       <c r="F430" t="n">
-        <v>0.06678838911712001</v>
+        <v>0.06678838911712029</v>
       </c>
     </row>
     <row r="431">
@@ -11615,7 +11615,7 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Clase ['Quiebre', 'Normal', 'Exceso'][1]</t>
+          <t>Clase 1</t>
         </is>
       </c>
       <c r="D431" t="n">
@@ -11625,7 +11625,7 @@
         <v>1.057872046383418</v>
       </c>
       <c r="F431" t="n">
-        <v>0.697933355980434</v>
+        <v>0.6979333559804343</v>
       </c>
     </row>
     <row r="432">
@@ -11641,14 +11641,14 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Clase ['Quiebre', 'Normal', 'Exceso'][2]</t>
+          <t>Clase 2</t>
         </is>
       </c>
       <c r="D432" t="n">
-        <v>1.849260145894056</v>
+        <v>1.849260145894057</v>
       </c>
       <c r="E432" t="n">
-        <v>1.849260145894056</v>
+        <v>1.849260145894057</v>
       </c>
       <c r="F432" t="n">
         <v>1.220053355334541</v>
@@ -11667,7 +11667,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Clase ['Quiebre', 'Normal', 'Exceso'][0]</t>
+          <t>Clase 0</t>
         </is>
       </c>
       <c r="D433" t="n">
@@ -11677,7 +11677,7 @@
         <v>2.124211644284504</v>
       </c>
       <c r="F433" t="n">
-        <v>1.401453197271514</v>
+        <v>1.401453197271513</v>
       </c>
     </row>
     <row r="434">
@@ -11693,17 +11693,17 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Clase ['Quiebre', 'Normal', 'Exceso'][1]</t>
+          <t>Clase 1</t>
         </is>
       </c>
       <c r="D434" t="n">
-        <v>0.9745952277802817</v>
+        <v>0.9745952277802821</v>
       </c>
       <c r="E434" t="n">
-        <v>0.9745952277802817</v>
+        <v>0.9745952277802821</v>
       </c>
       <c r="F434" t="n">
-        <v>0.6429912959441914</v>
+        <v>0.6429912959441915</v>
       </c>
     </row>
     <row r="435">
@@ -11719,7 +11719,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Clase ['Quiebre', 'Normal', 'Exceso'][2]</t>
+          <t>Clase 2</t>
         </is>
       </c>
       <c r="D435" t="n">
@@ -11745,14 +11745,14 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Clase ['Quiebre', 'Normal', 'Exceso'][0]</t>
+          <t>Clase 0</t>
         </is>
       </c>
       <c r="D436" t="n">
-        <v>1.428182753358793</v>
+        <v>1.428182753358794</v>
       </c>
       <c r="E436" t="n">
-        <v>1.428182753358793</v>
+        <v>1.428182753358794</v>
       </c>
       <c r="F436" t="n">
         <v>0.9422466407093292</v>
@@ -11771,14 +11771,14 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Clase ['Quiebre', 'Normal', 'Exceso'][1]</t>
+          <t>Clase 1</t>
         </is>
       </c>
       <c r="D437" t="n">
-        <v>-1.664508953213003</v>
+        <v>-1.664508953213004</v>
       </c>
       <c r="E437" t="n">
-        <v>1.664508953213003</v>
+        <v>1.664508953213004</v>
       </c>
       <c r="F437" t="n">
         <v>1.098163358930817</v>
@@ -11797,7 +11797,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Clase ['Quiebre', 'Normal', 'Exceso'][2]</t>
+          <t>Clase 2</t>
         </is>
       </c>
       <c r="D438" t="n">
@@ -11807,7 +11807,7 @@
         <v>1.093550140833812</v>
       </c>
       <c r="F438" t="n">
-        <v>0.7214720554667094</v>
+        <v>0.7214720554667093</v>
       </c>
     </row>
     <row r="439">
@@ -11823,17 +11823,17 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Clase ['Quiebre', 'Normal', 'Exceso'][0]</t>
+          <t>Clase 0</t>
         </is>
       </c>
       <c r="D439" t="n">
-        <v>-0.830191656518964</v>
+        <v>-0.8301916565189628</v>
       </c>
       <c r="E439" t="n">
-        <v>0.830191656518964</v>
+        <v>0.8301916565189628</v>
       </c>
       <c r="F439" t="n">
-        <v>0.5477207294796316</v>
+        <v>0.5477207294796307</v>
       </c>
     </row>
     <row r="440">
@@ -11849,14 +11849,14 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Clase ['Quiebre', 'Normal', 'Exceso'][1]</t>
+          <t>Clase 1</t>
         </is>
       </c>
       <c r="D440" t="n">
-        <v>1.038745939621353</v>
+        <v>1.038745939621354</v>
       </c>
       <c r="E440" t="n">
-        <v>1.038745939621353</v>
+        <v>1.038745939621354</v>
       </c>
       <c r="F440" t="n">
         <v>0.6853148659419426</v>
@@ -11875,17 +11875,17 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Clase ['Quiebre', 'Normal', 'Exceso'][2]</t>
+          <t>Clase 2</t>
         </is>
       </c>
       <c r="D441" t="n">
-        <v>0.3315814089031888</v>
+        <v>0.3315814089031885</v>
       </c>
       <c r="E441" t="n">
-        <v>0.3315814089031888</v>
+        <v>0.3315814089031885</v>
       </c>
       <c r="F441" t="n">
-        <v>0.2187615470960711</v>
+        <v>0.2187615470960708</v>
       </c>
     </row>
     <row r="442">
@@ -11901,17 +11901,17 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Clase ['Quiebre', 'Normal', 'Exceso'][0]</t>
+          <t>Clase 0</t>
         </is>
       </c>
       <c r="D442" t="n">
-        <v>-0.2245733724781507</v>
+        <v>-0.2245733724781505</v>
       </c>
       <c r="E442" t="n">
-        <v>0.2245733724781507</v>
+        <v>0.2245733724781505</v>
       </c>
       <c r="F442" t="n">
-        <v>0.1481627651031735</v>
+        <v>0.1481627651031733</v>
       </c>
     </row>
     <row r="443">
@@ -11927,17 +11927,17 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Clase ['Quiebre', 'Normal', 'Exceso'][1]</t>
+          <t>Clase 1</t>
         </is>
       </c>
       <c r="D443" t="n">
-        <v>0.09066238138493514</v>
+        <v>0.09066238138493535</v>
       </c>
       <c r="E443" t="n">
-        <v>0.09066238138493514</v>
+        <v>0.09066238138493535</v>
       </c>
       <c r="F443" t="n">
-        <v>0.05981470095319239</v>
+        <v>0.05981470095319252</v>
       </c>
     </row>
     <row r="444">
@@ -11953,18 +11953,278 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Clase ['Quiebre', 'Normal', 'Exceso'][2]</t>
+          <t>Clase 2</t>
         </is>
       </c>
       <c r="D444" t="n">
-        <v>0.1339109910932158</v>
+        <v>0.1339109910932155</v>
       </c>
       <c r="E444" t="n">
-        <v>0.1339109910932158</v>
+        <v>0.1339109910932155</v>
       </c>
       <c r="F444" t="n">
-        <v>0.08834806414998124</v>
-      </c>
+        <v>0.088348064149981</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>CONFIGURACIÓN_SISTEMA</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Tipo de Modelo</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Red Neuronal Artificial (MLP) de 3 Capas</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr"/>
+      <c r="E445" t="inlineStr"/>
+      <c r="F445" t="inlineStr"/>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>CONFIGURACIÓN_SISTEMA</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Capas Ocultas (hidden_units)</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Capa 1: 16 Neuronas, Capa 2: 10 Neuronas</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr"/>
+      <c r="E446" t="inlineStr"/>
+      <c r="F446" t="inlineStr"/>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>CONFIGURACIÓN_SISTEMA</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Función de Activación Oculta</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>Sigmoide (Múltiples regresiones logísticas paralelas)</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr"/>
+      <c r="E447" t="inlineStr"/>
+      <c r="F447" t="inlineStr"/>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>CONFIGURACIÓN_SISTEMA</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Tasa de Aprendizaje Inicial</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr"/>
+      <c r="E448" t="inlineStr"/>
+      <c r="F448" t="inlineStr"/>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>CONFIGURACIÓN_SISTEMA</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Regularización L2 (lambda)</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr"/>
+      <c r="E449" t="inlineStr"/>
+      <c r="F449" t="inlineStr"/>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>CONFIGURACIÓN_SISTEMA</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Épocas de Entrenamiento</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr"/>
+      <c r="E450" t="inlineStr"/>
+      <c r="F450" t="inlineStr"/>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>CONFIGURACIÓN_SISTEMA</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Muestras de Train Final (80%)</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>9868</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr"/>
+      <c r="E451" t="inlineStr"/>
+      <c r="F451" t="inlineStr"/>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>CONFIGURACIÓN_SISTEMA</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Muestras de Test Final (20%)</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>2468</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr"/>
+      <c r="E452" t="inlineStr"/>
+      <c r="F452" t="inlineStr"/>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>CONFIGURACIÓN_SISTEMA</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Accuracy Promedio Folds (CV)</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>92.5583</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr"/>
+      <c r="E453" t="inlineStr"/>
+      <c r="F453" t="inlineStr"/>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>CONFIGURACIÓN_SISTEMA</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Accuracy Final Train Set</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>96.9193</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr"/>
+      <c r="E454" t="inlineStr"/>
+      <c r="F454" t="inlineStr"/>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>CONFIGURACIÓN_SISTEMA</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Accuracy Final Test Set</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>96.718</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr"/>
+      <c r="E455" t="inlineStr"/>
+      <c r="F455" t="inlineStr"/>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>CONFIGURACIÓN_SISTEMA</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Loss Final Train Set</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>0.088384</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr"/>
+      <c r="E456" t="inlineStr"/>
+      <c r="F456" t="inlineStr"/>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>CONFIGURACIÓN_SISTEMA</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Loss Final Test Set</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>0.094437</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr"/>
+      <c r="E457" t="inlineStr"/>
+      <c r="F457" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/fact_inventario/outputs/01_pesos_finales.xlsx
+++ b/fact_inventario/outputs/01_pesos_finales.xlsx
@@ -465,13 +465,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.01720205134254953</v>
+        <v>-0.0198744566385793</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01720205134254953</v>
+        <v>0.0198744566385793</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01134909034064965</v>
+        <v>0.01306724686407883</v>
       </c>
     </row>
     <row r="3">
@@ -491,13 +491,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.1678030643567723</v>
+        <v>-0.169101631911457</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1678030643567723</v>
+        <v>0.169101631911457</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1107084323200608</v>
+        <v>0.1111825500183112</v>
       </c>
     </row>
     <row r="4">
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.4351649251456693</v>
+        <v>-0.4349162283078713</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4351649251456693</v>
+        <v>0.4349162283078713</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2871009945391936</v>
+        <v>0.2859528601884472</v>
       </c>
     </row>
     <row r="5">
@@ -543,13 +543,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.2210375970584088</v>
+        <v>-0.2687297241667685</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2210375970584088</v>
+        <v>0.2687297241667685</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1458300296715774</v>
+        <v>0.1766869761151867</v>
       </c>
     </row>
     <row r="6">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.2657088671996445</v>
+        <v>0.267522709181239</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2657088671996445</v>
+        <v>0.267522709181239</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1753019961463217</v>
+        <v>0.175893376417274</v>
       </c>
     </row>
     <row r="7">
@@ -595,13 +595,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.215348743121361</v>
+        <v>0.2518383612427147</v>
       </c>
       <c r="E7" t="n">
-        <v>0.215348743121361</v>
+        <v>0.2518383612427147</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1420767960611987</v>
+        <v>0.1655810820918552</v>
       </c>
     </row>
     <row r="8">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.238283710441993</v>
+        <v>0.2424094653470939</v>
       </c>
       <c r="E8" t="n">
-        <v>0.238283710441993</v>
+        <v>0.2424094653470939</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1572081900384895</v>
+        <v>0.1593816818987144</v>
       </c>
     </row>
     <row r="9">
@@ -647,13 +647,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.2808382559013413</v>
+        <v>0.2872866996833172</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2808382559013413</v>
+        <v>0.2872866996833172</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1852836428554933</v>
+        <v>0.1888879929547969</v>
       </c>
     </row>
     <row r="10">
@@ -673,13 +673,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.0241304039007444</v>
+        <v>-0.01375959933174562</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0241304039007444</v>
+        <v>0.01375959933174562</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0159200858300266</v>
+        <v>0.009046792296686753</v>
       </c>
     </row>
     <row r="11">
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.4984185467830455</v>
+        <v>-0.5695185550230676</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4984185467830455</v>
+        <v>0.5695185550230676</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3288327073471999</v>
+        <v>0.3744524787517347</v>
       </c>
     </row>
     <row r="12">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.3918480332147747</v>
+        <v>-0.3846170596312342</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3918480332147747</v>
+        <v>0.3846170596312342</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2585225819992961</v>
+        <v>0.2528816841503715</v>
       </c>
     </row>
     <row r="13">
@@ -751,13 +751,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.6214263994842752</v>
+        <v>0.6217834489694287</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6214263994842752</v>
+        <v>0.6217834489694287</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4099874025121007</v>
+        <v>0.4088160985448049</v>
       </c>
     </row>
     <row r="14">
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.2328399541800045</v>
+        <v>0.2582400411338718</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2328399541800045</v>
+        <v>0.2582400411338718</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1536166601459489</v>
+        <v>0.169790119501219</v>
       </c>
     </row>
     <row r="15">
@@ -803,13 +803,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.2823871307507417</v>
+        <v>-0.2900962791910637</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2823871307507417</v>
+        <v>0.2900962791910637</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1863055163659348</v>
+        <v>0.1907352620238146</v>
       </c>
     </row>
     <row r="16">
@@ -829,13 +829,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.03118721546171591</v>
+        <v>0.111393657725856</v>
       </c>
       <c r="E16" t="n">
-        <v>0.03118721546171591</v>
+        <v>0.111393657725856</v>
       </c>
       <c r="F16" t="n">
-        <v>0.02057583242254529</v>
+        <v>0.0732401620364759</v>
       </c>
     </row>
     <row r="17">
@@ -855,13 +855,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.7544636701196979</v>
+        <v>0.7447072038620323</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7544636701196979</v>
+        <v>0.7447072038620323</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4977590277124178</v>
+        <v>0.4896371785799263</v>
       </c>
     </row>
     <row r="18">
@@ -881,13 +881,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.2121757700647908</v>
+        <v>-0.2034938619835325</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2121757700647908</v>
+        <v>0.2034938619835325</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1399834202683717</v>
+        <v>0.1337950807018233</v>
       </c>
     </row>
     <row r="19">
@@ -907,13 +907,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.3120404355066062</v>
+        <v>-0.3103531614383311</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3120404355066062</v>
+        <v>0.3103531614383311</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2058693479039032</v>
+        <v>0.2040539497160252</v>
       </c>
     </row>
     <row r="20">
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.1030165900234798</v>
+        <v>0.1026772588105201</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1030165900234798</v>
+        <v>0.1026772588105201</v>
       </c>
       <c r="F20" t="n">
-        <v>0.06796541665180612</v>
+        <v>0.06750922113762448</v>
       </c>
     </row>
     <row r="21">
@@ -959,13 +959,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.07094451355466762</v>
+        <v>0.06379234370176926</v>
       </c>
       <c r="E21" t="n">
-        <v>0.07094451355466762</v>
+        <v>0.06379234370176926</v>
       </c>
       <c r="F21" t="n">
-        <v>0.04680579527825275</v>
+        <v>0.04194279714651718</v>
       </c>
     </row>
     <row r="22">
@@ -985,13 +985,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.09489948024889669</v>
+        <v>0.1001013676146068</v>
       </c>
       <c r="E22" t="n">
-        <v>0.09489948024889669</v>
+        <v>0.1001013676146068</v>
       </c>
       <c r="F22" t="n">
-        <v>0.06261013603426432</v>
+        <v>0.065815599683508</v>
       </c>
     </row>
     <row r="23">
@@ -1011,13 +1011,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.1664143838388772</v>
+        <v>0.1486248153659518</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1664143838388772</v>
+        <v>0.1486248153659518</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1097922473640894</v>
+        <v>0.09771925783093301</v>
       </c>
     </row>
     <row r="24">
@@ -1037,13 +1037,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.3060770098962858</v>
+        <v>0.2991368405130814</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3060770098962858</v>
+        <v>0.2991368405130814</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2019349650420253</v>
+        <v>0.1966793363063451</v>
       </c>
     </row>
     <row r="25">
@@ -1063,13 +1063,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.08293224211623104</v>
+        <v>0.08635290997199016</v>
       </c>
       <c r="E25" t="n">
-        <v>0.08293224211623104</v>
+        <v>0.08635290997199016</v>
       </c>
       <c r="F25" t="n">
-        <v>0.05471472495850827</v>
+        <v>0.05677613293060735</v>
       </c>
     </row>
     <row r="26">
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.1989830091763157</v>
+        <v>0.2001718598584065</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1989830091763157</v>
+        <v>0.2001718598584065</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1312794679208081</v>
+        <v>0.1316108991344263</v>
       </c>
     </row>
     <row r="27">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-0.01031521888564037</v>
+        <v>0.02038528165983419</v>
       </c>
       <c r="E27" t="n">
-        <v>0.01031521888564037</v>
+        <v>0.02038528165983419</v>
       </c>
       <c r="F27" t="n">
-        <v>0.006805487827323107</v>
+        <v>0.01340310895975639</v>
       </c>
     </row>
     <row r="28">
@@ -1141,13 +1141,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-0.003733207688397674</v>
+        <v>-0.0006545982910663299</v>
       </c>
       <c r="E28" t="n">
-        <v>0.003733207688397674</v>
+        <v>0.0006545982910663299</v>
       </c>
       <c r="F28" t="n">
-        <v>0.002462991795125847</v>
+        <v>0.0004303915131729266</v>
       </c>
     </row>
     <row r="29">
@@ -1167,13 +1167,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-0.4329768894859887</v>
+        <v>-0.4285822441152756</v>
       </c>
       <c r="E29" t="n">
-        <v>0.4329768894859887</v>
+        <v>0.4285822441152756</v>
       </c>
       <c r="F29" t="n">
-        <v>0.285657433310606</v>
+        <v>0.2817883319911251</v>
       </c>
     </row>
     <row r="30">
@@ -1193,13 +1193,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-0.2560725127730249</v>
+        <v>-0.2742780781766161</v>
       </c>
       <c r="E30" t="n">
-        <v>0.2560725127730249</v>
+        <v>0.2742780781766161</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1689443906047249</v>
+        <v>0.1803349607043726</v>
       </c>
     </row>
     <row r="31">
@@ -1219,13 +1219,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.1040280552947548</v>
+        <v>0.1099618443239334</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1040280552947548</v>
+        <v>0.1099618443239334</v>
       </c>
       <c r="F31" t="n">
-        <v>0.06863273303818004</v>
+        <v>0.07229875973670685</v>
       </c>
     </row>
     <row r="32">
@@ -1245,13 +1245,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-0.3791405065816921</v>
+        <v>-0.4012962897971243</v>
       </c>
       <c r="E32" t="n">
-        <v>0.3791405065816921</v>
+        <v>0.4012962897971243</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2501387639945016</v>
+        <v>0.2638481031093382</v>
       </c>
     </row>
     <row r="33">
@@ -1271,13 +1271,13 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-0.346771515427099</v>
+        <v>-0.3383489926883932</v>
       </c>
       <c r="E33" t="n">
-        <v>0.346771515427099</v>
+        <v>0.3383489926883932</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2287832525189312</v>
+        <v>0.2224609152377656</v>
       </c>
     </row>
     <row r="34">
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>-0.2232199533740553</v>
+        <v>-0.2237997318194161</v>
       </c>
       <c r="E34" t="n">
-        <v>0.2232199533740553</v>
+        <v>0.2237997318194161</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1472698439407336</v>
+        <v>0.1471459772199336</v>
       </c>
     </row>
     <row r="35">
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.01778206734325321</v>
+        <v>0.01666463967694336</v>
       </c>
       <c r="E35" t="n">
-        <v>0.01778206734325321</v>
+        <v>0.01666463967694336</v>
       </c>
       <c r="F35" t="n">
-        <v>0.01173175714357483</v>
+        <v>0.01095682586545964</v>
       </c>
     </row>
     <row r="36">
@@ -1349,13 +1349,13 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-0.221553421599323</v>
+        <v>-0.2148759327927519</v>
       </c>
       <c r="E36" t="n">
-        <v>0.221553421599323</v>
+        <v>0.2148759327927519</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1461703460209583</v>
+        <v>0.1412786729223917</v>
       </c>
     </row>
     <row r="37">
@@ -1375,13 +1375,13 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>-0.3868583956063532</v>
+        <v>-0.416013192411426</v>
       </c>
       <c r="E37" t="n">
-        <v>0.3868583956063532</v>
+        <v>0.416013192411426</v>
       </c>
       <c r="F37" t="n">
-        <v>0.2552306578643524</v>
+        <v>0.2735243122773607</v>
       </c>
     </row>
     <row r="38">
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.0002523875681593033</v>
+        <v>0.00356538339545798</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0002523875681593033</v>
+        <v>0.00356538339545798</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0001665132404768345</v>
+        <v>0.002344202200884291</v>
       </c>
     </row>
     <row r="39">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.6001467996576632</v>
+        <v>0.6233265411369358</v>
       </c>
       <c r="E39" t="n">
-        <v>0.6001467996576632</v>
+        <v>0.6233265411369358</v>
       </c>
       <c r="F39" t="n">
-        <v>0.3959481407963931</v>
+        <v>0.409830665466232</v>
       </c>
     </row>
     <row r="40">
@@ -1453,13 +1453,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.2259264396334942</v>
+        <v>0.2326414307707923</v>
       </c>
       <c r="E40" t="n">
-        <v>0.2259264396334942</v>
+        <v>0.2326414307707923</v>
       </c>
       <c r="F40" t="n">
-        <v>0.1490554540666679</v>
+        <v>0.1529593015787604</v>
       </c>
     </row>
     <row r="41">
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.105882477842336</v>
+        <v>0.1040127309173088</v>
       </c>
       <c r="E41" t="n">
-        <v>0.105882477842336</v>
+        <v>0.1040127309173088</v>
       </c>
       <c r="F41" t="n">
-        <v>0.06985619229912178</v>
+        <v>0.06838728004594324</v>
       </c>
     </row>
     <row r="42">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.128937870188745</v>
+        <v>0.1062889148272637</v>
       </c>
       <c r="E42" t="n">
-        <v>0.128937870188745</v>
+        <v>0.1062889148272637</v>
       </c>
       <c r="F42" t="n">
-        <v>0.08506703694596364</v>
+        <v>0.06988384710185402</v>
       </c>
     </row>
     <row r="43">
@@ -1531,13 +1531,13 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>-0.6771883226391106</v>
+        <v>-0.7245185708790119</v>
       </c>
       <c r="E43" t="n">
-        <v>0.6771883226391106</v>
+        <v>0.7245185708790119</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4467764511465059</v>
+        <v>0.4763633640633917</v>
       </c>
     </row>
     <row r="44">
@@ -1557,13 +1557,13 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>-0.3792990207095798</v>
+        <v>-0.3735712532909651</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3792990207095798</v>
+        <v>0.3735712532909651</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2502433440310242</v>
+        <v>0.2456191822925385</v>
       </c>
     </row>
     <row r="45">
@@ -1583,13 +1583,13 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.2660680004636837</v>
+        <v>0.2568632816659488</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2660680004636837</v>
+        <v>0.2568632816659488</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1755389350890529</v>
+        <v>0.168884914585836</v>
       </c>
     </row>
     <row r="46">
@@ -1609,13 +1609,13 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.5630356570138377</v>
+        <v>0.5718419165311123</v>
       </c>
       <c r="E46" t="n">
-        <v>0.5630356570138377</v>
+        <v>0.5718419165311123</v>
       </c>
       <c r="F46" t="n">
-        <v>0.3714639846848646</v>
+        <v>0.3759800645837511</v>
       </c>
     </row>
     <row r="47">
@@ -1635,13 +1635,13 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-0.1316561839127882</v>
+        <v>-0.1435315731647824</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1316561839127882</v>
+        <v>0.1435315731647824</v>
       </c>
       <c r="F47" t="n">
-        <v>0.08686045026708802</v>
+        <v>0.09437050448428638</v>
       </c>
     </row>
     <row r="48">
@@ -1661,13 +1661,13 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.08322207419077757</v>
+        <v>0.1516753833336351</v>
       </c>
       <c r="E48" t="n">
-        <v>0.08322207419077757</v>
+        <v>0.1516753833336351</v>
       </c>
       <c r="F48" t="n">
-        <v>0.05490594229254274</v>
+        <v>0.09972497428569081</v>
       </c>
     </row>
     <row r="49">
@@ -1687,13 +1687,13 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.8811770867208217</v>
+        <v>0.8615600059560854</v>
       </c>
       <c r="E49" t="n">
-        <v>0.8811770867208217</v>
+        <v>0.8615600059560854</v>
       </c>
       <c r="F49" t="n">
-        <v>0.5813584766235724</v>
+        <v>0.5664666708015306</v>
       </c>
     </row>
     <row r="50">
@@ -1713,13 +1713,13 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.03281472281817768</v>
+        <v>0.03949260917964879</v>
       </c>
       <c r="E50" t="n">
-        <v>0.03281472281817768</v>
+        <v>0.03949260917964879</v>
       </c>
       <c r="F50" t="n">
-        <v>0.02164958389850263</v>
+        <v>0.02596597647129166</v>
       </c>
     </row>
     <row r="51">
@@ -1739,13 +1739,13 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.09356392931694281</v>
+        <v>0.09414963700752793</v>
       </c>
       <c r="E51" t="n">
-        <v>0.09356392931694281</v>
+        <v>0.09414963700752793</v>
       </c>
       <c r="F51" t="n">
-        <v>0.06172900343679372</v>
+        <v>0.06190239921088601</v>
       </c>
     </row>
     <row r="52">
@@ -1765,13 +1765,13 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>-0.3331047480840262</v>
+        <v>-0.3274816758241264</v>
       </c>
       <c r="E52" t="n">
-        <v>0.3331047480840262</v>
+        <v>0.3274816758241264</v>
       </c>
       <c r="F52" t="n">
-        <v>0.2197665733943016</v>
+        <v>0.2153157683390128</v>
       </c>
     </row>
     <row r="53">
@@ -1791,13 +1791,13 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.305999647016324</v>
+        <v>0.3321475909763495</v>
       </c>
       <c r="E53" t="n">
-        <v>0.305999647016324</v>
+        <v>0.3321475909763495</v>
       </c>
       <c r="F53" t="n">
-        <v>0.2018839247157168</v>
+        <v>0.2183835586313316</v>
       </c>
     </row>
     <row r="54">
@@ -1817,13 +1817,13 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.01988359986406831</v>
+        <v>0.01813006074686858</v>
       </c>
       <c r="E54" t="n">
-        <v>0.01988359986406831</v>
+        <v>0.01813006074686858</v>
       </c>
       <c r="F54" t="n">
-        <v>0.01311824774039972</v>
+        <v>0.01192032485457738</v>
       </c>
     </row>
     <row r="55">
@@ -1843,13 +1843,13 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>-0.03384198667782844</v>
+        <v>-0.03380274179330699</v>
       </c>
       <c r="E55" t="n">
-        <v>0.03384198667782844</v>
+        <v>0.03380274179330699</v>
       </c>
       <c r="F55" t="n">
-        <v>0.02232732343750886</v>
+        <v>0.02222494832077241</v>
       </c>
     </row>
     <row r="56">
@@ -1869,13 +1869,13 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>-0.1485936887322684</v>
+        <v>-0.1353843868637866</v>
       </c>
       <c r="E56" t="n">
-        <v>0.1485936887322684</v>
+        <v>0.1353843868637866</v>
       </c>
       <c r="F56" t="n">
-        <v>0.09803500547062917</v>
+        <v>0.08901381491139537</v>
       </c>
     </row>
     <row r="57">
@@ -1895,13 +1895,13 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>-0.2517690437795882</v>
+        <v>-0.2491084833868396</v>
       </c>
       <c r="E57" t="n">
-        <v>0.2517690437795882</v>
+        <v>0.2491084833868396</v>
       </c>
       <c r="F57" t="n">
-        <v>0.1661051676881016</v>
+        <v>0.1637862160233028</v>
       </c>
     </row>
     <row r="58">
@@ -1921,13 +1921,13 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>-0.1076931080503719</v>
+        <v>-0.1026781292004938</v>
       </c>
       <c r="E58" t="n">
-        <v>0.1076931080503719</v>
+        <v>0.1026781292004938</v>
       </c>
       <c r="F58" t="n">
-        <v>0.07105075946993823</v>
+        <v>0.06750979340990652</v>
       </c>
     </row>
     <row r="59">
@@ -1947,13 +1947,13 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.2083750233268926</v>
+        <v>0.2151354959429504</v>
       </c>
       <c r="E59" t="n">
-        <v>0.2083750233268926</v>
+        <v>0.2151354959429504</v>
       </c>
       <c r="F59" t="n">
-        <v>0.1374758694401956</v>
+        <v>0.1414493329722306</v>
       </c>
     </row>
     <row r="60">
@@ -1973,13 +1973,13 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.3088525780538263</v>
+        <v>0.332752870700786</v>
       </c>
       <c r="E60" t="n">
-        <v>0.3088525780538263</v>
+        <v>0.332752870700786</v>
       </c>
       <c r="F60" t="n">
-        <v>0.2037661520986899</v>
+        <v>0.218781523704031</v>
       </c>
     </row>
     <row r="61">
@@ -1999,13 +1999,13 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>-0.007620815319650634</v>
+        <v>-0.04144352856143818</v>
       </c>
       <c r="E61" t="n">
-        <v>0.007620815319650634</v>
+        <v>0.04144352856143818</v>
       </c>
       <c r="F61" t="n">
-        <v>0.005027849284357688</v>
+        <v>0.02724868551020305</v>
       </c>
     </row>
     <row r="62">
@@ -2025,13 +2025,13 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.1483634676876706</v>
+        <v>0.1296286010286399</v>
       </c>
       <c r="E62" t="n">
-        <v>0.1483634676876706</v>
+        <v>0.1296286010286399</v>
       </c>
       <c r="F62" t="n">
-        <v>0.09788311664170818</v>
+        <v>0.08522944607191564</v>
       </c>
     </row>
     <row r="63">
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.02765391919337822</v>
+        <v>0.02625892412665466</v>
       </c>
       <c r="E63" t="n">
-        <v>0.02765391919337822</v>
+        <v>0.02625892412665466</v>
       </c>
       <c r="F63" t="n">
-        <v>0.01824473261641592</v>
+        <v>0.01726496729888161</v>
       </c>
     </row>
     <row r="64">
@@ -2077,13 +2077,13 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.04417187916363711</v>
+        <v>0.02924390679434857</v>
       </c>
       <c r="E64" t="n">
-        <v>0.04417187916363711</v>
+        <v>0.02924390679434857</v>
       </c>
       <c r="F64" t="n">
-        <v>0.02914249220407673</v>
+        <v>0.01922756210653221</v>
       </c>
     </row>
     <row r="65">
@@ -2103,13 +2103,13 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.1498424929507562</v>
+        <v>0.1074460673592415</v>
       </c>
       <c r="E65" t="n">
-        <v>0.1498424929507562</v>
+        <v>0.1074460673592415</v>
       </c>
       <c r="F65" t="n">
-        <v>0.09885890673747087</v>
+        <v>0.07064466275934454</v>
       </c>
     </row>
     <row r="66">
@@ -2129,13 +2129,13 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.3853319507746643</v>
+        <v>0.3774659821376612</v>
       </c>
       <c r="E66" t="n">
-        <v>0.3853319507746643</v>
+        <v>0.3774659821376612</v>
       </c>
       <c r="F66" t="n">
-        <v>0.2542235826062985</v>
+        <v>0.2481799256745556</v>
       </c>
     </row>
     <row r="67">
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>-0.388363048534463</v>
+        <v>-0.3874312223489635</v>
       </c>
       <c r="E67" t="n">
-        <v>0.388363048534463</v>
+        <v>0.3874312223489635</v>
       </c>
       <c r="F67" t="n">
-        <v>0.256223355867189</v>
+        <v>0.2547319666318998</v>
       </c>
     </row>
     <row r="68">
@@ -2181,13 +2181,13 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.3119235106596341</v>
+        <v>0.321483632323364</v>
       </c>
       <c r="E68" t="n">
-        <v>0.3119235106596341</v>
+        <v>0.321483632323364</v>
       </c>
       <c r="F68" t="n">
-        <v>0.2057922064848405</v>
+        <v>0.2113721176243662</v>
       </c>
     </row>
     <row r="69">
@@ -2207,13 +2207,13 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>-0.2068401964467619</v>
+        <v>-0.1374638723245996</v>
       </c>
       <c r="E69" t="n">
-        <v>0.2068401964467619</v>
+        <v>0.1374638723245996</v>
       </c>
       <c r="F69" t="n">
-        <v>0.1364632641076691</v>
+        <v>0.09038105479930049</v>
       </c>
     </row>
     <row r="70">
@@ -2233,13 +2233,13 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>-0.288164383258551</v>
+        <v>-0.281228713444079</v>
       </c>
       <c r="E70" t="n">
-        <v>0.288164383258551</v>
+        <v>0.281228713444079</v>
       </c>
       <c r="F70" t="n">
-        <v>0.1901170711233428</v>
+        <v>0.1849049305180782</v>
       </c>
     </row>
     <row r="71">
@@ -2259,13 +2259,13 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>-0.07000533736934135</v>
+        <v>-0.0921743463118103</v>
       </c>
       <c r="E71" t="n">
-        <v>0.07000533736934135</v>
+        <v>0.0921743463118103</v>
       </c>
       <c r="F71" t="n">
-        <v>0.04618617177168351</v>
+        <v>0.06060366628859036</v>
       </c>
     </row>
     <row r="72">
@@ -2285,13 +2285,13 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>-0.2684404434199759</v>
+        <v>-0.2658860585398171</v>
       </c>
       <c r="E72" t="n">
-        <v>0.2684404434199759</v>
+        <v>0.2658860585398171</v>
       </c>
       <c r="F72" t="n">
-        <v>0.1771041594278734</v>
+        <v>0.1748172957801712</v>
       </c>
     </row>
     <row r="73">
@@ -2311,13 +2311,13 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.3497011569179131</v>
+        <v>0.3406815757213083</v>
       </c>
       <c r="E73" t="n">
-        <v>0.3497011569179131</v>
+        <v>0.3406815757213083</v>
       </c>
       <c r="F73" t="n">
-        <v>0.2307160897883285</v>
+        <v>0.2239945641257002</v>
       </c>
     </row>
     <row r="74">
@@ -2337,13 +2337,13 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.1112993347071229</v>
+        <v>0.1215672793311867</v>
       </c>
       <c r="E74" t="n">
-        <v>0.1112993347071229</v>
+        <v>0.1215672793311867</v>
       </c>
       <c r="F74" t="n">
-        <v>0.07342997525655152</v>
+        <v>0.07992921157559756</v>
       </c>
     </row>
     <row r="75">
@@ -2363,13 +2363,13 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.3595356312478758</v>
+        <v>0.4197754925724105</v>
       </c>
       <c r="E75" t="n">
-        <v>0.3595356312478758</v>
+        <v>0.4197754925724105</v>
       </c>
       <c r="F75" t="n">
-        <v>0.2372044053619178</v>
+        <v>0.2759979851869846</v>
       </c>
     </row>
     <row r="76">
@@ -2389,13 +2389,13 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>-0.2956577858396833</v>
+        <v>-0.3019352667935279</v>
       </c>
       <c r="E76" t="n">
-        <v>0.2956577858396833</v>
+        <v>0.3019352667935279</v>
       </c>
       <c r="F76" t="n">
-        <v>0.1950608595796516</v>
+        <v>0.1985192722453503</v>
       </c>
     </row>
     <row r="77">
@@ -2415,13 +2415,13 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>-0.2394151921092406</v>
+        <v>-0.2400878276211187</v>
       </c>
       <c r="E77" t="n">
-        <v>0.2394151921092406</v>
+        <v>0.2400878276211187</v>
       </c>
       <c r="F77" t="n">
-        <v>0.1579546875000229</v>
+        <v>0.1578552294353355</v>
       </c>
     </row>
     <row r="78">
@@ -2441,13 +2441,13 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>-0.02522880922510278</v>
+        <v>-0.0627145401298364</v>
       </c>
       <c r="E78" t="n">
-        <v>0.02522880922510278</v>
+        <v>0.0627145401298364</v>
       </c>
       <c r="F78" t="n">
-        <v>0.01664476110325749</v>
+        <v>0.04123415259831385</v>
       </c>
     </row>
     <row r="79">
@@ -2467,13 +2467,13 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>-0.3041807409454864</v>
+        <v>-0.3303192419782208</v>
       </c>
       <c r="E79" t="n">
-        <v>0.3041807409454864</v>
+        <v>0.3303192419782208</v>
       </c>
       <c r="F79" t="n">
-        <v>0.200683897526632</v>
+        <v>0.2171814383345753</v>
       </c>
     </row>
     <row r="80">
@@ -2493,13 +2493,13 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>-0.3340675022083794</v>
+        <v>-0.3208778928635121</v>
       </c>
       <c r="E80" t="n">
-        <v>0.3340675022083794</v>
+        <v>0.3208778928635121</v>
       </c>
       <c r="F80" t="n">
-        <v>0.2204017524968132</v>
+        <v>0.2109738502804514</v>
       </c>
     </row>
     <row r="81">
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>-0.2640915362424738</v>
+        <v>-0.2621365608815597</v>
       </c>
       <c r="E81" t="n">
-        <v>0.2640915362424738</v>
+        <v>0.2621365608815597</v>
       </c>
       <c r="F81" t="n">
-        <v>0.1742349585716658</v>
+        <v>0.1723520403818613</v>
       </c>
     </row>
     <row r="82">
@@ -2545,13 +2545,13 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>-0.2908239202239663</v>
+        <v>-0.2935833736901258</v>
       </c>
       <c r="E82" t="n">
-        <v>0.2908239202239663</v>
+        <v>0.2935833736901258</v>
       </c>
       <c r="F82" t="n">
-        <v>0.1918717063516505</v>
+        <v>0.1930279900961466</v>
       </c>
     </row>
     <row r="83">
@@ -2571,13 +2571,13 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.1825353590884093</v>
+        <v>0.1811060075110439</v>
       </c>
       <c r="E83" t="n">
-        <v>0.1825353590884093</v>
+        <v>0.1811060075110439</v>
       </c>
       <c r="F83" t="n">
-        <v>0.120428095429126</v>
+        <v>0.1190753011139275</v>
       </c>
     </row>
     <row r="84">
@@ -2597,13 +2597,13 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>-0.08024786201111687</v>
+        <v>-0.05891332084852698</v>
       </c>
       <c r="E84" t="n">
-        <v>0.08024786201111687</v>
+        <v>0.05891332084852698</v>
       </c>
       <c r="F84" t="n">
-        <v>0.05294369941539604</v>
+        <v>0.03873489077512787</v>
       </c>
     </row>
     <row r="85">
@@ -2623,13 +2623,13 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>-0.3214604661168977</v>
+        <v>-0.3317435277442727</v>
       </c>
       <c r="E85" t="n">
-        <v>0.3214604661168977</v>
+        <v>0.3317435277442727</v>
       </c>
       <c r="F85" t="n">
-        <v>0.2120842333427951</v>
+        <v>0.2181178912926837</v>
       </c>
     </row>
     <row r="86">
@@ -2649,13 +2649,13 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.4725974346821236</v>
+        <v>0.4879000133140313</v>
       </c>
       <c r="E86" t="n">
-        <v>0.4725974346821236</v>
+        <v>0.4879000133140313</v>
       </c>
       <c r="F86" t="n">
-        <v>0.3117971731487551</v>
+        <v>0.3207891433160479</v>
       </c>
     </row>
     <row r="87">
@@ -2675,13 +2675,13 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.4785528407944308</v>
+        <v>0.4913856650230981</v>
       </c>
       <c r="E87" t="n">
-        <v>0.4785528407944308</v>
+        <v>0.4913856650230981</v>
       </c>
       <c r="F87" t="n">
-        <v>0.3157262651295847</v>
+        <v>0.3230809227690851</v>
       </c>
     </row>
     <row r="88">
@@ -2701,13 +2701,13 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>-0.2311952217361309</v>
+        <v>-0.211216360858597</v>
       </c>
       <c r="E88" t="n">
-        <v>0.2311952217361309</v>
+        <v>0.211216360858597</v>
       </c>
       <c r="F88" t="n">
-        <v>0.1525315443815547</v>
+        <v>0.1388725427448436</v>
       </c>
     </row>
     <row r="89">
@@ -2727,13 +2727,13 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>-0.2728701254506482</v>
+        <v>-0.26799492885644</v>
       </c>
       <c r="E89" t="n">
-        <v>0.2728701254506482</v>
+        <v>0.26799492885644</v>
       </c>
       <c r="F89" t="n">
-        <v>0.1800266516670462</v>
+        <v>0.1762038559026828</v>
       </c>
     </row>
     <row r="90">
@@ -2753,13 +2753,13 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>-0.1186585795104678</v>
+        <v>-0.1338914376879377</v>
       </c>
       <c r="E90" t="n">
-        <v>0.1186585795104678</v>
+        <v>0.1338914376879377</v>
       </c>
       <c r="F90" t="n">
-        <v>0.0782852528306585</v>
+        <v>0.08803221648125403</v>
       </c>
     </row>
     <row r="91">
@@ -2779,13 +2779,13 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>-0.3436245415470214</v>
+        <v>-0.3593303849883411</v>
       </c>
       <c r="E91" t="n">
-        <v>0.3436245415470214</v>
+        <v>0.3593303849883411</v>
       </c>
       <c r="F91" t="n">
-        <v>0.2267070297386676</v>
+        <v>0.2362559606934133</v>
       </c>
     </row>
     <row r="92">
@@ -2805,13 +2805,13 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.06100052785126208</v>
+        <v>0.07356843929132559</v>
       </c>
       <c r="E92" t="n">
-        <v>0.06100052785126208</v>
+        <v>0.07356843929132559</v>
       </c>
       <c r="F92" t="n">
-        <v>0.04024522934069338</v>
+        <v>0.04837047749816963</v>
       </c>
     </row>
     <row r="93">
@@ -2831,13 +2831,13 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0.612451415259066</v>
+        <v>0.5916920287612063</v>
       </c>
       <c r="E93" t="n">
-        <v>0.612451415259066</v>
+        <v>0.5916920287612063</v>
       </c>
       <c r="F93" t="n">
-        <v>0.4040661373821764</v>
+        <v>0.3890313052544923</v>
       </c>
     </row>
     <row r="94">
@@ -2857,13 +2857,13 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0.08634182248979913</v>
+        <v>0.07310846112232418</v>
       </c>
       <c r="E94" t="n">
-        <v>0.08634182248979913</v>
+        <v>0.07310846112232418</v>
       </c>
       <c r="F94" t="n">
-        <v>0.05696420293719655</v>
+        <v>0.04806804667473968</v>
       </c>
     </row>
     <row r="95">
@@ -2883,13 +2883,13 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.3574406206475763</v>
+        <v>0.3360157230251342</v>
       </c>
       <c r="E95" t="n">
-        <v>0.3574406206475763</v>
+        <v>0.3360157230251342</v>
       </c>
       <c r="F95" t="n">
-        <v>0.2358222176161687</v>
+        <v>0.2209268148975788</v>
       </c>
     </row>
     <row r="96">
@@ -2909,13 +2909,13 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.2083441282725198</v>
+        <v>0.3131605664013363</v>
       </c>
       <c r="E96" t="n">
-        <v>0.2083441282725198</v>
+        <v>0.3131605664013363</v>
       </c>
       <c r="F96" t="n">
-        <v>0.1374554863616794</v>
+        <v>0.2058997890446747</v>
       </c>
     </row>
     <row r="97">
@@ -2935,13 +2935,13 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.3636130315236296</v>
+        <v>0.326417473645829</v>
       </c>
       <c r="E97" t="n">
-        <v>0.3636130315236296</v>
+        <v>0.326417473645829</v>
       </c>
       <c r="F97" t="n">
-        <v>0.2398944789562256</v>
+        <v>0.2146160665645195</v>
       </c>
     </row>
     <row r="98">
@@ -2961,13 +2961,13 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>-0.3524281497029925</v>
+        <v>-0.3570950240168736</v>
       </c>
       <c r="E98" t="n">
-        <v>0.3524281497029925</v>
+        <v>0.3570950240168736</v>
       </c>
       <c r="F98" t="n">
-        <v>0.2325152291386229</v>
+        <v>0.2347862342915457</v>
       </c>
     </row>
     <row r="99">
@@ -2987,13 +2987,13 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>-0.0722662491184077</v>
+        <v>-0.07367330447645391</v>
       </c>
       <c r="E99" t="n">
-        <v>0.0722662491184077</v>
+        <v>0.07367330447645391</v>
       </c>
       <c r="F99" t="n">
-        <v>0.04767781315685492</v>
+        <v>0.04843942525792167</v>
       </c>
     </row>
     <row r="100">
@@ -3013,13 +3013,13 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>-0.2627912214334839</v>
+        <v>-0.2623620547541022</v>
       </c>
       <c r="E100" t="n">
-        <v>0.2627912214334839</v>
+        <v>0.2623620547541022</v>
       </c>
       <c r="F100" t="n">
-        <v>0.1733770730820435</v>
+        <v>0.1725003002388442</v>
       </c>
     </row>
     <row r="101">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>-0.1630608659402634</v>
+        <v>-0.1713791486133061</v>
       </c>
       <c r="E101" t="n">
-        <v>0.1630608659402634</v>
+        <v>0.1713791486133061</v>
       </c>
       <c r="F101" t="n">
-        <v>0.1075797567237311</v>
+        <v>0.1126799933709186</v>
       </c>
     </row>
     <row r="102">
@@ -3065,13 +3065,13 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.07358052296812426</v>
+        <v>0.07834249805088704</v>
       </c>
       <c r="E102" t="n">
-        <v>0.07358052296812426</v>
+        <v>0.07834249805088704</v>
       </c>
       <c r="F102" t="n">
-        <v>0.04854490815359477</v>
+        <v>0.05150937107847064</v>
       </c>
     </row>
     <row r="103">
@@ -3091,13 +3091,13 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0.264638980020179</v>
+        <v>0.2448425411035297</v>
       </c>
       <c r="E103" t="n">
-        <v>0.264638980020179</v>
+        <v>0.2448425411035297</v>
       </c>
       <c r="F103" t="n">
-        <v>0.1745961357804697</v>
+        <v>0.1609814036987377</v>
       </c>
     </row>
     <row r="104">
@@ -3117,13 +3117,13 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>-0.4117658492051712</v>
+        <v>-0.4006968147751367</v>
       </c>
       <c r="E104" t="n">
-        <v>0.4117658492051712</v>
+        <v>0.4006968147751367</v>
       </c>
       <c r="F104" t="n">
-        <v>0.2716634039025716</v>
+        <v>0.2634539545676389</v>
       </c>
     </row>
     <row r="105">
@@ -3143,13 +3143,13 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>-0.2875477646950562</v>
+        <v>-0.2887663488394774</v>
       </c>
       <c r="E105" t="n">
-        <v>0.2875477646950562</v>
+        <v>0.2887663488394774</v>
       </c>
       <c r="F105" t="n">
-        <v>0.1897102557009569</v>
+        <v>0.1898608467614383</v>
       </c>
     </row>
     <row r="106">
@@ -3169,13 +3169,13 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>-0.1469458685259343</v>
+        <v>-0.1270653051678496</v>
       </c>
       <c r="E106" t="n">
-        <v>0.1469458685259343</v>
+        <v>0.1270653051678496</v>
       </c>
       <c r="F106" t="n">
-        <v>0.09694785254831606</v>
+        <v>0.08354410591858542</v>
       </c>
     </row>
     <row r="107">
@@ -3195,13 +3195,13 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0.02957639128356525</v>
+        <v>0.03064474783124544</v>
       </c>
       <c r="E107" t="n">
-        <v>0.02957639128356525</v>
+        <v>0.03064474783124544</v>
       </c>
       <c r="F107" t="n">
-        <v>0.01951308770933104</v>
+        <v>0.02014860040102981</v>
       </c>
     </row>
     <row r="108">
@@ -3221,13 +3221,13 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0.2476075243739539</v>
+        <v>0.2446111007739234</v>
       </c>
       <c r="E108" t="n">
-        <v>0.2476075243739539</v>
+        <v>0.2446111007739234</v>
       </c>
       <c r="F108" t="n">
-        <v>0.1633595963170822</v>
+        <v>0.1608292341085814</v>
       </c>
     </row>
     <row r="109">
@@ -3247,13 +3247,13 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0.1722925961008302</v>
+        <v>0.1855869887417801</v>
       </c>
       <c r="E109" t="n">
-        <v>0.1722925961008302</v>
+        <v>0.1855869887417801</v>
       </c>
       <c r="F109" t="n">
-        <v>0.1136704105362574</v>
+        <v>0.1220214992918274</v>
       </c>
     </row>
     <row r="110">
@@ -3273,13 +3273,13 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.3392202591308543</v>
+        <v>0.3389690394437457</v>
       </c>
       <c r="E110" t="n">
-        <v>0.3392202591308543</v>
+        <v>0.3389690394437457</v>
       </c>
       <c r="F110" t="n">
-        <v>0.2238012949497487</v>
+        <v>0.2228685894784658</v>
       </c>
     </row>
     <row r="111">
@@ -3299,13 +3299,13 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>-0.06175104805696559</v>
+        <v>-0.06249681495662485</v>
       </c>
       <c r="E111" t="n">
-        <v>0.06175104805696559</v>
+        <v>0.06249681495662485</v>
       </c>
       <c r="F111" t="n">
-        <v>0.04074038665928267</v>
+        <v>0.04109100057968926</v>
       </c>
     </row>
     <row r="112">
@@ -3325,13 +3325,13 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>-0.1391549418787722</v>
+        <v>-0.09324879037409695</v>
       </c>
       <c r="E112" t="n">
-        <v>0.1391549418787722</v>
+        <v>0.09324879037409695</v>
       </c>
       <c r="F112" t="n">
-        <v>0.09180777195006148</v>
+        <v>0.06131010199442443</v>
       </c>
     </row>
     <row r="113">
@@ -3351,13 +3351,13 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0.02677083471440832</v>
+        <v>0.03749265211505204</v>
       </c>
       <c r="E113" t="n">
-        <v>0.02677083471440832</v>
+        <v>0.03749265211505204</v>
       </c>
       <c r="F113" t="n">
-        <v>0.01766211573365701</v>
+        <v>0.02465102567007508</v>
       </c>
     </row>
     <row r="114">
@@ -3377,13 +3377,13 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>-0.1282887699375677</v>
+        <v>-0.1517249217561853</v>
       </c>
       <c r="E114" t="n">
-        <v>0.1282887699375677</v>
+        <v>0.1517249217561853</v>
       </c>
       <c r="F114" t="n">
-        <v>0.08463879166032562</v>
+        <v>0.09975754527912688</v>
       </c>
     </row>
     <row r="115">
@@ -3403,13 +3403,13 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.3485336964355674</v>
+        <v>0.3442055625915715</v>
       </c>
       <c r="E115" t="n">
-        <v>0.3485336964355674</v>
+        <v>0.3442055625915715</v>
       </c>
       <c r="F115" t="n">
-        <v>0.2299458552262152</v>
+        <v>0.2263115485452951</v>
       </c>
     </row>
     <row r="116">
@@ -3429,13 +3429,13 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.04312474956893264</v>
+        <v>0.02571571528731645</v>
       </c>
       <c r="E116" t="n">
-        <v>0.04312474956893264</v>
+        <v>0.02571571528731645</v>
       </c>
       <c r="F116" t="n">
-        <v>0.02845164620367713</v>
+        <v>0.01690781318234574</v>
       </c>
     </row>
     <row r="117">
@@ -3455,13 +3455,13 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.262898038425264</v>
+        <v>0.2898584439418284</v>
       </c>
       <c r="E117" t="n">
-        <v>0.262898038425264</v>
+        <v>0.2898584439418284</v>
       </c>
       <c r="F117" t="n">
-        <v>0.1734475458219213</v>
+        <v>0.1905788878410505</v>
       </c>
     </row>
     <row r="118">
@@ -3481,13 +3481,13 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0.1551347065603079</v>
+        <v>0.1495643180204882</v>
       </c>
       <c r="E118" t="n">
-        <v>0.1551347065603079</v>
+        <v>0.1495643180204882</v>
       </c>
       <c r="F118" t="n">
-        <v>0.1023504560393995</v>
+        <v>0.09833697097597835</v>
       </c>
     </row>
     <row r="119">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>0.2270766956747884</v>
+        <v>0.1516465108977149</v>
       </c>
       <c r="E119" t="n">
-        <v>0.2270766956747884</v>
+        <v>0.1516465108977149</v>
       </c>
       <c r="F119" t="n">
-        <v>0.1498143379618249</v>
+        <v>0.09970599096178934</v>
       </c>
     </row>
     <row r="120">
@@ -3533,13 +3533,13 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>-0.3822318553985871</v>
+        <v>-0.4036804494064006</v>
       </c>
       <c r="E120" t="n">
-        <v>0.3822318553985871</v>
+        <v>0.4036804494064006</v>
       </c>
       <c r="F120" t="n">
-        <v>0.2521782880197916</v>
+        <v>0.2654156630554704</v>
       </c>
     </row>
     <row r="121">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0.5214397614291514</v>
+        <v>0.4272768660455234</v>
       </c>
       <c r="E121" t="n">
-        <v>0.5214397614291514</v>
+        <v>0.4272768660455234</v>
       </c>
       <c r="F121" t="n">
-        <v>0.3440210031828184</v>
+        <v>0.2809300595966338</v>
       </c>
     </row>
     <row r="122">
@@ -3585,13 +3585,13 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0.5126038161327463</v>
+        <v>0.4667529919902754</v>
       </c>
       <c r="E122" t="n">
-        <v>0.5126038161327463</v>
+        <v>0.4667529919902754</v>
       </c>
       <c r="F122" t="n">
-        <v>0.338191469284969</v>
+        <v>0.3068851985138009</v>
       </c>
     </row>
     <row r="123">
@@ -3611,13 +3611,13 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>-0.1975116599540619</v>
+        <v>-0.03642751476047377</v>
       </c>
       <c r="E123" t="n">
-        <v>0.1975116599540619</v>
+        <v>0.03642751476047377</v>
       </c>
       <c r="F123" t="n">
-        <v>0.13030874210948</v>
+        <v>0.02395070902698213</v>
       </c>
     </row>
     <row r="124">
@@ -3637,13 +3637,13 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>-0.06195984287419787</v>
+        <v>-0.0748548395527892</v>
       </c>
       <c r="E124" t="n">
-        <v>0.06195984287419787</v>
+        <v>0.0748548395527892</v>
       </c>
       <c r="F124" t="n">
-        <v>0.04087813948865408</v>
+        <v>0.04921627218268596</v>
       </c>
     </row>
     <row r="125">
@@ -3663,13 +3663,13 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>-0.09217726763235919</v>
+        <v>-0.06393311559558705</v>
       </c>
       <c r="E125" t="n">
-        <v>0.09217726763235919</v>
+        <v>0.06393311559558705</v>
       </c>
       <c r="F125" t="n">
-        <v>0.06081415041043805</v>
+        <v>0.04203535319076496</v>
       </c>
     </row>
     <row r="126">
@@ -3689,13 +3689,13 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>-0.03833778901507943</v>
+        <v>-0.0177564307531734</v>
       </c>
       <c r="E126" t="n">
-        <v>0.03833778901507943</v>
+        <v>0.0177564307531734</v>
       </c>
       <c r="F126" t="n">
-        <v>0.02529343869104019</v>
+        <v>0.01167466705108494</v>
       </c>
     </row>
     <row r="127">
@@ -3715,13 +3715,13 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0.5170222960934284</v>
+        <v>0.546905417304691</v>
       </c>
       <c r="E127" t="n">
-        <v>0.5170222960934284</v>
+        <v>0.546905417304691</v>
       </c>
       <c r="F127" t="n">
-        <v>0.3411065709343923</v>
+        <v>0.3595845777916729</v>
       </c>
     </row>
     <row r="128">
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>-0.2900685041276017</v>
+        <v>-0.4152515966985876</v>
       </c>
       <c r="E128" t="n">
-        <v>0.2900685041276017</v>
+        <v>0.4152515966985876</v>
       </c>
       <c r="F128" t="n">
-        <v>0.1913733189586763</v>
+        <v>0.2730235710811981</v>
       </c>
     </row>
     <row r="129">
@@ -3767,13 +3767,13 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>-0.1369732064754696</v>
+        <v>-0.09522805993901383</v>
       </c>
       <c r="E129" t="n">
-        <v>0.1369732064754696</v>
+        <v>0.09522805993901383</v>
       </c>
       <c r="F129" t="n">
-        <v>0.09036836732915858</v>
+        <v>0.06261145098150173</v>
       </c>
     </row>
     <row r="130">
@@ -3793,13 +3793,13 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0.2776067594993097</v>
+        <v>0.2691944098947189</v>
       </c>
       <c r="E130" t="n">
-        <v>0.2776067594993097</v>
+        <v>0.2691944098947189</v>
       </c>
       <c r="F130" t="n">
-        <v>0.1831516561597307</v>
+        <v>0.1769925021092688</v>
       </c>
     </row>
     <row r="131">
@@ -3819,13 +3819,13 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>-0.03490057600408691</v>
+        <v>-0.03723218016662212</v>
       </c>
       <c r="E131" t="n">
-        <v>0.03490057600408691</v>
+        <v>0.03723218016662212</v>
       </c>
       <c r="F131" t="n">
-        <v>0.0230257300204283</v>
+        <v>0.02447976809492737</v>
       </c>
     </row>
     <row r="132">
@@ -3845,13 +3845,13 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>0.1439443037425319</v>
+        <v>0.1477223294814995</v>
       </c>
       <c r="E132" t="n">
-        <v>0.1439443037425319</v>
+        <v>0.1477223294814995</v>
       </c>
       <c r="F132" t="n">
-        <v>0.09496756373206967</v>
+        <v>0.09712588282411179</v>
       </c>
     </row>
     <row r="133">
@@ -3871,13 +3871,13 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>-0.1596479044383414</v>
+        <v>-0.06408084393959211</v>
       </c>
       <c r="E133" t="n">
-        <v>0.1596479044383414</v>
+        <v>0.06408084393959211</v>
       </c>
       <c r="F133" t="n">
-        <v>0.1053280480383453</v>
+        <v>0.04213248302807525</v>
       </c>
     </row>
     <row r="134">
@@ -3897,13 +3897,13 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>0.2647468936334678</v>
+        <v>0.2839084100904958</v>
       </c>
       <c r="E134" t="n">
-        <v>0.2647468936334678</v>
+        <v>0.2839084100904958</v>
       </c>
       <c r="F134" t="n">
-        <v>0.1746673320187445</v>
+        <v>0.1866668029675419</v>
       </c>
     </row>
     <row r="135">
@@ -3923,13 +3923,13 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>0.4233439067965399</v>
+        <v>0.4138970676015508</v>
       </c>
       <c r="E135" t="n">
-        <v>0.4233439067965399</v>
+        <v>0.4138970676015508</v>
       </c>
       <c r="F135" t="n">
-        <v>0.2793020522798537</v>
+        <v>0.2721329824015962</v>
       </c>
     </row>
     <row r="136">
@@ -3949,13 +3949,13 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>0.3339157546823794</v>
+        <v>0.3554782757549606</v>
       </c>
       <c r="E136" t="n">
-        <v>0.3339157546823794</v>
+        <v>0.3554782757549606</v>
       </c>
       <c r="F136" t="n">
-        <v>0.2203016367404274</v>
+        <v>0.2337232392603016</v>
       </c>
     </row>
     <row r="137">
@@ -3975,13 +3975,13 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>-0.2858083788561387</v>
+        <v>-0.2247404983745038</v>
       </c>
       <c r="E137" t="n">
-        <v>0.2858083788561387</v>
+        <v>0.2247404983745038</v>
       </c>
       <c r="F137" t="n">
-        <v>0.1885626921557712</v>
+        <v>0.14776452136634</v>
       </c>
     </row>
     <row r="138">
@@ -4001,13 +4001,13 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>-0.1191672382391929</v>
+        <v>-0.06958680210233111</v>
       </c>
       <c r="E138" t="n">
-        <v>0.1191672382391929</v>
+        <v>0.06958680210233111</v>
       </c>
       <c r="F138" t="n">
-        <v>0.0786208415200482</v>
+        <v>0.04575259279229085</v>
       </c>
     </row>
     <row r="139">
@@ -4027,13 +4027,13 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>-0.1980165995948731</v>
+        <v>-0.1001852099184218</v>
       </c>
       <c r="E139" t="n">
-        <v>0.1980165995948731</v>
+        <v>0.1001852099184218</v>
       </c>
       <c r="F139" t="n">
-        <v>0.1306418771226262</v>
+        <v>0.06587072511921305</v>
       </c>
     </row>
     <row r="140">
@@ -4053,13 +4053,13 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>-0.1071797840745198</v>
+        <v>-0.07341079135003283</v>
       </c>
       <c r="E140" t="n">
-        <v>0.1071797840745198</v>
+        <v>0.07341079135003283</v>
       </c>
       <c r="F140" t="n">
-        <v>0.07071209287373074</v>
+        <v>0.04826682562964571</v>
       </c>
     </row>
     <row r="141">
@@ -4079,13 +4079,13 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>0.03483248353244396</v>
+        <v>0.02732882151139761</v>
       </c>
       <c r="E141" t="n">
-        <v>0.03483248353244396</v>
+        <v>0.02732882151139761</v>
       </c>
       <c r="F141" t="n">
-        <v>0.02298080586593037</v>
+        <v>0.0179684136119008</v>
       </c>
     </row>
     <row r="142">
@@ -4105,13 +4105,13 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>-0.4826886402231795</v>
+        <v>-0.4587370159275982</v>
       </c>
       <c r="E142" t="n">
-        <v>0.4826886402231795</v>
+        <v>0.4587370159275982</v>
       </c>
       <c r="F142" t="n">
-        <v>0.3184548676905814</v>
+        <v>0.3016147782969171</v>
       </c>
     </row>
     <row r="143">
@@ -4131,13 +4131,13 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>-0.1422832071244089</v>
+        <v>-0.163596179410062</v>
       </c>
       <c r="E143" t="n">
-        <v>0.1422832071244089</v>
+        <v>0.163596179410062</v>
       </c>
       <c r="F143" t="n">
-        <v>0.09387165166854763</v>
+        <v>0.1075627727211276</v>
       </c>
     </row>
     <row r="144">
@@ -4157,13 +4157,13 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>0.5135248448984392</v>
+        <v>0.5528759862679808</v>
       </c>
       <c r="E144" t="n">
-        <v>0.5135248448984392</v>
+        <v>0.5528759862679808</v>
       </c>
       <c r="F144" t="n">
-        <v>0.3387991199924361</v>
+        <v>0.3635101642859909</v>
       </c>
     </row>
     <row r="145">
@@ -4183,13 +4183,13 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>-0.02927052199977994</v>
+        <v>-0.04553457225432403</v>
       </c>
       <c r="E145" t="n">
-        <v>0.02927052199977994</v>
+        <v>0.04553457225432403</v>
       </c>
       <c r="F145" t="n">
-        <v>0.01931128979203714</v>
+        <v>0.02993850384530665</v>
       </c>
     </row>
     <row r="146">
@@ -4209,13 +4209,13 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>-0.07867275643710443</v>
+        <v>-0.09046210178888424</v>
       </c>
       <c r="E146" t="n">
-        <v>0.07867275643710443</v>
+        <v>0.09046210178888424</v>
       </c>
       <c r="F146" t="n">
-        <v>0.05190452012802167</v>
+        <v>0.05947788346697048</v>
       </c>
     </row>
     <row r="147">
@@ -4235,13 +4235,13 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>0.2356116726742473</v>
+        <v>0.2350359737374935</v>
       </c>
       <c r="E147" t="n">
-        <v>0.2356116726742473</v>
+        <v>0.2350359737374935</v>
       </c>
       <c r="F147" t="n">
-        <v>0.15544530737898</v>
+        <v>0.1545336884735341</v>
       </c>
     </row>
     <row r="148">
@@ -4261,13 +4261,13 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>0.2192438041588358</v>
+        <v>0.2232505606271667</v>
       </c>
       <c r="E148" t="n">
-        <v>0.2192438041588358</v>
+        <v>0.2232505606271667</v>
       </c>
       <c r="F148" t="n">
-        <v>0.1446465709512029</v>
+        <v>0.1467849029188716</v>
       </c>
     </row>
     <row r="149">
@@ -4287,13 +4287,13 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>-0.445152717025487</v>
+        <v>-0.4518599429901194</v>
       </c>
       <c r="E149" t="n">
-        <v>0.445152717025487</v>
+        <v>0.4518599429901194</v>
       </c>
       <c r="F149" t="n">
-        <v>0.2936904616957809</v>
+        <v>0.2970931749439041</v>
       </c>
     </row>
     <row r="150">
@@ -4313,13 +4313,13 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>0.346852670858328</v>
+        <v>0.3598486694445974</v>
       </c>
       <c r="E150" t="n">
-        <v>0.346852670858328</v>
+        <v>0.3598486694445974</v>
       </c>
       <c r="F150" t="n">
-        <v>0.2288367949890885</v>
+        <v>0.2365967272893951</v>
       </c>
     </row>
     <row r="151">
@@ -4339,13 +4339,13 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>0.3905560084734602</v>
+        <v>0.418472159816553</v>
       </c>
       <c r="E151" t="n">
-        <v>0.3905560084734602</v>
+        <v>0.418472159816553</v>
       </c>
       <c r="F151" t="n">
-        <v>0.2576701658996381</v>
+        <v>0.2751410575649348</v>
       </c>
     </row>
     <row r="152">
@@ -4365,13 +4365,13 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>-0.2280205938802524</v>
+        <v>-0.2276065085054648</v>
       </c>
       <c r="E152" t="n">
-        <v>0.2280205938802524</v>
+        <v>0.2276065085054648</v>
       </c>
       <c r="F152" t="n">
-        <v>0.1504370768313278</v>
+        <v>0.1496488929784685</v>
       </c>
     </row>
     <row r="153">
@@ -4391,13 +4391,13 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>0.3958261415056059</v>
+        <v>0.3851152228435869</v>
       </c>
       <c r="E153" t="n">
-        <v>0.3958261415056059</v>
+        <v>0.3851152228435869</v>
       </c>
       <c r="F153" t="n">
-        <v>0.2611471474931716</v>
+        <v>0.2532092212394499</v>
       </c>
     </row>
     <row r="154">
@@ -4417,13 +4417,13 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>-0.01976679893959477</v>
+        <v>-0.01017218881433301</v>
       </c>
       <c r="E154" t="n">
-        <v>0.01976679893959477</v>
+        <v>0.01017218881433301</v>
       </c>
       <c r="F154" t="n">
-        <v>0.01304118807947179</v>
+        <v>0.006688107494062924</v>
       </c>
     </row>
     <row r="155">
@@ -4443,13 +4443,13 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>-0.2180870442213674</v>
+        <v>-0.2318938480403951</v>
       </c>
       <c r="E155" t="n">
-        <v>0.2180870442213674</v>
+        <v>0.2318938480403951</v>
       </c>
       <c r="F155" t="n">
-        <v>0.143883396096568</v>
+        <v>0.1524677737716324</v>
       </c>
     </row>
     <row r="156">
@@ -4469,13 +4469,13 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>0.1178799029148213</v>
+        <v>0.110051826057024</v>
       </c>
       <c r="E156" t="n">
-        <v>0.1178799029148213</v>
+        <v>0.110051826057024</v>
       </c>
       <c r="F156" t="n">
-        <v>0.07777151927329592</v>
+        <v>0.07235792178279117</v>
       </c>
     </row>
     <row r="157">
@@ -4495,13 +4495,13 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>-0.238294932819867</v>
+        <v>-0.2314860533486187</v>
       </c>
       <c r="E157" t="n">
-        <v>0.238294932819867</v>
+        <v>0.2314860533486187</v>
       </c>
       <c r="F157" t="n">
-        <v>0.1572155940264089</v>
+        <v>0.1521996530373548</v>
       </c>
     </row>
     <row r="158">
@@ -4521,13 +4521,13 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>0.1766380826345332</v>
+        <v>0.2081174109190554</v>
       </c>
       <c r="E158" t="n">
-        <v>0.1766380826345332</v>
+        <v>0.2081174109190554</v>
       </c>
       <c r="F158" t="n">
-        <v>0.1165373546153676</v>
+        <v>0.1368350156508547</v>
       </c>
     </row>
     <row r="159">
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>0.4728363278693481</v>
+        <v>0.4889446740813099</v>
       </c>
       <c r="E159" t="n">
-        <v>0.4728363278693481</v>
+        <v>0.4889446740813099</v>
       </c>
       <c r="F159" t="n">
-        <v>0.3119547834424107</v>
+        <v>0.3214759968176802</v>
       </c>
     </row>
     <row r="160">
@@ -4573,13 +4573,13 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>0.4017484266877598</v>
+        <v>0.4280479429164364</v>
       </c>
       <c r="E160" t="n">
-        <v>0.4017484266877598</v>
+        <v>0.4280479429164364</v>
       </c>
       <c r="F160" t="n">
-        <v>0.2650543878691553</v>
+        <v>0.2814370345548242</v>
       </c>
     </row>
     <row r="161">
@@ -4599,13 +4599,13 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>0.09334636272745357</v>
+        <v>0.1185504276495844</v>
       </c>
       <c r="E161" t="n">
-        <v>0.09334636272745357</v>
+        <v>0.1185504276495844</v>
       </c>
       <c r="F161" t="n">
-        <v>0.06158546341182514</v>
+        <v>0.07794566322543618</v>
       </c>
     </row>
     <row r="162">
@@ -4625,13 +4625,13 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>0.1084729944545469</v>
+        <v>0.098282778950882</v>
       </c>
       <c r="E162" t="n">
-        <v>0.1084729944545469</v>
+        <v>0.098282778950882</v>
       </c>
       <c r="F162" t="n">
-        <v>0.07156529120107738</v>
+        <v>0.06461989670428903</v>
       </c>
     </row>
     <row r="163">
@@ -4651,13 +4651,13 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>0.1593988864140461</v>
+        <v>0.1570134398782556</v>
       </c>
       <c r="E163" t="n">
-        <v>0.1593988864140461</v>
+        <v>0.1570134398782556</v>
       </c>
       <c r="F163" t="n">
-        <v>0.1051637578616739</v>
+        <v>0.1032346904963753</v>
       </c>
     </row>
     <row r="164">
@@ -4677,13 +4677,13 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>0.04491353994748734</v>
+        <v>0.03795262415220434</v>
       </c>
       <c r="E164" t="n">
-        <v>0.04491353994748734</v>
+        <v>0.03795262415220434</v>
       </c>
       <c r="F164" t="n">
-        <v>0.02963180450005932</v>
+        <v>0.02495345246187853</v>
       </c>
     </row>
     <row r="165">
@@ -4703,13 +4703,13 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>-0.3736815978321218</v>
+        <v>-0.4145293418468877</v>
       </c>
       <c r="E165" t="n">
-        <v>0.3736815978321218</v>
+        <v>0.4145293418468877</v>
       </c>
       <c r="F165" t="n">
-        <v>0.246537237215716</v>
+        <v>0.2725486960887608</v>
       </c>
     </row>
     <row r="166">
@@ -4729,13 +4729,13 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>0.2055435686015051</v>
+        <v>0.1945063810729359</v>
       </c>
       <c r="E166" t="n">
-        <v>0.2055435686015051</v>
+        <v>0.1945063810729359</v>
       </c>
       <c r="F166" t="n">
-        <v>0.1356078111002931</v>
+        <v>0.1278859062332751</v>
       </c>
     </row>
     <row r="167">
@@ -4755,13 +4755,13 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>0.122289215582862</v>
+        <v>0.07291447707815855</v>
       </c>
       <c r="E167" t="n">
-        <v>0.122289215582862</v>
+        <v>0.07291447707815855</v>
       </c>
       <c r="F167" t="n">
-        <v>0.08068057278169849</v>
+        <v>0.04794050419954647</v>
       </c>
     </row>
     <row r="168">
@@ -4781,13 +4781,13 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>0.1549159105124742</v>
+        <v>0.1316360708935578</v>
       </c>
       <c r="E168" t="n">
-        <v>0.1549159105124742</v>
+        <v>0.1316360708935578</v>
       </c>
       <c r="F168" t="n">
-        <v>0.102206104876646</v>
+        <v>0.08654933646057465</v>
       </c>
     </row>
     <row r="169">
@@ -4807,13 +4807,13 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>0.1630165922785029</v>
+        <v>0.2850573778205619</v>
       </c>
       <c r="E169" t="n">
-        <v>0.1630165922785029</v>
+        <v>0.2850573778205619</v>
       </c>
       <c r="F169" t="n">
-        <v>0.10755054708024</v>
+        <v>0.1874222372035899</v>
       </c>
     </row>
     <row r="170">
@@ -4833,13 +4833,13 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>0.4175375177381172</v>
+        <v>0.4592254682882603</v>
       </c>
       <c r="E170" t="n">
-        <v>0.4175375177381172</v>
+        <v>0.4592254682882603</v>
       </c>
       <c r="F170" t="n">
-        <v>0.2754712746205636</v>
+        <v>0.3019359306028234</v>
       </c>
     </row>
     <row r="171">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>0.1289008711279852</v>
+        <v>0.1239823673757614</v>
       </c>
       <c r="E171" t="n">
-        <v>0.1289008711279852</v>
+        <v>0.1239823673757614</v>
       </c>
       <c r="F171" t="n">
-        <v>0.08504262673611596</v>
+        <v>0.08151710664366617</v>
       </c>
     </row>
     <row r="172">
@@ -4885,13 +4885,13 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>0.1241768892143308</v>
+        <v>0.1059857751556901</v>
       </c>
       <c r="E172" t="n">
-        <v>0.1241768892143308</v>
+        <v>0.1059857751556901</v>
       </c>
       <c r="F172" t="n">
-        <v>0.08192596951669198</v>
+        <v>0.06968453594609347</v>
       </c>
     </row>
     <row r="173">
@@ -4911,13 +4911,13 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>-0.03416981151427625</v>
+        <v>-0.02534851852663433</v>
       </c>
       <c r="E173" t="n">
-        <v>0.03416981151427625</v>
+        <v>0.02534851852663433</v>
       </c>
       <c r="F173" t="n">
-        <v>0.02254360657785457</v>
+        <v>0.01666638516210949</v>
       </c>
     </row>
     <row r="174">
@@ -4937,13 +4937,13 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>0.2376313760575364</v>
+        <v>0.1886527592594325</v>
       </c>
       <c r="E174" t="n">
-        <v>0.2376313760575364</v>
+        <v>0.1886527592594325</v>
       </c>
       <c r="F174" t="n">
-        <v>0.1567778110264703</v>
+        <v>0.1240372112637972</v>
       </c>
     </row>
     <row r="175">
@@ -4963,13 +4963,13 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>0.1155647108566097</v>
+        <v>0.1792196117745581</v>
       </c>
       <c r="E175" t="n">
-        <v>0.1155647108566097</v>
+        <v>0.1792196117745581</v>
       </c>
       <c r="F175" t="n">
-        <v>0.07624406633751694</v>
+        <v>0.1178350156952984</v>
       </c>
     </row>
     <row r="176">
@@ -4989,13 +4989,13 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>0.2788639021465563</v>
+        <v>0.1547039884852272</v>
       </c>
       <c r="E176" t="n">
-        <v>0.2788639021465563</v>
+        <v>0.1547039884852272</v>
       </c>
       <c r="F176" t="n">
-        <v>0.1839810587228654</v>
+        <v>0.1017162504191401</v>
       </c>
     </row>
     <row r="177">
@@ -5015,13 +5015,13 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>0.0222517135780417</v>
+        <v>0.02038038646644011</v>
       </c>
       <c r="E177" t="n">
-        <v>0.0222517135780417</v>
+        <v>0.02038038646644011</v>
       </c>
       <c r="F177" t="n">
-        <v>0.01468061585229678</v>
+        <v>0.01339989042142394</v>
       </c>
     </row>
     <row r="178">
@@ -5041,13 +5041,13 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>-0.5295871836104395</v>
+        <v>-0.525156122776817</v>
       </c>
       <c r="E178" t="n">
-        <v>0.5295871836104395</v>
+        <v>0.525156122776817</v>
       </c>
       <c r="F178" t="n">
-        <v>0.3493962824758256</v>
+        <v>0.3452846446723137</v>
       </c>
     </row>
     <row r="179">
@@ -5067,13 +5067,13 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>-0.2576344514532183</v>
+        <v>-0.2620636994199434</v>
       </c>
       <c r="E179" t="n">
-        <v>0.2576344514532183</v>
+        <v>0.2620636994199434</v>
       </c>
       <c r="F179" t="n">
-        <v>0.1699748830056064</v>
+        <v>0.172304134734772</v>
       </c>
     </row>
     <row r="180">
@@ -5093,13 +5093,13 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>-0.3901617193819207</v>
+        <v>-0.3942055543532655</v>
       </c>
       <c r="E180" t="n">
-        <v>0.3901617193819207</v>
+        <v>0.3942055543532655</v>
       </c>
       <c r="F180" t="n">
-        <v>0.2574100328241631</v>
+        <v>0.2591860188985469</v>
       </c>
     </row>
     <row r="181">
@@ -5119,13 +5119,13 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>-0.2500141122253302</v>
+        <v>-0.2317505298544321</v>
       </c>
       <c r="E181" t="n">
-        <v>0.2500141122253302</v>
+        <v>0.2317505298544321</v>
       </c>
       <c r="F181" t="n">
-        <v>0.1649473478238121</v>
+        <v>0.152373543566996</v>
       </c>
     </row>
     <row r="182">
@@ -5145,13 +5145,13 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>0.1978687288535339</v>
+        <v>0.1597787326877328</v>
       </c>
       <c r="E182" t="n">
-        <v>0.1978687288535339</v>
+        <v>0.1597787326877328</v>
       </c>
       <c r="F182" t="n">
-        <v>0.1305443190832518</v>
+        <v>0.1050528415256094</v>
       </c>
     </row>
     <row r="183">
@@ -5171,13 +5171,13 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>-0.06634882451767576</v>
+        <v>-0.02230453533818379</v>
       </c>
       <c r="E183" t="n">
-        <v>0.06634882451767576</v>
+        <v>0.02230453533818379</v>
       </c>
       <c r="F183" t="n">
-        <v>0.04377377955990974</v>
+        <v>0.01466499813065843</v>
       </c>
     </row>
     <row r="184">
@@ -5197,13 +5197,13 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>-0.8156719097497791</v>
+        <v>-0.8413736209049374</v>
       </c>
       <c r="E184" t="n">
-        <v>0.8156719097497791</v>
+        <v>0.8413736209049374</v>
       </c>
       <c r="F184" t="n">
-        <v>0.538141295345562</v>
+        <v>0.5531943342766334</v>
       </c>
     </row>
     <row r="185">
@@ -5223,13 +5223,13 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>0.4428150813781882</v>
+        <v>0.4842721608136416</v>
       </c>
       <c r="E185" t="n">
-        <v>0.4428150813781882</v>
+        <v>0.4842721608136416</v>
       </c>
       <c r="F185" t="n">
-        <v>0.2921482015538701</v>
+        <v>0.3184038683336347</v>
       </c>
     </row>
     <row r="186">
@@ -5249,13 +5249,13 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>-0.2935442457697542</v>
+        <v>-0.381700941859803</v>
       </c>
       <c r="E186" t="n">
-        <v>0.2935442457697542</v>
+        <v>0.381700941859803</v>
       </c>
       <c r="F186" t="n">
-        <v>0.1936664469764944</v>
+        <v>0.2509643672899926</v>
       </c>
     </row>
     <row r="187">
@@ -5275,13 +5275,13 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>-0.09531441779033291</v>
+        <v>-0.1394314007493634</v>
       </c>
       <c r="E187" t="n">
-        <v>0.09531441779033291</v>
+        <v>0.1394314007493634</v>
       </c>
       <c r="F187" t="n">
-        <v>0.06288389196893233</v>
+        <v>0.09167468410982833</v>
       </c>
     </row>
     <row r="188">
@@ -5301,13 +5301,13 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>-0.9127330151836275</v>
+        <v>-0.9085879766343598</v>
       </c>
       <c r="E188" t="n">
-        <v>0.9127330151836275</v>
+        <v>0.9085879766343598</v>
       </c>
       <c r="F188" t="n">
-        <v>0.6021775682409551</v>
+        <v>0.597387068452895</v>
       </c>
     </row>
     <row r="189">
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>0.4657612462792803</v>
+        <v>0.4732935995802775</v>
       </c>
       <c r="E189" t="n">
-        <v>0.4657612462792803</v>
+        <v>0.4732935995802775</v>
       </c>
       <c r="F189" t="n">
-        <v>0.3072869831589332</v>
+        <v>0.3111855794285536</v>
       </c>
     </row>
     <row r="190">
@@ -5353,13 +5353,13 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>0.4934550462208951</v>
+        <v>0.4683566842294229</v>
       </c>
       <c r="E190" t="n">
-        <v>0.4934550462208951</v>
+        <v>0.4683566842294229</v>
       </c>
       <c r="F190" t="n">
-        <v>0.3255580271847024</v>
+        <v>0.307939609346964</v>
       </c>
     </row>
     <row r="191">
@@ -5379,13 +5379,13 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>0.1651915187487974</v>
+        <v>0.03822394465731709</v>
       </c>
       <c r="E191" t="n">
-        <v>0.1651915187487974</v>
+        <v>0.03822394465731709</v>
       </c>
       <c r="F191" t="n">
-        <v>0.1089854594929584</v>
+        <v>0.02513184284930238</v>
       </c>
     </row>
     <row r="192">
@@ -5405,13 +5405,13 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>-0.4637260065706528</v>
+        <v>-0.2672381366292206</v>
       </c>
       <c r="E192" t="n">
-        <v>0.4637260065706528</v>
+        <v>0.2672381366292206</v>
       </c>
       <c r="F192" t="n">
-        <v>0.3059442293874131</v>
+        <v>0.1757062729479521</v>
       </c>
     </row>
     <row r="193">
@@ -5431,13 +5431,13 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>0.4785102086747803</v>
+        <v>0.4821067862889112</v>
       </c>
       <c r="E193" t="n">
-        <v>0.4785102086747803</v>
+        <v>0.4821067862889112</v>
       </c>
       <c r="F193" t="n">
-        <v>0.3156981384970284</v>
+        <v>0.3169801572867167</v>
       </c>
     </row>
     <row r="194">
@@ -5457,13 +5457,13 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>-0.1027545573495628</v>
+        <v>-0.1179738065993413</v>
       </c>
       <c r="E194" t="n">
-        <v>0.1027545573495628</v>
+        <v>0.1179738065993413</v>
       </c>
       <c r="F194" t="n">
-        <v>0.0677925400320782</v>
+        <v>0.07756654093054406</v>
       </c>
     </row>
     <row r="195">
@@ -5483,13 +5483,13 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>0.2339641274629753</v>
+        <v>0.2368068571316543</v>
       </c>
       <c r="E195" t="n">
-        <v>0.2339641274629753</v>
+        <v>0.2368068571316543</v>
       </c>
       <c r="F195" t="n">
-        <v>0.15435833588525</v>
+        <v>0.1556980257381856</v>
       </c>
     </row>
     <row r="196">
@@ -5509,13 +5509,13 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>-0.2605529485852828</v>
+        <v>-0.2618664952192721</v>
       </c>
       <c r="E196" t="n">
-        <v>0.2605529485852828</v>
+        <v>0.2618664952192721</v>
       </c>
       <c r="F196" t="n">
-        <v>0.1719003677603692</v>
+        <v>0.1721744750404384</v>
       </c>
     </row>
     <row r="197">
@@ -5535,13 +5535,13 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>0.2579740139195111</v>
+        <v>0.2401440510543127</v>
       </c>
       <c r="E197" t="n">
-        <v>0.2579740139195111</v>
+        <v>0.2401440510543127</v>
       </c>
       <c r="F197" t="n">
-        <v>0.1701989100724666</v>
+        <v>0.1578921957531802</v>
       </c>
     </row>
     <row r="198">
@@ -5561,13 +5561,13 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>-0.5540818398462158</v>
+        <v>-0.539732384053502</v>
       </c>
       <c r="E198" t="n">
-        <v>0.5540818398462158</v>
+        <v>0.539732384053502</v>
       </c>
       <c r="F198" t="n">
-        <v>0.3655566845666718</v>
+        <v>0.3548683836354218</v>
       </c>
     </row>
     <row r="199">
@@ -5587,13 +5587,13 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>0.5391986065954352</v>
+        <v>0.4895935352797011</v>
       </c>
       <c r="E199" t="n">
-        <v>0.5391986065954352</v>
+        <v>0.4895935352797011</v>
       </c>
       <c r="F199" t="n">
-        <v>0.355737439445233</v>
+        <v>0.3219026162525704</v>
       </c>
     </row>
     <row r="200">
@@ -5613,13 +5613,13 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>-0.1121477602507695</v>
+        <v>-0.1175000914373821</v>
       </c>
       <c r="E200" t="n">
-        <v>0.1121477602507695</v>
+        <v>0.1175000914373821</v>
       </c>
       <c r="F200" t="n">
-        <v>0.07398972583224843</v>
+        <v>0.07725507817827128</v>
       </c>
     </row>
     <row r="201">
@@ -5639,13 +5639,13 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>-0.4749388789002535</v>
+        <v>-0.5023917583277082</v>
       </c>
       <c r="E201" t="n">
-        <v>0.4749388789002535</v>
+        <v>0.5023917583277082</v>
       </c>
       <c r="F201" t="n">
-        <v>0.3133419460034564</v>
+        <v>0.3303173137223477</v>
       </c>
     </row>
     <row r="202">
@@ -5665,13 +5665,13 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>0.02568030225822884</v>
+        <v>0.05821597833086833</v>
       </c>
       <c r="E202" t="n">
-        <v>0.02568030225822884</v>
+        <v>0.05821597833086833</v>
       </c>
       <c r="F202" t="n">
-        <v>0.01694263460212603</v>
+        <v>0.03827639538112674</v>
       </c>
     </row>
     <row r="203">
@@ -5691,13 +5691,13 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>-0.4284835228123413</v>
+        <v>-0.404772136517094</v>
       </c>
       <c r="E203" t="n">
-        <v>0.4284835228123413</v>
+        <v>0.404772136517094</v>
       </c>
       <c r="F203" t="n">
-        <v>0.2826929249913715</v>
+        <v>0.2661334358848454</v>
       </c>
     </row>
     <row r="204">
@@ -5717,13 +5717,13 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>0.03267165655842827</v>
+        <v>0.02360116848844033</v>
       </c>
       <c r="E204" t="n">
-        <v>0.03267165655842827</v>
+        <v>0.02360116848844033</v>
       </c>
       <c r="F204" t="n">
-        <v>0.02155519562618195</v>
+        <v>0.01551752083226834</v>
       </c>
     </row>
     <row r="205">
@@ -5743,13 +5743,13 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>0.3660767187696763</v>
+        <v>0.3671729769219678</v>
       </c>
       <c r="E205" t="n">
-        <v>0.3660767187696763</v>
+        <v>0.3671729769219678</v>
       </c>
       <c r="F205" t="n">
-        <v>0.2415199019112966</v>
+        <v>0.2414123826633102</v>
       </c>
     </row>
     <row r="206">
@@ -5769,13 +5769,13 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>0.1054532378389021</v>
+        <v>0.1308786482521234</v>
       </c>
       <c r="E206" t="n">
-        <v>0.1054532378389021</v>
+        <v>0.1308786482521234</v>
       </c>
       <c r="F206" t="n">
-        <v>0.06957300028441467</v>
+        <v>0.08605133901510724</v>
       </c>
     </row>
     <row r="207">
@@ -5795,13 +5795,13 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>0.01059117451696839</v>
+        <v>0.09730865919854739</v>
       </c>
       <c r="E207" t="n">
-        <v>0.01059117451696839</v>
+        <v>0.09730865919854739</v>
       </c>
       <c r="F207" t="n">
-        <v>0.006987550148123536</v>
+        <v>0.06397942318038786</v>
       </c>
     </row>
     <row r="208">
@@ -5821,13 +5821,13 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>-0.2903426046330607</v>
+        <v>-0.3738926992331163</v>
       </c>
       <c r="E208" t="n">
-        <v>0.2903426046330607</v>
+        <v>0.3738926992331163</v>
       </c>
       <c r="F208" t="n">
-        <v>0.1915541573561979</v>
+        <v>0.2458305296292699</v>
       </c>
     </row>
     <row r="209">
@@ -5847,13 +5847,13 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>0.5282747148179201</v>
+        <v>0.5239495232572409</v>
       </c>
       <c r="E209" t="n">
-        <v>0.5282747148179201</v>
+        <v>0.5239495232572409</v>
       </c>
       <c r="F209" t="n">
-        <v>0.3485303783694506</v>
+        <v>0.3444913181389093</v>
       </c>
     </row>
     <row r="210">
@@ -5873,13 +5873,13 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>0.138668769725259</v>
+        <v>0.1538879280807398</v>
       </c>
       <c r="E210" t="n">
-        <v>0.138668769725259</v>
+        <v>0.1538879280807398</v>
       </c>
       <c r="F210" t="n">
-        <v>0.09148701882699173</v>
+        <v>0.1011796992592589</v>
       </c>
     </row>
     <row r="211">
@@ -5899,13 +5899,13 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>-0.4866541726635998</v>
+        <v>-0.4894962628062899</v>
       </c>
       <c r="E211" t="n">
-        <v>0.4866541726635998</v>
+        <v>0.4894962628062899</v>
       </c>
       <c r="F211" t="n">
-        <v>0.3210711362401227</v>
+        <v>0.3218386606211658</v>
       </c>
     </row>
     <row r="212">
@@ -5925,13 +5925,13 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>0.1010057707741057</v>
+        <v>0.1023197212016101</v>
       </c>
       <c r="E212" t="n">
-        <v>0.1010057707741057</v>
+        <v>0.1023197212016101</v>
       </c>
       <c r="F212" t="n">
-        <v>0.06663877433075827</v>
+        <v>0.06727414390840603</v>
       </c>
     </row>
     <row r="213">
@@ -5951,13 +5951,13 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>-0.1196818108671995</v>
+        <v>-0.1018521980024393</v>
       </c>
       <c r="E213" t="n">
-        <v>0.1196818108671995</v>
+        <v>0.1018521980024393</v>
       </c>
       <c r="F213" t="n">
-        <v>0.07896033191719797</v>
+        <v>0.0669667523067464</v>
       </c>
     </row>
     <row r="214">
@@ -5977,13 +5977,13 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>0.06936591482911793</v>
+        <v>0.05501768579075674</v>
       </c>
       <c r="E214" t="n">
-        <v>0.06936591482911793</v>
+        <v>0.05501768579075674</v>
       </c>
       <c r="F214" t="n">
-        <v>0.04576431137664486</v>
+        <v>0.03617355156883083</v>
       </c>
     </row>
     <row r="215">
@@ -6003,13 +6003,13 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>-0.0625025193778741</v>
+        <v>-0.01289865451949134</v>
       </c>
       <c r="E215" t="n">
-        <v>0.0625025193778741</v>
+        <v>0.01289865451949134</v>
       </c>
       <c r="F215" t="n">
-        <v>0.04123617147817241</v>
+        <v>0.008480730109294102</v>
       </c>
     </row>
     <row r="216">
@@ -6029,13 +6029,13 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>0.008826568692098365</v>
+        <v>0.01417916137256192</v>
       </c>
       <c r="E216" t="n">
-        <v>0.008826568692098365</v>
+        <v>0.01417916137256192</v>
       </c>
       <c r="F216" t="n">
-        <v>0.005823347663007692</v>
+        <v>0.009322649939582057</v>
       </c>
     </row>
     <row r="217">
@@ -6055,13 +6055,13 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>0.1196586747961975</v>
+        <v>0.14711245339093</v>
       </c>
       <c r="E217" t="n">
-        <v>0.1196586747961975</v>
+        <v>0.14711245339093</v>
       </c>
       <c r="F217" t="n">
-        <v>0.07894506784463472</v>
+        <v>0.09672489568887105</v>
       </c>
     </row>
     <row r="218">
@@ -6081,13 +6081,13 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>-0.2723028916186313</v>
+        <v>-0.3048379435186053</v>
       </c>
       <c r="E218" t="n">
-        <v>0.2723028916186313</v>
+        <v>0.3048379435186053</v>
       </c>
       <c r="F218" t="n">
-        <v>0.1796524179273811</v>
+        <v>0.2004277517586756</v>
       </c>
     </row>
     <row r="219">
@@ -6107,13 +6107,13 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>-0.1188168835717077</v>
+        <v>-0.1425268847207828</v>
       </c>
       <c r="E219" t="n">
-        <v>0.1188168835717077</v>
+        <v>0.1425268847207828</v>
       </c>
       <c r="F219" t="n">
-        <v>0.07838969427525873</v>
+        <v>0.09370993236611611</v>
       </c>
     </row>
     <row r="220">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>0.4135516400915928</v>
+        <v>0.4226209988273133</v>
       </c>
       <c r="E220" t="n">
-        <v>0.4135516400915928</v>
+        <v>0.4226209988273133</v>
       </c>
       <c r="F220" t="n">
-        <v>0.2728415832775731</v>
+        <v>0.2778688757155799</v>
       </c>
     </row>
     <row r="221">
@@ -6159,13 +6159,13 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>-0.2024070774334519</v>
+        <v>-0.2035037498127755</v>
       </c>
       <c r="E221" t="n">
-        <v>0.2024070774334519</v>
+        <v>0.2035037498127755</v>
       </c>
       <c r="F221" t="n">
-        <v>0.133538504311815</v>
+        <v>0.1338015818458806</v>
       </c>
     </row>
     <row r="222">
@@ -6185,13 +6185,13 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>0.06152424944943009</v>
+        <v>0.0360984164389469</v>
       </c>
       <c r="E222" t="n">
-        <v>0.06152424944943009</v>
+        <v>0.0360984164389469</v>
       </c>
       <c r="F222" t="n">
-        <v>0.04059075579056835</v>
+        <v>0.02373433033104345</v>
       </c>
     </row>
     <row r="223">
@@ -6211,13 +6211,13 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>0.4927950582570122</v>
+        <v>0.406076299572067</v>
       </c>
       <c r="E223" t="n">
-        <v>0.4927950582570122</v>
+        <v>0.406076299572067</v>
       </c>
       <c r="F223" t="n">
-        <v>0.325122598707209</v>
+        <v>0.2669909094198584</v>
       </c>
     </row>
     <row r="224">
@@ -6237,13 +6237,13 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>-0.3006575256966522</v>
+        <v>-0.2171059353557528</v>
       </c>
       <c r="E224" t="n">
-        <v>0.3006575256966522</v>
+        <v>0.2171059353557528</v>
       </c>
       <c r="F224" t="n">
-        <v>0.1983594486947843</v>
+        <v>0.1427448762268733</v>
       </c>
     </row>
     <row r="225">
@@ -6263,13 +6263,13 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>0.02328289865493431</v>
+        <v>0.02760669429409818</v>
       </c>
       <c r="E225" t="n">
-        <v>0.02328289865493431</v>
+        <v>0.02760669429409818</v>
       </c>
       <c r="F225" t="n">
-        <v>0.01536094242280505</v>
+        <v>0.01815111205314062</v>
       </c>
     </row>
     <row r="226">
@@ -6289,13 +6289,13 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>-0.04879525642099163</v>
+        <v>-0.04922893582518684</v>
       </c>
       <c r="E226" t="n">
-        <v>0.04879525642099163</v>
+        <v>0.04922893582518684</v>
       </c>
       <c r="F226" t="n">
-        <v>0.03219277528530631</v>
+        <v>0.03236750915921369</v>
       </c>
     </row>
     <row r="227">
@@ -6315,13 +6315,13 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>-0.01237287969440778</v>
+        <v>-0.01268283118557977</v>
       </c>
       <c r="E227" t="n">
-        <v>0.01237287969440778</v>
+        <v>0.01268283118557977</v>
       </c>
       <c r="F227" t="n">
-        <v>0.00816303396784372</v>
+        <v>0.008338828530069207</v>
       </c>
     </row>
     <row r="228">
@@ -6341,13 +6341,13 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>-0.02048615286616465</v>
+        <v>-0.01927982796588378</v>
       </c>
       <c r="E228" t="n">
-        <v>0.02048615286616465</v>
+        <v>0.01927982796588378</v>
       </c>
       <c r="F228" t="n">
-        <v>0.01351578337842598</v>
+        <v>0.01267628474622707</v>
       </c>
     </row>
     <row r="229">
@@ -6367,13 +6367,13 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>-0.05721181326401191</v>
+        <v>-0.06386007620822982</v>
       </c>
       <c r="E229" t="n">
-        <v>0.05721181326401191</v>
+        <v>0.06386007620822982</v>
       </c>
       <c r="F229" t="n">
-        <v>0.03774561674976464</v>
+        <v>0.04198733055936656</v>
       </c>
     </row>
     <row r="230">
@@ -6393,13 +6393,13 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>-0.03151746853254632</v>
+        <v>-0.02477203500829286</v>
       </c>
       <c r="E230" t="n">
-        <v>0.03151746853254632</v>
+        <v>0.02477203500829286</v>
       </c>
       <c r="F230" t="n">
-        <v>0.02079371759574323</v>
+        <v>0.01628735329300079</v>
       </c>
     </row>
     <row r="231">
@@ -6419,13 +6419,13 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>0.1266419037833108</v>
+        <v>0.118069419708193</v>
       </c>
       <c r="E231" t="n">
-        <v>0.1266419037833108</v>
+        <v>0.118069419708193</v>
       </c>
       <c r="F231" t="n">
-        <v>0.08355226817592069</v>
+        <v>0.0776294055471486</v>
       </c>
     </row>
     <row r="232">
@@ -6445,13 +6445,13 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>0.07164883541520507</v>
+        <v>0.08388932304265405</v>
       </c>
       <c r="E232" t="n">
-        <v>0.07164883541520507</v>
+        <v>0.08388932304265405</v>
       </c>
       <c r="F232" t="n">
-        <v>0.04727047313933797</v>
+        <v>0.05515635035429968</v>
       </c>
     </row>
     <row r="233">
@@ -6471,13 +6471,13 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>-0.0382604220474245</v>
+        <v>-0.05099317639531364</v>
       </c>
       <c r="E233" t="n">
-        <v>0.0382604220474245</v>
+        <v>0.05099317639531364</v>
       </c>
       <c r="F233" t="n">
-        <v>0.02524239566786736</v>
+        <v>0.03352747883671014</v>
       </c>
     </row>
     <row r="234">
@@ -6497,13 +6497,13 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>0.156699029886527</v>
+        <v>0.1832385792395643</v>
       </c>
       <c r="E234" t="n">
-        <v>0.156699029886527</v>
+        <v>0.1832385792395643</v>
       </c>
       <c r="F234" t="n">
-        <v>0.103382521715621</v>
+        <v>0.1204774446662618</v>
       </c>
     </row>
     <row r="235">
@@ -6523,13 +6523,13 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>-0.1164793041784383</v>
+        <v>-0.1246139111219579</v>
       </c>
       <c r="E235" t="n">
-        <v>0.1164793041784383</v>
+        <v>0.1246139111219579</v>
       </c>
       <c r="F235" t="n">
-        <v>0.07684747124706469</v>
+        <v>0.08193234003530489</v>
       </c>
     </row>
     <row r="236">
@@ -6549,13 +6549,13 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>-0.003150879813793613</v>
+        <v>-0.007939022181546509</v>
       </c>
       <c r="E236" t="n">
-        <v>0.003150879813793613</v>
+        <v>0.007939022181546509</v>
       </c>
       <c r="F236" t="n">
-        <v>0.002078799728426639</v>
+        <v>0.005219823846871302</v>
       </c>
     </row>
     <row r="237">
@@ -6575,13 +6575,13 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>0.1374551550478915</v>
+        <v>0.1352866254344709</v>
       </c>
       <c r="E237" t="n">
-        <v>0.1374551550478915</v>
+        <v>0.1352866254344709</v>
       </c>
       <c r="F237" t="n">
-        <v>0.09068633393552684</v>
+        <v>0.08894953779661006</v>
       </c>
     </row>
     <row r="238">
@@ -6601,13 +6601,13 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>0.1280855125210753</v>
+        <v>0.1412941057495518</v>
       </c>
       <c r="E238" t="n">
-        <v>0.1280855125210753</v>
+        <v>0.1412941057495518</v>
       </c>
       <c r="F238" t="n">
-        <v>0.08450469214299228</v>
+        <v>0.09289939311772979</v>
       </c>
     </row>
     <row r="239">
@@ -6627,13 +6627,13 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>-0.02022698223041922</v>
+        <v>0.005075924480664711</v>
       </c>
       <c r="E239" t="n">
-        <v>0.02022698223041922</v>
+        <v>0.005075924480664711</v>
       </c>
       <c r="F239" t="n">
-        <v>0.01334479499453231</v>
+        <v>0.003337367126984172</v>
       </c>
     </row>
     <row r="240">
@@ -6653,13 +6653,13 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>0.1495862160544351</v>
+        <v>0.1034898978922679</v>
       </c>
       <c r="E240" t="n">
-        <v>0.1495862160544351</v>
+        <v>0.1034898978922679</v>
       </c>
       <c r="F240" t="n">
-        <v>0.09868982750438109</v>
+        <v>0.06804352281367558</v>
       </c>
     </row>
     <row r="241">
@@ -6679,13 +6679,13 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>0.2372053550811997</v>
+        <v>0.2361531554128026</v>
       </c>
       <c r="E241" t="n">
-        <v>0.2372053550811997</v>
+        <v>0.2361531554128026</v>
       </c>
       <c r="F241" t="n">
-        <v>0.1564967427718083</v>
+        <v>0.1552682237118435</v>
       </c>
     </row>
     <row r="242">
@@ -6705,13 +6705,13 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>0.596901219313261</v>
+        <v>0.5825765429965434</v>
       </c>
       <c r="E242" t="n">
-        <v>0.596901219313261</v>
+        <v>0.5825765429965434</v>
       </c>
       <c r="F242" t="n">
-        <v>0.3938068621893849</v>
+        <v>0.3830379689364755</v>
       </c>
     </row>
     <row r="243">
@@ -6731,13 +6731,13 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>0.1986695266352894</v>
+        <v>0.1917998084855894</v>
       </c>
       <c r="E243" t="n">
-        <v>0.1986695266352894</v>
+        <v>0.1917998084855894</v>
       </c>
       <c r="F243" t="n">
-        <v>0.1310726471406885</v>
+        <v>0.1261063631344337</v>
       </c>
     </row>
     <row r="244">
@@ -6757,13 +6757,13 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>-0.648109905623576</v>
+        <v>-0.6418398113123894</v>
       </c>
       <c r="E244" t="n">
-        <v>0.648109905623576</v>
+        <v>0.6418398113123894</v>
       </c>
       <c r="F244" t="n">
-        <v>0.4275919030306604</v>
+        <v>0.4220029465023054</v>
       </c>
     </row>
     <row r="245">
@@ -6783,13 +6783,13 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>0.03473298502174572</v>
+        <v>0.0203436657614035</v>
       </c>
       <c r="E245" t="n">
-        <v>0.03473298502174572</v>
+        <v>0.0203436657614035</v>
       </c>
       <c r="F245" t="n">
-        <v>0.02291516150967379</v>
+        <v>0.01337574694286438</v>
       </c>
     </row>
     <row r="246">
@@ -6809,13 +6809,13 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>-0.2971287808760879</v>
+        <v>-0.2868418076237865</v>
       </c>
       <c r="E246" t="n">
-        <v>0.2971287808760879</v>
+        <v>0.2868418076237865</v>
       </c>
       <c r="F246" t="n">
-        <v>0.1960313517161045</v>
+        <v>0.1885954810901721</v>
       </c>
     </row>
     <row r="247">
@@ -6835,13 +6835,13 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>-0.01927420782052985</v>
+        <v>-0.02551722471060344</v>
       </c>
       <c r="E247" t="n">
-        <v>0.01927420782052985</v>
+        <v>0.02551722471060344</v>
       </c>
       <c r="F247" t="n">
-        <v>0.01271620003008483</v>
+        <v>0.01677730770925182</v>
       </c>
     </row>
     <row r="248">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>-0.6068467813513777</v>
+        <v>-0.6130069064227306</v>
       </c>
       <c r="E248" t="n">
-        <v>0.6068467813513777</v>
+        <v>0.6130069064227306</v>
       </c>
       <c r="F248" t="n">
-        <v>0.4003684681171575</v>
+        <v>0.4030456138389149</v>
       </c>
     </row>
     <row r="249">
@@ -6887,13 +6887,13 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>-0.6750526378191108</v>
+        <v>-0.6587893007111528</v>
       </c>
       <c r="E249" t="n">
-        <v>0.6750526378191108</v>
+        <v>0.6587893007111528</v>
       </c>
       <c r="F249" t="n">
-        <v>0.4453674284969003</v>
+        <v>0.4331470580733254</v>
       </c>
     </row>
     <row r="250">
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>-0.05672152269405895</v>
+        <v>-0.06583370032670059</v>
       </c>
       <c r="E250" t="n">
-        <v>0.05672152269405895</v>
+        <v>0.06583370032670059</v>
       </c>
       <c r="F250" t="n">
-        <v>0.0374221464925982</v>
+        <v>0.0432849677245958</v>
       </c>
     </row>
     <row r="251">
@@ -6939,13 +6939,13 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>0.1648322752641109</v>
+        <v>0.1724682579963911</v>
       </c>
       <c r="E251" t="n">
-        <v>0.1648322752641109</v>
+        <v>0.1724682579963911</v>
       </c>
       <c r="F251" t="n">
-        <v>0.1087484478319181</v>
+        <v>0.1133960713714175</v>
       </c>
     </row>
     <row r="252">
@@ -6965,13 +6965,13 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>0.3499978867857373</v>
+        <v>0.3417426373229543</v>
       </c>
       <c r="E252" t="n">
-        <v>0.3499978867857373</v>
+        <v>0.3417426373229543</v>
       </c>
       <c r="F252" t="n">
-        <v>0.2309118579563014</v>
+        <v>0.2246922010039729</v>
       </c>
     </row>
     <row r="253">
@@ -6991,13 +6991,13 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>-0.6287469941713977</v>
+        <v>-0.6382412525815916</v>
       </c>
       <c r="E253" t="n">
-        <v>0.6287469941713977</v>
+        <v>0.6382412525815916</v>
       </c>
       <c r="F253" t="n">
-        <v>0.4148171805889704</v>
+        <v>0.4196369318662654</v>
       </c>
     </row>
     <row r="254">
@@ -7017,13 +7017,13 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>0.05632998825695371</v>
+        <v>0.07608702114699931</v>
       </c>
       <c r="E254" t="n">
-        <v>0.05632998825695371</v>
+        <v>0.07608702114699931</v>
       </c>
       <c r="F254" t="n">
-        <v>0.0371638308063061</v>
+        <v>0.0500264186619443</v>
       </c>
     </row>
     <row r="255">
@@ -7043,13 +7043,13 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>0.3469485357445691</v>
+        <v>0.3345796192431798</v>
       </c>
       <c r="E255" t="n">
-        <v>0.3469485357445691</v>
+        <v>0.3345796192431798</v>
       </c>
       <c r="F255" t="n">
-        <v>0.2289000420538008</v>
+        <v>0.2199825917179218</v>
       </c>
     </row>
     <row r="256">
@@ -7069,13 +7069,13 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>0.1462984179284378</v>
+        <v>0.158859872867059</v>
       </c>
       <c r="E256" t="n">
-        <v>0.1462984179284378</v>
+        <v>0.158859872867059</v>
       </c>
       <c r="F256" t="n">
-        <v>0.09652069562523907</v>
+        <v>0.1044487008273968</v>
       </c>
     </row>
     <row r="257">
@@ -7095,13 +7095,13 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>-0.0401827632435801</v>
+        <v>-0.05030154275713452</v>
       </c>
       <c r="E257" t="n">
-        <v>0.0401827632435801</v>
+        <v>0.05030154275713452</v>
       </c>
       <c r="F257" t="n">
-        <v>0.02651066440316395</v>
+        <v>0.03307273697111146</v>
       </c>
     </row>
     <row r="258">
@@ -7121,13 +7121,13 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>-0.4201588294544533</v>
+        <v>-0.4103870118830789</v>
       </c>
       <c r="E258" t="n">
-        <v>0.4201588294544533</v>
+        <v>0.4103870118830789</v>
       </c>
       <c r="F258" t="n">
-        <v>0.2772006906586448</v>
+        <v>0.2698251575682416</v>
       </c>
     </row>
     <row r="259">
@@ -7147,13 +7147,13 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>0.2556082340748427</v>
+        <v>0.2674074886526471</v>
       </c>
       <c r="E259" t="n">
-        <v>0.2556082340748427</v>
+        <v>0.2674074886526471</v>
       </c>
       <c r="F259" t="n">
-        <v>0.168638081735859</v>
+        <v>0.1758176201277663</v>
       </c>
     </row>
     <row r="260">
@@ -7173,13 +7173,13 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>0.1581741862904837</v>
+        <v>0.1585700302393579</v>
       </c>
       <c r="E260" t="n">
-        <v>0.1581741862904837</v>
+        <v>0.1585700302393579</v>
       </c>
       <c r="F260" t="n">
-        <v>0.1043557593232592</v>
+        <v>0.1042581323385681</v>
       </c>
     </row>
     <row r="261">
@@ -7199,13 +7199,13 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>-0.01351161612359391</v>
+        <v>-0.01203954149042061</v>
       </c>
       <c r="E261" t="n">
-        <v>0.01351161612359391</v>
+        <v>0.01203954149042061</v>
       </c>
       <c r="F261" t="n">
-        <v>0.008914317774156714</v>
+        <v>0.007915872300139109</v>
       </c>
     </row>
     <row r="262">
@@ -7225,13 +7225,13 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>-0.1662052243159494</v>
+        <v>-0.1788647729118825</v>
       </c>
       <c r="E262" t="n">
-        <v>0.1662052243159494</v>
+        <v>0.1788647729118825</v>
       </c>
       <c r="F262" t="n">
-        <v>0.1096542539193516</v>
+        <v>0.1176017128634338</v>
       </c>
     </row>
     <row r="263">
@@ -7251,13 +7251,13 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>0.3889513860037943</v>
+        <v>0.3828311584713447</v>
       </c>
       <c r="E263" t="n">
-        <v>0.3889513860037943</v>
+        <v>0.3828311584713447</v>
       </c>
       <c r="F263" t="n">
-        <v>0.2566115127769241</v>
+        <v>0.2517074728622088</v>
       </c>
     </row>
     <row r="264">
@@ -7277,13 +7277,13 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>-0.02655270913829695</v>
+        <v>-0.02143380932466024</v>
       </c>
       <c r="E264" t="n">
-        <v>0.02655270913829695</v>
+        <v>0.02143380932466024</v>
       </c>
       <c r="F264" t="n">
-        <v>0.01751820691606321</v>
+        <v>0.01409250490598325</v>
       </c>
     </row>
     <row r="265">
@@ -7303,13 +7303,13 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>-0.1706703178961324</v>
+        <v>-0.1793446480071106</v>
       </c>
       <c r="E265" t="n">
-        <v>0.1706703178961324</v>
+        <v>0.1793446480071106</v>
       </c>
       <c r="F265" t="n">
-        <v>0.1126001090044139</v>
+        <v>0.1179172257072464</v>
       </c>
     </row>
     <row r="266">
@@ -7329,13 +7329,13 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>0.2105769503360435</v>
+        <v>0.21698489917318</v>
       </c>
       <c r="E266" t="n">
-        <v>0.2105769503360435</v>
+        <v>0.21698489917318</v>
       </c>
       <c r="F266" t="n">
-        <v>0.138928595516449</v>
+        <v>0.142665296205848</v>
       </c>
     </row>
     <row r="267">
@@ -7355,13 +7355,13 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>0.6033472643699221</v>
+        <v>0.5983002341113028</v>
       </c>
       <c r="E267" t="n">
-        <v>0.6033472643699221</v>
+        <v>0.5983002341113028</v>
       </c>
       <c r="F267" t="n">
-        <v>0.3980596542681407</v>
+        <v>0.3933761309877713</v>
       </c>
     </row>
     <row r="268">
@@ -7381,13 +7381,13 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>-0.4305478822354777</v>
+        <v>-0.4399621992415729</v>
       </c>
       <c r="E268" t="n">
-        <v>0.4305478822354777</v>
+        <v>0.4399621992415729</v>
       </c>
       <c r="F268" t="n">
-        <v>0.2840548905571174</v>
+        <v>0.2892705331723542</v>
       </c>
     </row>
     <row r="269">
@@ -7407,13 +7407,13 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>-0.2959700261449871</v>
+        <v>-0.2819317312635837</v>
       </c>
       <c r="E269" t="n">
-        <v>0.2959700261449871</v>
+        <v>0.2819317312635837</v>
       </c>
       <c r="F269" t="n">
-        <v>0.1952668607920837</v>
+        <v>0.1853671573635399</v>
       </c>
     </row>
     <row r="270">
@@ -7433,13 +7433,13 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>0.3964473004753207</v>
+        <v>0.3876012477450489</v>
       </c>
       <c r="E270" t="n">
-        <v>0.3964473004753207</v>
+        <v>0.3876012477450489</v>
       </c>
       <c r="F270" t="n">
-        <v>0.2615569584583186</v>
+        <v>0.2548437565471772</v>
       </c>
     </row>
     <row r="271">
@@ -7459,13 +7459,13 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>-0.1735701668459845</v>
+        <v>-0.1719221016582543</v>
       </c>
       <c r="E271" t="n">
-        <v>0.1735701668459845</v>
+        <v>0.1719221016582543</v>
       </c>
       <c r="F271" t="n">
-        <v>0.1145132905808869</v>
+        <v>0.1130369793053249</v>
       </c>
     </row>
     <row r="272">
@@ -7485,13 +7485,13 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>0.172737610387383</v>
+        <v>0.1623803371690319</v>
       </c>
       <c r="E272" t="n">
-        <v>0.172737610387383</v>
+        <v>0.1623803371690319</v>
       </c>
       <c r="F272" t="n">
-        <v>0.1139640096681514</v>
+        <v>0.1067633691952735</v>
       </c>
     </row>
     <row r="273">
@@ -7511,13 +7511,13 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>0.6948675141852829</v>
+        <v>0.7001251447218866</v>
       </c>
       <c r="E273" t="n">
-        <v>0.6948675141852829</v>
+        <v>0.7001251447218866</v>
       </c>
       <c r="F273" t="n">
-        <v>0.4584403357618754</v>
+        <v>0.4603249421204701</v>
       </c>
     </row>
     <row r="274">
@@ -7537,13 +7537,13 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>-0.156935336180221</v>
+        <v>-0.1526680170642254</v>
       </c>
       <c r="E274" t="n">
-        <v>0.156935336180221</v>
+        <v>0.1526680170642254</v>
       </c>
       <c r="F274" t="n">
-        <v>0.1035384253007105</v>
+        <v>0.1003776205561834</v>
       </c>
     </row>
     <row r="275">
@@ -7563,13 +7563,13 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>0.6783215979269961</v>
+        <v>0.6781920331228741</v>
       </c>
       <c r="E275" t="n">
-        <v>0.6783215979269961</v>
+        <v>0.6781920331228741</v>
       </c>
       <c r="F275" t="n">
-        <v>0.4475241319531097</v>
+        <v>0.4459041512040864</v>
       </c>
     </row>
     <row r="276">
@@ -7589,13 +7589,13 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>-0.7927724821450397</v>
+        <v>-0.7929321817708083</v>
       </c>
       <c r="E276" t="n">
-        <v>0.7927724821450397</v>
+        <v>0.7929321817708083</v>
       </c>
       <c r="F276" t="n">
-        <v>0.5230333487722066</v>
+        <v>0.5213445959352</v>
       </c>
     </row>
     <row r="277">
@@ -7615,13 +7615,13 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>0.07527126862799974</v>
+        <v>0.07801348514202462</v>
       </c>
       <c r="E277" t="n">
-        <v>0.07527126862799974</v>
+        <v>0.07801348514202462</v>
       </c>
       <c r="F277" t="n">
-        <v>0.04966038123612913</v>
+        <v>0.05129304854046333</v>
       </c>
     </row>
     <row r="278">
@@ -7641,13 +7641,13 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>0.1249537637231955</v>
+        <v>0.1225788595923318</v>
       </c>
       <c r="E278" t="n">
-        <v>0.1249537637231955</v>
+        <v>0.1225788595923318</v>
       </c>
       <c r="F278" t="n">
-        <v>0.08243851414342751</v>
+        <v>0.08059431499128307</v>
       </c>
     </row>
     <row r="279">
@@ -7667,13 +7667,13 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>-1.04921845099177</v>
+        <v>-1.054073876377428</v>
       </c>
       <c r="E279" t="n">
-        <v>1.04921845099177</v>
+        <v>1.054073876377428</v>
       </c>
       <c r="F279" t="n">
-        <v>0.6922241278241198</v>
+        <v>0.6930425221720659</v>
       </c>
     </row>
     <row r="280">
@@ -7693,13 +7693,13 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>0.9194944319607509</v>
+        <v>0.9331571077331607</v>
       </c>
       <c r="E280" t="n">
-        <v>0.9194944319607509</v>
+        <v>0.9331571077331607</v>
       </c>
       <c r="F280" t="n">
-        <v>0.6066384274900233</v>
+        <v>0.6135410145527719</v>
       </c>
     </row>
     <row r="281">
@@ -7719,13 +7719,13 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>-0.840087293122705</v>
+        <v>-0.8575507165590375</v>
       </c>
       <c r="E281" t="n">
-        <v>0.840087293122705</v>
+        <v>0.8575507165590375</v>
       </c>
       <c r="F281" t="n">
-        <v>0.5542493969947845</v>
+        <v>0.5638306050587791</v>
       </c>
     </row>
     <row r="282">
@@ -7745,13 +7745,13 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>-0.2990827614434261</v>
+        <v>-0.3005446188938454</v>
       </c>
       <c r="E282" t="n">
-        <v>0.2990827614434261</v>
+        <v>0.3005446188938454</v>
       </c>
       <c r="F282" t="n">
-        <v>0.1973204945945322</v>
+        <v>0.1976049358317001</v>
       </c>
     </row>
     <row r="283">
@@ -7771,13 +7771,13 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>-0.3636790362227444</v>
+        <v>-0.3612057519995108</v>
       </c>
       <c r="E283" t="n">
-        <v>0.3636790362227444</v>
+        <v>0.3612057519995108</v>
       </c>
       <c r="F283" t="n">
-        <v>0.2399380256983114</v>
+        <v>0.2374889948407789</v>
       </c>
     </row>
     <row r="284">
@@ -7797,13 +7797,13 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>-0.2790540506783332</v>
+        <v>-0.2855773200554104</v>
       </c>
       <c r="E284" t="n">
-        <v>0.2790540506783332</v>
+        <v>0.2855773200554104</v>
       </c>
       <c r="F284" t="n">
-        <v>0.1841065096253366</v>
+        <v>0.1877640937716149</v>
       </c>
     </row>
     <row r="285">
@@ -7823,13 +7823,13 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>-0.6783062027552585</v>
+        <v>-0.6798465838588706</v>
       </c>
       <c r="E285" t="n">
-        <v>0.6783062027552585</v>
+        <v>0.6798465838588706</v>
       </c>
       <c r="F285" t="n">
-        <v>0.4475139749554715</v>
+        <v>0.4469920009656966</v>
       </c>
     </row>
     <row r="286">
@@ -7849,13 +7849,13 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>0.1582480331202747</v>
+        <v>0.1587525752456837</v>
       </c>
       <c r="E286" t="n">
-        <v>0.1582480331202747</v>
+        <v>0.1587525752456837</v>
       </c>
       <c r="F286" t="n">
-        <v>0.1044044799279115</v>
+        <v>0.1043781537663154</v>
       </c>
     </row>
     <row r="287">
@@ -7875,13 +7875,13 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>-0.03478134404048067</v>
+        <v>-0.03211362089558716</v>
       </c>
       <c r="E287" t="n">
-        <v>0.03478134404048067</v>
+        <v>0.03211362089558716</v>
       </c>
       <c r="F287" t="n">
-        <v>0.02294706647620824</v>
+        <v>0.0211143690402836</v>
       </c>
     </row>
     <row r="288">
@@ -7901,13 +7901,13 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>-0.262205668594487</v>
+        <v>-0.2664048313507129</v>
       </c>
       <c r="E288" t="n">
-        <v>0.262205668594487</v>
+        <v>0.2664048313507129</v>
       </c>
       <c r="F288" t="n">
-        <v>0.1729907533381556</v>
+        <v>0.1751583834642083</v>
       </c>
     </row>
     <row r="289">
@@ -7927,13 +7927,13 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>0.4402773646636987</v>
+        <v>0.4485457315671825</v>
       </c>
       <c r="E289" t="n">
-        <v>0.4402773646636987</v>
+        <v>0.4485457315671825</v>
       </c>
       <c r="F289" t="n">
-        <v>0.2904739374979038</v>
+        <v>0.294914115681514</v>
       </c>
     </row>
     <row r="290">
@@ -7953,13 +7953,13 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>-0.9445347014608363</v>
+        <v>-0.9533884165632297</v>
       </c>
       <c r="E290" t="n">
-        <v>0.9445347014608363</v>
+        <v>0.9533884165632297</v>
       </c>
       <c r="F290" t="n">
-        <v>0.6231587991045267</v>
+        <v>0.6268428879913016</v>
       </c>
     </row>
     <row r="291">
@@ -7979,13 +7979,13 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>0.3569540893211798</v>
+        <v>0.3648991310661887</v>
       </c>
       <c r="E291" t="n">
-        <v>0.3569540893211798</v>
+        <v>0.3648991310661887</v>
       </c>
       <c r="F291" t="n">
-        <v>0.2355012275280173</v>
+        <v>0.2399173528535065</v>
       </c>
     </row>
     <row r="292">
@@ -8005,13 +8005,13 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>0.06049376594486173</v>
+        <v>0.03977543220328252</v>
       </c>
       <c r="E292" t="n">
-        <v>0.06049376594486173</v>
+        <v>0.03977543220328252</v>
       </c>
       <c r="F292" t="n">
-        <v>0.03991089208390869</v>
+        <v>0.02615192964404373</v>
       </c>
     </row>
     <row r="293">
@@ -8031,13 +8031,13 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>-0.7587637820465488</v>
+        <v>-0.7617096644254592</v>
       </c>
       <c r="E293" t="n">
-        <v>0.7587637820465488</v>
+        <v>0.7617096644254592</v>
       </c>
       <c r="F293" t="n">
-        <v>0.5005960357971467</v>
+        <v>0.5008161181363311</v>
       </c>
     </row>
     <row r="294">
@@ -8057,13 +8057,13 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>0.5528492351695411</v>
+        <v>0.5647525691397292</v>
       </c>
       <c r="E294" t="n">
-        <v>0.5528492351695411</v>
+        <v>0.5647525691397292</v>
       </c>
       <c r="F294" t="n">
-        <v>0.3647434709823543</v>
+        <v>0.3713188930029093</v>
       </c>
     </row>
     <row r="295">
@@ -8083,13 +8083,13 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>-0.3909850548862743</v>
+        <v>-0.4128205501729444</v>
       </c>
       <c r="E295" t="n">
-        <v>0.3909850548862743</v>
+        <v>0.4128205501729444</v>
       </c>
       <c r="F295" t="n">
-        <v>0.2579532301925178</v>
+        <v>0.2714251834791453</v>
       </c>
     </row>
     <row r="296">
@@ -8109,13 +8109,13 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>0.3174612857822016</v>
+        <v>0.3376674121701435</v>
       </c>
       <c r="E296" t="n">
-        <v>0.3174612857822016</v>
+        <v>0.3376674121701435</v>
       </c>
       <c r="F296" t="n">
-        <v>0.2094457655226957</v>
+        <v>0.2220127831931175</v>
       </c>
     </row>
     <row r="297">
@@ -8135,13 +8135,13 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>-0.8173585364399653</v>
+        <v>-0.8266154536668053</v>
       </c>
       <c r="E297" t="n">
-        <v>0.8173585364399653</v>
+        <v>0.8266154536668053</v>
       </c>
       <c r="F297" t="n">
-        <v>0.5392540509289921</v>
+        <v>0.5434909940510856</v>
       </c>
     </row>
     <row r="298">
@@ -8161,13 +8161,13 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>0.6708164475063023</v>
+        <v>0.6643800401794061</v>
       </c>
       <c r="E298" t="n">
-        <v>0.6708164475063023</v>
+        <v>0.6643800401794061</v>
       </c>
       <c r="F298" t="n">
-        <v>0.442572592834404</v>
+        <v>0.4368229106570183</v>
       </c>
     </row>
     <row r="299">
@@ -8187,13 +8187,13 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>-0.06920538030551886</v>
+        <v>-0.04072218751056898</v>
       </c>
       <c r="E299" t="n">
-        <v>0.06920538030551886</v>
+        <v>0.04072218751056898</v>
       </c>
       <c r="F299" t="n">
-        <v>0.04565839837970986</v>
+        <v>0.02677441133223107</v>
       </c>
     </row>
     <row r="300">
@@ -8213,13 +8213,13 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>-0.7402247441739621</v>
+        <v>-0.7546872474000489</v>
       </c>
       <c r="E300" t="n">
-        <v>0.7402247441739621</v>
+        <v>0.7546872474000489</v>
       </c>
       <c r="F300" t="n">
-        <v>0.4883648657201059</v>
+        <v>0.4961989525693782</v>
       </c>
     </row>
     <row r="301">
@@ -8239,13 +8239,13 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>0.4334092634988503</v>
+        <v>0.4458371655230287</v>
       </c>
       <c r="E301" t="n">
-        <v>0.4334092634988503</v>
+        <v>0.4458371655230287</v>
       </c>
       <c r="F301" t="n">
-        <v>0.2859426929947682</v>
+        <v>0.2931332619057225</v>
       </c>
     </row>
     <row r="302">
@@ -8265,13 +8265,13 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>-0.2130734919933953</v>
+        <v>-0.2300165234865888</v>
       </c>
       <c r="E302" t="n">
-        <v>0.2130734919933953</v>
+        <v>0.2300165234865888</v>
       </c>
       <c r="F302" t="n">
-        <v>0.140575694239983</v>
+        <v>0.1512334525605073</v>
       </c>
     </row>
     <row r="303">
@@ -8291,13 +8291,13 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>0.5542097883028112</v>
+        <v>0.5694725052176993</v>
       </c>
       <c r="E303" t="n">
-        <v>0.5542097883028112</v>
+        <v>0.5694725052176993</v>
       </c>
       <c r="F303" t="n">
-        <v>0.3656410988358733</v>
+        <v>0.3744222014875189</v>
       </c>
     </row>
     <row r="304">
@@ -8317,13 +8317,13 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>0.02545232320661906</v>
+        <v>0.01929178998704062</v>
       </c>
       <c r="E304" t="n">
-        <v>0.02545232320661906</v>
+        <v>0.01929178998704062</v>
       </c>
       <c r="F304" t="n">
-        <v>0.01679222493289692</v>
+        <v>0.01268414964972065</v>
       </c>
     </row>
     <row r="305">
@@ -8343,13 +8343,13 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>0.3521001358707782</v>
+        <v>0.3437806855348041</v>
       </c>
       <c r="E305" t="n">
-        <v>0.3521001358707782</v>
+        <v>0.3437806855348041</v>
       </c>
       <c r="F305" t="n">
-        <v>0.232298821307914</v>
+        <v>0.2260321963351378</v>
       </c>
     </row>
     <row r="306">
@@ -8369,13 +8369,13 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>0.1290801342050991</v>
+        <v>0.1309604984391029</v>
       </c>
       <c r="E306" t="n">
-        <v>0.1290801342050991</v>
+        <v>0.1309604984391029</v>
       </c>
       <c r="F306" t="n">
-        <v>0.08516089593648023</v>
+        <v>0.08610515465487956</v>
       </c>
     </row>
     <row r="307">
@@ -8395,13 +8395,13 @@
         </is>
       </c>
       <c r="D307" t="n">
-        <v>0.7247091511131948</v>
+        <v>0.7312937567405906</v>
       </c>
       <c r="E307" t="n">
-        <v>0.7247091511131948</v>
+        <v>0.7312937567405906</v>
       </c>
       <c r="F307" t="n">
-        <v>0.47812841985508</v>
+        <v>0.4808179777322459</v>
       </c>
     </row>
     <row r="308">
@@ -8421,13 +8421,13 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>-0.2628462606850108</v>
+        <v>-0.2808335398590271</v>
       </c>
       <c r="E308" t="n">
-        <v>0.2628462606850108</v>
+        <v>0.2808335398590271</v>
       </c>
       <c r="F308" t="n">
-        <v>0.1734133853465183</v>
+        <v>0.1846451080291448</v>
       </c>
     </row>
     <row r="309">
@@ -8447,13 +8447,13 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>0.13821044592683</v>
+        <v>0.1485184988052038</v>
       </c>
       <c r="E309" t="n">
-        <v>0.13821044592683</v>
+        <v>0.1485184988052038</v>
       </c>
       <c r="F309" t="n">
-        <v>0.09118463871603516</v>
+        <v>0.0976493558069281</v>
       </c>
     </row>
     <row r="310">
@@ -8473,13 +8473,13 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>-0.009078314708187719</v>
+        <v>-0.02180520732452658</v>
       </c>
       <c r="E310" t="n">
-        <v>0.009078314708187719</v>
+        <v>0.02180520732452658</v>
       </c>
       <c r="F310" t="n">
-        <v>0.005989437638127675</v>
+        <v>0.01433669519693479</v>
       </c>
     </row>
     <row r="311">
@@ -8499,13 +8499,13 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>0.2669531651726454</v>
+        <v>0.271843905422841</v>
       </c>
       <c r="E311" t="n">
-        <v>0.2669531651726454</v>
+        <v>0.271843905422841</v>
       </c>
       <c r="F311" t="n">
-        <v>0.1761229244080194</v>
+        <v>0.1787345176401003</v>
       </c>
     </row>
     <row r="312">
@@ -8525,13 +8525,13 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>-0.4825654495332907</v>
+        <v>-0.4735634945225598</v>
       </c>
       <c r="E312" t="n">
-        <v>0.4825654495332907</v>
+        <v>0.4735634945225598</v>
       </c>
       <c r="F312" t="n">
-        <v>0.3183735923681891</v>
+        <v>0.3113630325233629</v>
       </c>
     </row>
     <row r="313">
@@ -8551,13 +8551,13 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>0.3886484653123254</v>
+        <v>0.3637031212395251</v>
       </c>
       <c r="E313" t="n">
-        <v>0.3886484653123254</v>
+        <v>0.3637031212395251</v>
       </c>
       <c r="F313" t="n">
-        <v>0.2564116601997476</v>
+        <v>0.2391309889321634</v>
       </c>
     </row>
     <row r="314">
@@ -8577,13 +8577,13 @@
         </is>
       </c>
       <c r="D314" t="n">
-        <v>0.4046493965693714</v>
+        <v>0.4212837427605504</v>
       </c>
       <c r="E314" t="n">
-        <v>0.4046493965693714</v>
+        <v>0.4212837427605504</v>
       </c>
       <c r="F314" t="n">
-        <v>0.2669683089827656</v>
+        <v>0.2769896438722822</v>
       </c>
     </row>
     <row r="315">
@@ -8603,13 +8603,13 @@
         </is>
       </c>
       <c r="D315" t="n">
-        <v>-0.0424465161710821</v>
+        <v>-0.04210099485403326</v>
       </c>
       <c r="E315" t="n">
-        <v>0.0424465161710821</v>
+        <v>0.04210099485403326</v>
       </c>
       <c r="F315" t="n">
-        <v>0.028004180261914</v>
+        <v>0.02768096270431126</v>
       </c>
     </row>
     <row r="316">
@@ -8629,13 +8629,13 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>-0.05791734675943368</v>
+        <v>-0.05348971689597905</v>
       </c>
       <c r="E316" t="n">
-        <v>0.05791734675943368</v>
+        <v>0.05348971689597905</v>
       </c>
       <c r="F316" t="n">
-        <v>0.03821109398956861</v>
+        <v>0.03516892804066171</v>
       </c>
     </row>
     <row r="317">
@@ -8655,13 +8655,13 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>-0.03389240205415412</v>
+        <v>-0.04734724578462336</v>
       </c>
       <c r="E317" t="n">
-        <v>0.03389240205415412</v>
+        <v>0.04734724578462336</v>
       </c>
       <c r="F317" t="n">
-        <v>0.02236058509038293</v>
+        <v>0.03113031768631618</v>
       </c>
     </row>
     <row r="318">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="D318" t="n">
-        <v>-0.5220671469701437</v>
+        <v>-0.492288536998458</v>
       </c>
       <c r="E318" t="n">
-        <v>0.5220671469701437</v>
+        <v>0.492288536998458</v>
       </c>
       <c r="F318" t="n">
-        <v>0.3444349221417467</v>
+        <v>0.32367455162663</v>
       </c>
     </row>
     <row r="319">
@@ -8707,13 +8707,13 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>0.7280288483391872</v>
+        <v>0.7335199052992791</v>
       </c>
       <c r="E319" t="n">
-        <v>0.7280288483391872</v>
+        <v>0.7335199052992791</v>
       </c>
       <c r="F319" t="n">
-        <v>0.4803185972339953</v>
+        <v>0.4822816470692998</v>
       </c>
     </row>
     <row r="320">
@@ -8733,13 +8733,13 @@
         </is>
       </c>
       <c r="D320" t="n">
-        <v>-0.9055931294549977</v>
+        <v>-0.8948264083562097</v>
       </c>
       <c r="E320" t="n">
-        <v>0.9055931294549977</v>
+        <v>0.8948264083562097</v>
       </c>
       <c r="F320" t="n">
-        <v>0.5974670132877966</v>
+        <v>0.588338981594591</v>
       </c>
     </row>
     <row r="321">
@@ -8759,13 +8759,13 @@
         </is>
       </c>
       <c r="D321" t="n">
-        <v>0.06779185523031694</v>
+        <v>0.05993450936330362</v>
       </c>
       <c r="E321" t="n">
-        <v>0.06779185523031694</v>
+        <v>0.05993450936330362</v>
       </c>
       <c r="F321" t="n">
-        <v>0.04472582217366405</v>
+        <v>0.03940631151683738</v>
       </c>
     </row>
     <row r="322">
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="D322" t="n">
-        <v>-0.3647183326646531</v>
+        <v>-0.3788394584512233</v>
       </c>
       <c r="E322" t="n">
-        <v>0.3647183326646531</v>
+        <v>0.3788394584512233</v>
       </c>
       <c r="F322" t="n">
-        <v>0.2406237037593205</v>
+        <v>0.2490829719503688</v>
       </c>
     </row>
     <row r="323">
@@ -8811,13 +8811,13 @@
         </is>
       </c>
       <c r="D323" t="n">
-        <v>0.2965973248175783</v>
+        <v>0.2787942514308042</v>
       </c>
       <c r="E323" t="n">
-        <v>0.2965973248175783</v>
+        <v>0.2787942514308042</v>
       </c>
       <c r="F323" t="n">
-        <v>0.1956807224393977</v>
+        <v>0.1833042972687177</v>
       </c>
     </row>
     <row r="324">
@@ -8837,13 +8837,13 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>-0.02080725521193721</v>
+        <v>-0.0001986012725867942</v>
       </c>
       <c r="E324" t="n">
-        <v>0.02080725521193721</v>
+        <v>0.0001986012725867942</v>
       </c>
       <c r="F324" t="n">
-        <v>0.013727631341102</v>
+        <v>0.0001305782544703252</v>
       </c>
     </row>
     <row r="325">
@@ -8863,13 +8863,13 @@
         </is>
       </c>
       <c r="D325" t="n">
-        <v>-0.2688982306742119</v>
+        <v>-0.2874507406985546</v>
       </c>
       <c r="E325" t="n">
-        <v>0.2688982306742119</v>
+        <v>0.2874507406985546</v>
       </c>
       <c r="F325" t="n">
-        <v>0.1774061855526456</v>
+        <v>0.1889958482024106</v>
       </c>
     </row>
     <row r="326">
@@ -8889,13 +8889,13 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>0.3028318879010508</v>
+        <v>0.320292550492828</v>
       </c>
       <c r="E326" t="n">
-        <v>0.3028318879010508</v>
+        <v>0.320292550492828</v>
       </c>
       <c r="F326" t="n">
-        <v>0.1997939888318651</v>
+        <v>0.2105889938088089</v>
       </c>
     </row>
     <row r="327">
@@ -8915,13 +8915,13 @@
         </is>
       </c>
       <c r="D327" t="n">
-        <v>-0.3647476650875068</v>
+        <v>-0.3820531145371741</v>
       </c>
       <c r="E327" t="n">
-        <v>0.3647476650875068</v>
+        <v>0.3820531145371741</v>
       </c>
       <c r="F327" t="n">
-        <v>0.2406430558883339</v>
+        <v>0.2511959171329733</v>
       </c>
     </row>
     <row r="328">
@@ -8941,13 +8941,13 @@
         </is>
       </c>
       <c r="D328" t="n">
-        <v>0.05925701661677226</v>
+        <v>0.05966945413025266</v>
       </c>
       <c r="E328" t="n">
-        <v>0.05925701661677226</v>
+        <v>0.05966945413025266</v>
       </c>
       <c r="F328" t="n">
-        <v>0.03909494405691338</v>
+        <v>0.03923204048010525</v>
       </c>
     </row>
     <row r="329">
@@ -8967,13 +8967,13 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>0.5525774852001094</v>
+        <v>0.5856700150974911</v>
       </c>
       <c r="E329" t="n">
-        <v>0.5525774852001094</v>
+        <v>0.5856700150974911</v>
       </c>
       <c r="F329" t="n">
-        <v>0.364564183356028</v>
+        <v>0.3850718944090218</v>
       </c>
     </row>
     <row r="330">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="D330" t="n">
-        <v>-0.5669260583928329</v>
+        <v>-0.5879753104283445</v>
       </c>
       <c r="E330" t="n">
-        <v>0.5669260583928329</v>
+        <v>0.5879753104283445</v>
       </c>
       <c r="F330" t="n">
-        <v>0.3740306853551732</v>
+        <v>0.3865876019189517</v>
       </c>
     </row>
     <row r="331">
@@ -9019,13 +9019,13 @@
         </is>
       </c>
       <c r="D331" t="n">
-        <v>0.2829109654352768</v>
+        <v>0.2900796595698654</v>
       </c>
       <c r="E331" t="n">
-        <v>0.2829109654352768</v>
+        <v>0.2900796595698654</v>
       </c>
       <c r="F331" t="n">
-        <v>0.1866511174247835</v>
+        <v>0.1907243347971268</v>
       </c>
     </row>
     <row r="332">
@@ -9045,13 +9045,13 @@
         </is>
       </c>
       <c r="D332" t="n">
-        <v>0.1815542428141183</v>
+        <v>0.1989260011361214</v>
       </c>
       <c r="E332" t="n">
-        <v>0.1815542428141183</v>
+        <v>0.1989260011361214</v>
       </c>
       <c r="F332" t="n">
-        <v>0.1197808018587326</v>
+        <v>0.1307917600868579</v>
       </c>
     </row>
     <row r="333">
@@ -9071,13 +9071,13 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>1.025888495582351</v>
+        <v>1.048891446488386</v>
       </c>
       <c r="E333" t="n">
-        <v>1.025888495582351</v>
+        <v>1.048891446488386</v>
       </c>
       <c r="F333" t="n">
-        <v>0.6768321396064182</v>
+        <v>0.689635128855741</v>
       </c>
     </row>
     <row r="334">
@@ -9097,13 +9097,13 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>-0.5558962603899275</v>
+        <v>-0.5789236225201452</v>
       </c>
       <c r="E334" t="n">
-        <v>0.5558962603899275</v>
+        <v>0.5789236225201452</v>
       </c>
       <c r="F334" t="n">
-        <v>0.3667537524195958</v>
+        <v>0.3806362120226645</v>
       </c>
     </row>
     <row r="335">
@@ -9123,13 +9123,13 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>0.4547816110700643</v>
+        <v>0.4902916663324365</v>
       </c>
       <c r="E335" t="n">
-        <v>0.4547816110700643</v>
+        <v>0.4902916663324365</v>
       </c>
       <c r="F335" t="n">
-        <v>0.3000431452342928</v>
+        <v>0.322361630100117</v>
       </c>
     </row>
     <row r="336">
@@ -9149,13 +9149,13 @@
         </is>
       </c>
       <c r="D336" t="n">
-        <v>-0.05543699835018503</v>
+        <v>-0.09271560799096468</v>
       </c>
       <c r="E336" t="n">
-        <v>0.05543699835018503</v>
+        <v>0.09271560799096468</v>
       </c>
       <c r="F336" t="n">
-        <v>0.03657467879627006</v>
+        <v>0.06095954016772056</v>
       </c>
     </row>
     <row r="337">
@@ -9175,13 +9175,13 @@
         </is>
       </c>
       <c r="D337" t="n">
-        <v>0.4269660212548875</v>
+        <v>0.4563355065640773</v>
       </c>
       <c r="E337" t="n">
-        <v>0.4269660212548875</v>
+        <v>0.4563355065640773</v>
       </c>
       <c r="F337" t="n">
-        <v>0.2816917500777134</v>
+        <v>0.3000358110692743</v>
       </c>
     </row>
     <row r="338">
@@ -9201,13 +9201,13 @@
         </is>
       </c>
       <c r="D338" t="n">
-        <v>-0.8198817943707831</v>
+        <v>-0.8272947625149999</v>
       </c>
       <c r="E338" t="n">
-        <v>0.8198817943707831</v>
+        <v>0.8272947625149999</v>
       </c>
       <c r="F338" t="n">
-        <v>0.5409187757713591</v>
+        <v>0.54393763249649</v>
       </c>
     </row>
     <row r="339">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>-0.340470771889847</v>
+        <v>-0.4044066099377567</v>
       </c>
       <c r="E339" t="n">
-        <v>0.340470771889847</v>
+        <v>0.4044066099377567</v>
       </c>
       <c r="F339" t="n">
-        <v>0.2246263234298602</v>
+        <v>0.2658931059913322</v>
       </c>
     </row>
     <row r="340">
@@ -9253,13 +9253,13 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>0.6856754240501365</v>
+        <v>0.7351751124281919</v>
       </c>
       <c r="E340" t="n">
-        <v>0.6856754240501365</v>
+        <v>0.7351751124281919</v>
       </c>
       <c r="F340" t="n">
-        <v>0.452375834541307</v>
+        <v>0.4833699284023704</v>
       </c>
     </row>
     <row r="341">
@@ -9279,13 +9279,13 @@
         </is>
       </c>
       <c r="D341" t="n">
-        <v>-0.4081382268446361</v>
+        <v>-0.4458381976878712</v>
       </c>
       <c r="E341" t="n">
-        <v>0.4081382268446361</v>
+        <v>0.4458381976878712</v>
       </c>
       <c r="F341" t="n">
-        <v>0.2692700722544072</v>
+        <v>0.2931339405432846</v>
       </c>
     </row>
     <row r="342">
@@ -9305,13 +9305,13 @@
         </is>
       </c>
       <c r="D342" t="n">
-        <v>-0.3419889650315637</v>
+        <v>-0.3522778138954611</v>
       </c>
       <c r="E342" t="n">
-        <v>0.3419889650315637</v>
+        <v>0.3522778138954611</v>
       </c>
       <c r="F342" t="n">
-        <v>0.225627954617722</v>
+        <v>0.2316189691432526</v>
       </c>
     </row>
     <row r="343">
@@ -9331,13 +9331,13 @@
         </is>
       </c>
       <c r="D343" t="n">
-        <v>0.6410075311730764</v>
+        <v>0.6285162956200602</v>
       </c>
       <c r="E343" t="n">
-        <v>0.6410075311730764</v>
+        <v>0.6285162956200602</v>
       </c>
       <c r="F343" t="n">
-        <v>0.4229060962238604</v>
+        <v>0.4132428746263711</v>
       </c>
     </row>
     <row r="344">
@@ -9357,13 +9357,13 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>-0.8509085555777485</v>
+        <v>-0.8368068613759353</v>
       </c>
       <c r="E344" t="n">
-        <v>0.8509085555777485</v>
+        <v>0.8368068613759353</v>
       </c>
       <c r="F344" t="n">
-        <v>0.5613887481545147</v>
+        <v>0.5501917377669751</v>
       </c>
     </row>
     <row r="345">
@@ -9383,13 +9383,13 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>0.2972391860735148</v>
+        <v>0.2881279807839603</v>
       </c>
       <c r="E345" t="n">
-        <v>0.2972391860735148</v>
+        <v>0.2881279807839603</v>
       </c>
       <c r="F345" t="n">
-        <v>0.196104191782369</v>
+        <v>0.1894411264579715</v>
       </c>
     </row>
     <row r="346">
@@ -9409,13 +9409,13 @@
         </is>
       </c>
       <c r="D346" t="n">
-        <v>-0.5201995361550551</v>
+        <v>-0.5126342618006335</v>
       </c>
       <c r="E346" t="n">
-        <v>0.5201995361550551</v>
+        <v>0.5126342618006335</v>
       </c>
       <c r="F346" t="n">
-        <v>0.3432027618929753</v>
+        <v>0.3370516523672138</v>
       </c>
     </row>
     <row r="347">
@@ -9435,13 +9435,13 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>0.8733135007935882</v>
+        <v>0.8651941529338374</v>
       </c>
       <c r="E347" t="n">
-        <v>0.8733135007935882</v>
+        <v>0.8651941529338374</v>
       </c>
       <c r="F347" t="n">
-        <v>0.5761704589091451</v>
+        <v>0.5688560843368143</v>
       </c>
     </row>
     <row r="348">
@@ -9461,13 +9461,13 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>-0.4005571852589871</v>
+        <v>-0.3944110719141707</v>
       </c>
       <c r="E348" t="n">
-        <v>0.4005571852589871</v>
+        <v>0.3944110719141707</v>
       </c>
       <c r="F348" t="n">
-        <v>0.2642684637765312</v>
+        <v>0.259321144540072</v>
       </c>
     </row>
     <row r="349">
@@ -9487,13 +9487,13 @@
         </is>
       </c>
       <c r="D349" t="n">
-        <v>0.2240289646621467</v>
+        <v>0.2362916288329806</v>
       </c>
       <c r="E349" t="n">
-        <v>0.2240289646621467</v>
+        <v>0.2362916288329806</v>
       </c>
       <c r="F349" t="n">
-        <v>0.1478035908766263</v>
+        <v>0.1553592685337718</v>
       </c>
     </row>
     <row r="350">
@@ -9513,13 +9513,13 @@
         </is>
       </c>
       <c r="D350" t="n">
-        <v>0.1874886931446745</v>
+        <v>0.1828888164162851</v>
       </c>
       <c r="E350" t="n">
-        <v>0.1874886931446745</v>
+        <v>0.1828888164162851</v>
       </c>
       <c r="F350" t="n">
-        <v>0.1236960682175178</v>
+        <v>0.12024747927708</v>
       </c>
     </row>
     <row r="351">
@@ -9539,13 +9539,13 @@
         </is>
       </c>
       <c r="D351" t="n">
-        <v>0.3116358400462009</v>
+        <v>0.3128494025267804</v>
       </c>
       <c r="E351" t="n">
-        <v>0.3116358400462009</v>
+        <v>0.3128494025267804</v>
       </c>
       <c r="F351" t="n">
-        <v>0.2056024151794206</v>
+        <v>0.2056952020595838</v>
       </c>
     </row>
     <row r="352">
@@ -9565,13 +9565,13 @@
         </is>
       </c>
       <c r="D352" t="n">
-        <v>-0.0663343719109053</v>
+        <v>-0.07182075387452747</v>
       </c>
       <c r="E352" t="n">
-        <v>0.0663343719109053</v>
+        <v>0.07182075387452747</v>
       </c>
       <c r="F352" t="n">
-        <v>0.04376424442153411</v>
+        <v>0.04722139266041257</v>
       </c>
     </row>
     <row r="353">
@@ -9591,13 +9591,13 @@
         </is>
       </c>
       <c r="D353" t="n">
-        <v>-0.7489897991437022</v>
+        <v>-0.737738542264883</v>
       </c>
       <c r="E353" t="n">
-        <v>0.7489897991437022</v>
+        <v>0.737738542264883</v>
       </c>
       <c r="F353" t="n">
-        <v>0.4941476295725941</v>
+        <v>0.4850553566434507</v>
       </c>
     </row>
     <row r="354">
@@ -9617,13 +9617,13 @@
         </is>
       </c>
       <c r="D354" t="n">
-        <v>0.4984453436306112</v>
+        <v>0.4950955225784409</v>
       </c>
       <c r="E354" t="n">
-        <v>0.4984453436306112</v>
+        <v>0.4950955225784409</v>
       </c>
       <c r="F354" t="n">
-        <v>0.328850386624968</v>
+        <v>0.3255201152153394</v>
       </c>
     </row>
     <row r="355">
@@ -9643,13 +9643,13 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>0.08366186973260149</v>
+        <v>0.08088732840358069</v>
       </c>
       <c r="E355" t="n">
-        <v>0.08366186973260149</v>
+        <v>0.08088732840358069</v>
       </c>
       <c r="F355" t="n">
-        <v>0.05519609834638667</v>
+        <v>0.05318257035383085</v>
       </c>
     </row>
     <row r="356">
@@ -9669,13 +9669,13 @@
         </is>
       </c>
       <c r="D356" t="n">
-        <v>0.06755675463288049</v>
+        <v>0.06880494738853815</v>
       </c>
       <c r="E356" t="n">
-        <v>0.06755675463288049</v>
+        <v>0.06880494738853815</v>
       </c>
       <c r="F356" t="n">
-        <v>0.04457071404927151</v>
+        <v>0.04523853151540824</v>
       </c>
     </row>
     <row r="357">
@@ -9695,13 +9695,13 @@
         </is>
       </c>
       <c r="D357" t="n">
-        <v>-0.674213716435348</v>
+        <v>-0.668641863365957</v>
       </c>
       <c r="E357" t="n">
-        <v>0.674213716435348</v>
+        <v>0.668641863365957</v>
       </c>
       <c r="F357" t="n">
-        <v>0.4448139483111112</v>
+        <v>0.4396250147186516</v>
       </c>
     </row>
     <row r="358">
@@ -9721,13 +9721,13 @@
         </is>
       </c>
       <c r="D358" t="n">
-        <v>0.9106854781005793</v>
+        <v>0.9098475701240529</v>
       </c>
       <c r="E358" t="n">
-        <v>0.9106854781005793</v>
+        <v>0.9098475701240529</v>
       </c>
       <c r="F358" t="n">
-        <v>0.6008267012502339</v>
+        <v>0.5982152379660307</v>
       </c>
     </row>
     <row r="359">
@@ -9747,13 +9747,13 @@
         </is>
       </c>
       <c r="D359" t="n">
-        <v>0.7458783541380288</v>
+        <v>0.7465966486444009</v>
       </c>
       <c r="E359" t="n">
-        <v>0.7458783541380288</v>
+        <v>0.7465966486444009</v>
       </c>
       <c r="F359" t="n">
-        <v>0.4920948470435705</v>
+        <v>0.4908794687142553</v>
       </c>
     </row>
     <row r="360">
@@ -9773,13 +9773,13 @@
         </is>
       </c>
       <c r="D360" t="n">
-        <v>-0.4968750054625379</v>
+        <v>-0.5022153731988492</v>
       </c>
       <c r="E360" t="n">
-        <v>0.4968750054625379</v>
+        <v>0.5022153731988492</v>
       </c>
       <c r="F360" t="n">
-        <v>0.3278143526439072</v>
+        <v>0.330201342349451</v>
       </c>
     </row>
     <row r="361">
@@ -9799,13 +9799,13 @@
         </is>
       </c>
       <c r="D361" t="n">
-        <v>0.1677345596559753</v>
+        <v>0.1708629208044312</v>
       </c>
       <c r="E361" t="n">
-        <v>0.1677345596559753</v>
+        <v>0.1708629208044312</v>
       </c>
       <c r="F361" t="n">
-        <v>0.1106632361964926</v>
+        <v>0.112340578999027</v>
       </c>
     </row>
     <row r="362">
@@ -9825,13 +9825,13 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>-0.1741153140677844</v>
+        <v>-0.161127584634814</v>
       </c>
       <c r="E362" t="n">
-        <v>0.1741153140677844</v>
+        <v>0.161127584634814</v>
       </c>
       <c r="F362" t="n">
-        <v>0.1148729526319969</v>
+        <v>0.1059396975386381</v>
       </c>
     </row>
     <row r="363">
@@ -9851,13 +9851,13 @@
         </is>
       </c>
       <c r="D363" t="n">
-        <v>-0.8266892085829823</v>
+        <v>-0.8368431653156209</v>
       </c>
       <c r="E363" t="n">
-        <v>0.8266892085829823</v>
+        <v>0.8368431653156209</v>
       </c>
       <c r="F363" t="n">
-        <v>0.5454099819270675</v>
+        <v>0.5502156072266859</v>
       </c>
     </row>
     <row r="364">
@@ -9877,13 +9877,13 @@
         </is>
       </c>
       <c r="D364" t="n">
-        <v>0.3687113823677003</v>
+        <v>0.3815708597211129</v>
       </c>
       <c r="E364" t="n">
-        <v>0.3687113823677003</v>
+        <v>0.3815708597211129</v>
       </c>
       <c r="F364" t="n">
-        <v>0.2432581268820148</v>
+        <v>0.2508788396476634</v>
       </c>
     </row>
     <row r="365">
@@ -9903,13 +9903,13 @@
         </is>
       </c>
       <c r="D365" t="n">
-        <v>-0.4359928034581432</v>
+        <v>-0.42487238958823</v>
       </c>
       <c r="E365" t="n">
-        <v>0.4359928034581432</v>
+        <v>0.42487238958823</v>
       </c>
       <c r="F365" t="n">
-        <v>0.2876471890349682</v>
+        <v>0.2793491415359444</v>
       </c>
     </row>
     <row r="366">
@@ -9929,13 +9929,13 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>0.62772391350881</v>
+        <v>0.6202573068540167</v>
       </c>
       <c r="E366" t="n">
-        <v>0.62772391350881</v>
+        <v>0.6202573068540167</v>
       </c>
       <c r="F366" t="n">
-        <v>0.4141422009232162</v>
+        <v>0.4078126761049157</v>
       </c>
     </row>
     <row r="367">
@@ -9955,13 +9955,13 @@
         </is>
       </c>
       <c r="D367" t="n">
-        <v>-0.09436591551484877</v>
+        <v>-0.1015613575043006</v>
       </c>
       <c r="E367" t="n">
-        <v>0.09436591551484877</v>
+        <v>0.1015613575043006</v>
       </c>
       <c r="F367" t="n">
-        <v>0.06225811555433958</v>
+        <v>0.06677552772856729</v>
       </c>
     </row>
     <row r="368">
@@ -9981,13 +9981,13 @@
         </is>
       </c>
       <c r="D368" t="n">
-        <v>0.6283814711032356</v>
+        <v>0.6482501782730576</v>
       </c>
       <c r="E368" t="n">
-        <v>0.6283814711032356</v>
+        <v>0.6482501782730576</v>
       </c>
       <c r="F368" t="n">
-        <v>0.4145760259592373</v>
+        <v>0.4262176955687923</v>
       </c>
     </row>
     <row r="369">
@@ -10007,13 +10007,13 @@
         </is>
       </c>
       <c r="D369" t="n">
-        <v>0.8760925574103519</v>
+        <v>0.8641840722926806</v>
       </c>
       <c r="E369" t="n">
-        <v>0.8760925574103519</v>
+        <v>0.8641840722926806</v>
       </c>
       <c r="F369" t="n">
-        <v>0.578003947484279</v>
+        <v>0.5681919669055483</v>
       </c>
     </row>
     <row r="370">
@@ -10033,13 +10033,13 @@
         </is>
       </c>
       <c r="D370" t="n">
-        <v>-0.4486046067141558</v>
+        <v>-0.4383756731062669</v>
       </c>
       <c r="E370" t="n">
-        <v>0.4486046067141558</v>
+        <v>0.4383756731062669</v>
       </c>
       <c r="F370" t="n">
-        <v>0.2959678533360301</v>
+        <v>0.2882274088724872</v>
       </c>
     </row>
     <row r="371">
@@ -10059,13 +10059,13 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>-0.02838093508102383</v>
+        <v>-0.04980191284886384</v>
       </c>
       <c r="E371" t="n">
-        <v>0.02838093508102383</v>
+        <v>0.04980191284886384</v>
       </c>
       <c r="F371" t="n">
-        <v>0.01872438291065546</v>
+        <v>0.03274423554484471</v>
       </c>
     </row>
     <row r="372">
@@ -10085,13 +10085,13 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>-0.5288378713619593</v>
+        <v>-0.5248237630492567</v>
       </c>
       <c r="E372" t="n">
-        <v>0.5288378713619593</v>
+        <v>0.5248237630492567</v>
       </c>
       <c r="F372" t="n">
-        <v>0.3489019221096102</v>
+        <v>0.3450661216361026</v>
       </c>
     </row>
     <row r="373">
@@ -10111,13 +10111,13 @@
         </is>
       </c>
       <c r="D373" t="n">
-        <v>-0.08066789159438224</v>
+        <v>-0.08885998911256272</v>
       </c>
       <c r="E373" t="n">
-        <v>0.08066789159438224</v>
+        <v>0.08885998911256272</v>
       </c>
       <c r="F373" t="n">
-        <v>0.05322081483560368</v>
+        <v>0.05842451117980441</v>
       </c>
     </row>
     <row r="374">
@@ -10137,13 +10137,13 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>-0.3929188802469179</v>
+        <v>-0.3873371165459391</v>
       </c>
       <c r="E374" t="n">
-        <v>0.3929188802469179</v>
+        <v>0.3873371165459391</v>
       </c>
       <c r="F374" t="n">
-        <v>0.2592290756300149</v>
+        <v>0.2546700930530732</v>
       </c>
     </row>
     <row r="375">
@@ -10163,13 +10163,13 @@
         </is>
       </c>
       <c r="D375" t="n">
-        <v>-0.731790627170597</v>
+        <v>-0.7295232843758362</v>
       </c>
       <c r="E375" t="n">
-        <v>0.731790627170597</v>
+        <v>0.7295232843758362</v>
       </c>
       <c r="F375" t="n">
-        <v>0.482800438902123</v>
+        <v>0.4796539107151198</v>
       </c>
     </row>
     <row r="376">
@@ -10189,13 +10189,13 @@
         </is>
       </c>
       <c r="D376" t="n">
-        <v>0.3590496919574185</v>
+        <v>0.357986599858585</v>
       </c>
       <c r="E376" t="n">
-        <v>0.3590496919574185</v>
+        <v>0.357986599858585</v>
       </c>
       <c r="F376" t="n">
-        <v>0.2368838058707495</v>
+        <v>0.2353724360596522</v>
       </c>
     </row>
     <row r="377">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="D377" t="n">
-        <v>-0.1537693404226911</v>
+        <v>-0.1547343484669264</v>
       </c>
       <c r="E377" t="n">
-        <v>0.1537693404226911</v>
+        <v>0.1547343484669264</v>
       </c>
       <c r="F377" t="n">
-        <v>0.1014496527959195</v>
+        <v>0.1017362117887949</v>
       </c>
     </row>
     <row r="378">
@@ -10241,13 +10241,13 @@
         </is>
       </c>
       <c r="D378" t="n">
-        <v>-0.09641165775068557</v>
+        <v>-0.08916872810979147</v>
       </c>
       <c r="E378" t="n">
-        <v>0.09641165775068557</v>
+        <v>0.08916872810979147</v>
       </c>
       <c r="F378" t="n">
-        <v>0.06360779839075606</v>
+        <v>0.0586275038334765</v>
       </c>
     </row>
     <row r="379">
@@ -10267,13 +10267,13 @@
         </is>
       </c>
       <c r="D379" t="n">
-        <v>0.1389739666384264</v>
+        <v>0.1341118737473864</v>
       </c>
       <c r="E379" t="n">
-        <v>0.1389739666384264</v>
+        <v>0.1341118737473864</v>
       </c>
       <c r="F379" t="n">
-        <v>0.09168837314632554</v>
+        <v>0.08817715087915702</v>
       </c>
     </row>
     <row r="380">
@@ -10293,13 +10293,13 @@
         </is>
       </c>
       <c r="D380" t="n">
-        <v>-0.1978506562620183</v>
+        <v>-0.181447914241513</v>
       </c>
       <c r="E380" t="n">
-        <v>0.1978506562620183</v>
+        <v>0.181447914241513</v>
       </c>
       <c r="F380" t="n">
-        <v>0.1305323956521612</v>
+        <v>0.1193001012044546</v>
       </c>
     </row>
     <row r="381">
@@ -10319,13 +10319,13 @@
         </is>
       </c>
       <c r="D381" t="n">
-        <v>0.1757423327222917</v>
+        <v>0.1652381479867619</v>
       </c>
       <c r="E381" t="n">
-        <v>0.1757423327222917</v>
+        <v>0.1652381479867619</v>
       </c>
       <c r="F381" t="n">
-        <v>0.1159463816857896</v>
+        <v>0.1086423498449192</v>
       </c>
     </row>
     <row r="382">
@@ -10345,13 +10345,13 @@
         </is>
       </c>
       <c r="D382" t="n">
-        <v>-0.3768192114640509</v>
+        <v>-0.3894088493489324</v>
       </c>
       <c r="E382" t="n">
-        <v>0.3768192114640509</v>
+        <v>0.3894088493489324</v>
       </c>
       <c r="F382" t="n">
-        <v>0.2486072845521483</v>
+        <v>0.2560322356497454</v>
       </c>
     </row>
     <row r="383">
@@ -10371,13 +10371,13 @@
         </is>
       </c>
       <c r="D383" t="n">
-        <v>0.1657673544880664</v>
+        <v>0.1522729150503496</v>
       </c>
       <c r="E383" t="n">
-        <v>0.1657673544880664</v>
+        <v>0.1522729150503496</v>
       </c>
       <c r="F383" t="n">
-        <v>0.1093653683594186</v>
+        <v>0.1001178451245478</v>
       </c>
     </row>
     <row r="384">
@@ -10397,13 +10397,13 @@
         </is>
       </c>
       <c r="D384" t="n">
-        <v>0.1475834424198134</v>
+        <v>0.1615321914440206</v>
       </c>
       <c r="E384" t="n">
-        <v>0.1475834424198134</v>
+        <v>0.1615321914440206</v>
       </c>
       <c r="F384" t="n">
-        <v>0.09736849329495631</v>
+        <v>0.1062057222735497</v>
       </c>
     </row>
     <row r="385">
@@ -10423,13 +10423,13 @@
         </is>
       </c>
       <c r="D385" t="n">
-        <v>-0.5377548191126125</v>
+        <v>-0.5606056231460174</v>
       </c>
       <c r="E385" t="n">
-        <v>0.5377548191126125</v>
+        <v>0.5606056231460174</v>
       </c>
       <c r="F385" t="n">
-        <v>0.3547848975507251</v>
+        <v>0.3685923194911261</v>
       </c>
     </row>
     <row r="386">
@@ -10449,13 +10449,13 @@
         </is>
       </c>
       <c r="D386" t="n">
-        <v>0.3511575955005061</v>
+        <v>0.3713397681741735</v>
       </c>
       <c r="E386" t="n">
-        <v>0.3511575955005061</v>
+        <v>0.3713397681741735</v>
       </c>
       <c r="F386" t="n">
-        <v>0.2316769782730972</v>
+        <v>0.2441520042244836</v>
       </c>
     </row>
     <row r="387">
@@ -10475,13 +10475,13 @@
         </is>
       </c>
       <c r="D387" t="n">
-        <v>0.03308343132924955</v>
+        <v>0.01682423921723583</v>
       </c>
       <c r="E387" t="n">
-        <v>0.03308343132924955</v>
+        <v>0.01682423921723583</v>
       </c>
       <c r="F387" t="n">
-        <v>0.02182686491613992</v>
+        <v>0.01106176088986413</v>
       </c>
     </row>
     <row r="388">
@@ -10501,13 +10501,13 @@
         </is>
       </c>
       <c r="D388" t="n">
-        <v>0.2853778172201071</v>
+        <v>0.2996399297646435</v>
       </c>
       <c r="E388" t="n">
-        <v>0.2853778172201071</v>
+        <v>0.2996399297646435</v>
       </c>
       <c r="F388" t="n">
-        <v>0.1882786281911176</v>
+        <v>0.1970101122145562</v>
       </c>
     </row>
     <row r="389">
@@ -10527,13 +10527,13 @@
         </is>
       </c>
       <c r="D389" t="n">
-        <v>0.6081514436725416</v>
+        <v>0.6416566157517853</v>
       </c>
       <c r="E389" t="n">
-        <v>0.6081514436725416</v>
+        <v>0.6416566157517853</v>
       </c>
       <c r="F389" t="n">
-        <v>0.4012292218872794</v>
+        <v>0.4218824973419409</v>
       </c>
     </row>
     <row r="390">
@@ -10553,13 +10553,13 @@
         </is>
       </c>
       <c r="D390" t="n">
-        <v>-0.7207833387812445</v>
+        <v>-0.7353581902138074</v>
       </c>
       <c r="E390" t="n">
-        <v>0.7207833387812445</v>
+        <v>0.7353581902138074</v>
       </c>
       <c r="F390" t="n">
-        <v>0.4755383567324607</v>
+        <v>0.4834903001269148</v>
       </c>
     </row>
     <row r="391">
@@ -10579,13 +10579,13 @@
         </is>
       </c>
       <c r="D391" t="n">
-        <v>0.7046154400860372</v>
+        <v>0.7228009440726622</v>
       </c>
       <c r="E391" t="n">
-        <v>0.7046154400860372</v>
+        <v>0.7228009440726622</v>
       </c>
       <c r="F391" t="n">
-        <v>0.4648715508233008</v>
+        <v>0.4752340424468519</v>
       </c>
     </row>
     <row r="392">
@@ -10605,13 +10605,13 @@
         </is>
       </c>
       <c r="D392" t="n">
-        <v>0.4442243582876745</v>
+        <v>0.4313883875473395</v>
       </c>
       <c r="E392" t="n">
-        <v>0.4442243582876745</v>
+        <v>0.4313883875473395</v>
       </c>
       <c r="F392" t="n">
-        <v>0.2930779750234557</v>
+        <v>0.2836333418764073</v>
       </c>
     </row>
     <row r="393">
@@ -10631,13 +10631,13 @@
         </is>
       </c>
       <c r="D393" t="n">
-        <v>-1.185064531678151</v>
+        <v>-1.157812242322138</v>
       </c>
       <c r="E393" t="n">
-        <v>1.185064531678151</v>
+        <v>1.157812242322138</v>
       </c>
       <c r="F393" t="n">
-        <v>0.7818488714917214</v>
+        <v>0.7612494101251334</v>
       </c>
     </row>
     <row r="394">
@@ -10657,13 +10657,13 @@
         </is>
       </c>
       <c r="D394" t="n">
-        <v>1.122791611843444</v>
+        <v>1.108472371139465</v>
       </c>
       <c r="E394" t="n">
-        <v>1.122791611843444</v>
+        <v>1.108472371139465</v>
       </c>
       <c r="F394" t="n">
-        <v>0.7407641788055653</v>
+        <v>0.728808962131486</v>
       </c>
     </row>
     <row r="395">
@@ -10683,13 +10683,13 @@
         </is>
       </c>
       <c r="D395" t="n">
-        <v>-0.218749079183552</v>
+        <v>-0.2244426632039557</v>
       </c>
       <c r="E395" t="n">
-        <v>0.218749079183552</v>
+        <v>0.2244426632039557</v>
       </c>
       <c r="F395" t="n">
-        <v>0.1443201750855899</v>
+        <v>0.1475686978643881</v>
       </c>
     </row>
     <row r="396">
@@ -10709,13 +10709,13 @@
         </is>
       </c>
       <c r="D396" t="n">
-        <v>0.5021269891812099</v>
+        <v>0.5042797621158419</v>
       </c>
       <c r="E396" t="n">
-        <v>0.5021269891812099</v>
+        <v>0.5042797621158419</v>
       </c>
       <c r="F396" t="n">
-        <v>0.3312793601888734</v>
+        <v>0.3315586564180755</v>
       </c>
     </row>
     <row r="397">
@@ -10735,13 +10735,13 @@
         </is>
       </c>
       <c r="D397" t="n">
-        <v>-0.8555266877073319</v>
+        <v>-0.8421072112639583</v>
       </c>
       <c r="E397" t="n">
-        <v>0.8555266877073319</v>
+        <v>0.8421072112639583</v>
       </c>
       <c r="F397" t="n">
-        <v>0.5644355707514254</v>
+        <v>0.553676662246286</v>
       </c>
     </row>
     <row r="398">
@@ -10761,13 +10761,13 @@
         </is>
       </c>
       <c r="D398" t="n">
-        <v>0.5956284074703451</v>
+        <v>0.5761862095989854</v>
       </c>
       <c r="E398" t="n">
-        <v>0.5956284074703451</v>
+        <v>0.5761862095989854</v>
       </c>
       <c r="F398" t="n">
-        <v>0.3929671218407341</v>
+        <v>0.3788363917276896</v>
       </c>
     </row>
     <row r="399">
@@ -10787,13 +10787,13 @@
         </is>
       </c>
       <c r="D399" t="n">
-        <v>0.8239792416519895</v>
+        <v>0.8297189965596554</v>
       </c>
       <c r="E399" t="n">
-        <v>0.8239792416519895</v>
+        <v>0.8297189965596554</v>
       </c>
       <c r="F399" t="n">
-        <v>0.5436220754205954</v>
+        <v>0.5455315409637196</v>
       </c>
     </row>
     <row r="400">
@@ -10813,13 +10813,13 @@
         </is>
       </c>
       <c r="D400" t="n">
-        <v>-0.2004715850873052</v>
+        <v>-0.2120328469123784</v>
       </c>
       <c r="E400" t="n">
-        <v>0.2004715850873052</v>
+        <v>0.2120328469123784</v>
       </c>
       <c r="F400" t="n">
-        <v>0.1322615590770499</v>
+        <v>0.1394093737646728</v>
       </c>
     </row>
     <row r="401">
@@ -10839,13 +10839,13 @@
         </is>
       </c>
       <c r="D401" t="n">
-        <v>0.2739592929023418</v>
+        <v>0.2805427115691585</v>
       </c>
       <c r="E401" t="n">
-        <v>0.2739592929023418</v>
+        <v>0.2805427115691585</v>
       </c>
       <c r="F401" t="n">
-        <v>0.1807452322339342</v>
+        <v>0.1844538914777754</v>
       </c>
     </row>
     <row r="402">
@@ -10865,13 +10865,13 @@
         </is>
       </c>
       <c r="D402" t="n">
-        <v>0.2996442891363075</v>
+        <v>0.2897848056793618</v>
       </c>
       <c r="E402" t="n">
-        <v>0.2996442891363075</v>
+        <v>0.2897848056793618</v>
       </c>
       <c r="F402" t="n">
-        <v>0.19769096369664</v>
+        <v>0.1905304714555467</v>
       </c>
     </row>
     <row r="403">
@@ -10891,13 +10891,13 @@
         </is>
       </c>
       <c r="D403" t="n">
-        <v>0.03770074149594446</v>
+        <v>0.02794463485010942</v>
       </c>
       <c r="E403" t="n">
-        <v>0.03770074149594446</v>
+        <v>0.02794463485010942</v>
       </c>
       <c r="F403" t="n">
-        <v>0.02487314522126858</v>
+        <v>0.01837330442554546</v>
       </c>
     </row>
     <row r="404">
@@ -10917,13 +10917,13 @@
         </is>
       </c>
       <c r="D404" t="n">
-        <v>-0.07000679658455129</v>
+        <v>-0.05627450355366253</v>
       </c>
       <c r="E404" t="n">
-        <v>0.07000679658455129</v>
+        <v>0.05627450355366253</v>
       </c>
       <c r="F404" t="n">
-        <v>0.04618713449205415</v>
+        <v>0.03699989607070613</v>
       </c>
     </row>
     <row r="405">
@@ -10943,13 +10943,13 @@
         </is>
       </c>
       <c r="D405" t="n">
-        <v>-0.1217547478795251</v>
+        <v>-0.1294612086974898</v>
       </c>
       <c r="E405" t="n">
-        <v>0.1217547478795251</v>
+        <v>0.1294612086974898</v>
       </c>
       <c r="F405" t="n">
-        <v>0.08032795656584481</v>
+        <v>0.0851193873692266</v>
       </c>
     </row>
     <row r="406">
@@ -10969,13 +10969,13 @@
         </is>
       </c>
       <c r="D406" t="n">
-        <v>0.04534502800860517</v>
+        <v>0.05246916999820841</v>
       </c>
       <c r="E406" t="n">
-        <v>0.04534502800860517</v>
+        <v>0.05246916999820841</v>
       </c>
       <c r="F406" t="n">
-        <v>0.02991647967565453</v>
+        <v>0.03449792915540655</v>
       </c>
     </row>
     <row r="407">
@@ -10995,13 +10995,13 @@
         </is>
       </c>
       <c r="D407" t="n">
-        <v>0.03615685052651104</v>
+        <v>0.02825344251890387</v>
       </c>
       <c r="E407" t="n">
-        <v>0.03615685052651104</v>
+        <v>0.02825344251890387</v>
       </c>
       <c r="F407" t="n">
-        <v>0.02385455983634575</v>
+        <v>0.018576342230052</v>
       </c>
     </row>
     <row r="408">
@@ -11021,13 +11021,13 @@
         </is>
       </c>
       <c r="D408" t="n">
-        <v>0.1360495013009898</v>
+        <v>0.1408635691441511</v>
       </c>
       <c r="E408" t="n">
-        <v>0.1360495013009898</v>
+        <v>0.1408635691441511</v>
       </c>
       <c r="F408" t="n">
-        <v>0.08975895085524266</v>
+        <v>0.09261631981368422</v>
       </c>
     </row>
     <row r="409">
@@ -11047,13 +11047,13 @@
         </is>
       </c>
       <c r="D409" t="n">
-        <v>0.01331556895149652</v>
+        <v>0.02407880492287518</v>
       </c>
       <c r="E409" t="n">
-        <v>0.01331556895149652</v>
+        <v>0.02407880492287518</v>
       </c>
       <c r="F409" t="n">
-        <v>0.008784975231057876</v>
+        <v>0.01583156178008087</v>
       </c>
     </row>
     <row r="410">
@@ -11073,13 +11073,13 @@
         </is>
       </c>
       <c r="D410" t="n">
-        <v>-0.08529699245071584</v>
+        <v>-0.08851778317314736</v>
       </c>
       <c r="E410" t="n">
-        <v>0.08529699245071584</v>
+        <v>0.08851778317314736</v>
       </c>
       <c r="F410" t="n">
-        <v>0.05627487407355979</v>
+        <v>0.05819951436253221</v>
       </c>
     </row>
     <row r="411">
@@ -11099,13 +11099,13 @@
         </is>
       </c>
       <c r="D411" t="n">
-        <v>-0.07010989165539959</v>
+        <v>-0.07721689724950877</v>
       </c>
       <c r="E411" t="n">
-        <v>0.07010989165539959</v>
+        <v>0.07721689724950877</v>
       </c>
       <c r="F411" t="n">
-        <v>0.04625515168659878</v>
+        <v>0.05076930035304194</v>
       </c>
     </row>
     <row r="412">
@@ -11125,13 +11125,13 @@
         </is>
       </c>
       <c r="D412" t="n">
-        <v>0.5821548882060108</v>
+        <v>0.5698755940984788</v>
       </c>
       <c r="E412" t="n">
-        <v>0.5821548882060108</v>
+        <v>0.5698755940984788</v>
       </c>
       <c r="F412" t="n">
-        <v>0.3840779385513445</v>
+        <v>0.3746872282004045</v>
       </c>
     </row>
     <row r="413">
@@ -11151,13 +11151,13 @@
         </is>
       </c>
       <c r="D413" t="n">
-        <v>-1.026079677913036</v>
+        <v>-1.011700750205004</v>
       </c>
       <c r="E413" t="n">
-        <v>1.026079677913036</v>
+        <v>1.011700750205004</v>
       </c>
       <c r="F413" t="n">
-        <v>0.6769582725599407</v>
+        <v>0.6651826359791015</v>
       </c>
     </row>
     <row r="414">
@@ -11177,13 +11177,13 @@
         </is>
       </c>
       <c r="D414" t="n">
-        <v>0.2582792660729253</v>
+        <v>0.2561801023173781</v>
       </c>
       <c r="E414" t="n">
-        <v>0.2582792660729253</v>
+        <v>0.2561801023173781</v>
       </c>
       <c r="F414" t="n">
-        <v>0.1704003008366719</v>
+        <v>0.168435731327015</v>
       </c>
     </row>
     <row r="415">
@@ -11203,13 +11203,13 @@
         </is>
       </c>
       <c r="D415" t="n">
-        <v>1.196122946287917</v>
+        <v>1.206698241845202</v>
       </c>
       <c r="E415" t="n">
-        <v>1.196122946287917</v>
+        <v>1.206698241845202</v>
       </c>
       <c r="F415" t="n">
-        <v>0.7891446842951724</v>
+        <v>0.7933914422612521</v>
       </c>
     </row>
     <row r="416">
@@ -11229,13 +11229,13 @@
         </is>
       </c>
       <c r="D416" t="n">
-        <v>1.107341259801132</v>
+        <v>1.09125096887286</v>
       </c>
       <c r="E416" t="n">
-        <v>1.107341259801132</v>
+        <v>1.09125096887286</v>
       </c>
       <c r="F416" t="n">
-        <v>0.7305707758426692</v>
+        <v>0.7174860707007586</v>
       </c>
     </row>
     <row r="417">
@@ -11255,13 +11255,13 @@
         </is>
       </c>
       <c r="D417" t="n">
-        <v>-2.317014863284311</v>
+        <v>-2.311499833618358</v>
       </c>
       <c r="E417" t="n">
-        <v>2.317014863284311</v>
+        <v>2.311499833618358</v>
       </c>
       <c r="F417" t="n">
-        <v>1.528655535342931</v>
+        <v>1.519786905446054</v>
       </c>
     </row>
     <row r="418">
@@ -11281,13 +11281,13 @@
         </is>
       </c>
       <c r="D418" t="n">
-        <v>-1.007523780057482</v>
+        <v>-1.028925648259245</v>
       </c>
       <c r="E418" t="n">
-        <v>1.007523780057482</v>
+        <v>1.028925648259245</v>
       </c>
       <c r="F418" t="n">
-        <v>0.6647159790729046</v>
+        <v>0.6765078258535484</v>
       </c>
     </row>
     <row r="419">
@@ -11307,13 +11307,13 @@
         </is>
       </c>
       <c r="D419" t="n">
-        <v>-0.8622682628214687</v>
+        <v>-0.8472537566034335</v>
       </c>
       <c r="E419" t="n">
-        <v>0.8622682628214687</v>
+        <v>0.8472537566034335</v>
       </c>
       <c r="F419" t="n">
-        <v>0.5688833394206982</v>
+        <v>0.5570604618475065</v>
       </c>
     </row>
     <row r="420">
@@ -11333,13 +11333,13 @@
         </is>
       </c>
       <c r="D420" t="n">
-        <v>1.704800120481033</v>
+        <v>1.711187900038106</v>
       </c>
       <c r="E420" t="n">
-        <v>1.704800120481033</v>
+        <v>1.711187900038106</v>
       </c>
       <c r="F420" t="n">
-        <v>1.124745543122072</v>
+        <v>1.125088103149319</v>
       </c>
     </row>
     <row r="421">
@@ -11359,13 +11359,13 @@
         </is>
       </c>
       <c r="D421" t="n">
-        <v>0.9249256349493455</v>
+        <v>0.9360584684400722</v>
       </c>
       <c r="E421" t="n">
-        <v>0.9249256349493455</v>
+        <v>0.9360584684400722</v>
       </c>
       <c r="F421" t="n">
-        <v>0.6102216753334653</v>
+        <v>0.615448628797951</v>
       </c>
     </row>
     <row r="422">
@@ -11385,13 +11385,13 @@
         </is>
       </c>
       <c r="D422" t="n">
-        <v>-0.8614997759163566</v>
+        <v>-0.865473111059648</v>
       </c>
       <c r="E422" t="n">
-        <v>0.8614997759163566</v>
+        <v>0.865473111059648</v>
       </c>
       <c r="F422" t="n">
-        <v>0.5683763285335635</v>
+        <v>0.5690394963797696</v>
       </c>
     </row>
     <row r="423">
@@ -11411,13 +11411,13 @@
         </is>
       </c>
       <c r="D423" t="n">
-        <v>-0.5773062122693723</v>
+        <v>-0.5844644100516979</v>
       </c>
       <c r="E423" t="n">
-        <v>0.5773062122693723</v>
+        <v>0.5844644100516979</v>
       </c>
       <c r="F423" t="n">
-        <v>0.3808790141822879</v>
+        <v>0.384279221731703</v>
       </c>
     </row>
     <row r="424">
@@ -11437,13 +11437,13 @@
         </is>
       </c>
       <c r="D424" t="n">
-        <v>-1.328292924614143</v>
+        <v>-1.346153414108111</v>
       </c>
       <c r="E424" t="n">
-        <v>1.328292924614143</v>
+        <v>1.346153414108111</v>
       </c>
       <c r="F424" t="n">
-        <v>0.876344111530676</v>
+        <v>0.8850817558920022</v>
       </c>
     </row>
     <row r="425">
@@ -11463,13 +11463,13 @@
         </is>
       </c>
       <c r="D425" t="n">
-        <v>0.06978997872861849</v>
+        <v>0.07752557280879187</v>
       </c>
       <c r="E425" t="n">
-        <v>0.06978997872861849</v>
+        <v>0.07752557280879187</v>
       </c>
       <c r="F425" t="n">
-        <v>0.04604408844565846</v>
+        <v>0.05097225129692989</v>
       </c>
     </row>
     <row r="426">
@@ -11489,13 +11489,13 @@
         </is>
       </c>
       <c r="D426" t="n">
-        <v>0.3751838014685119</v>
+        <v>0.3853109324495057</v>
       </c>
       <c r="E426" t="n">
-        <v>0.3751838014685119</v>
+        <v>0.3853109324495057</v>
       </c>
       <c r="F426" t="n">
-        <v>0.2475283192930769</v>
+        <v>0.253337898253404</v>
       </c>
     </row>
     <row r="427">
@@ -11515,13 +11515,13 @@
         </is>
       </c>
       <c r="D427" t="n">
-        <v>1.020253184001494</v>
+        <v>1.030236037893999</v>
       </c>
       <c r="E427" t="n">
-        <v>1.020253184001494</v>
+        <v>1.030236037893999</v>
       </c>
       <c r="F427" t="n">
-        <v>0.6731142306805998</v>
+        <v>0.6773693932994839</v>
       </c>
     </row>
     <row r="428">
@@ -11541,13 +11541,13 @@
         </is>
       </c>
       <c r="D428" t="n">
-        <v>0.6406339644855231</v>
+        <v>0.6286886742870575</v>
       </c>
       <c r="E428" t="n">
-        <v>0.6406339644855231</v>
+        <v>0.6286886742870575</v>
       </c>
       <c r="F428" t="n">
-        <v>0.4226596347989481</v>
+        <v>0.4133562117926</v>
       </c>
     </row>
     <row r="429">
@@ -11567,13 +11567,13 @@
         </is>
       </c>
       <c r="D429" t="n">
-        <v>-1.549709823612051</v>
+        <v>-1.547747668681603</v>
       </c>
       <c r="E429" t="n">
-        <v>1.549709823612051</v>
+        <v>1.547747668681603</v>
       </c>
       <c r="F429" t="n">
-        <v>1.022424386471962</v>
+        <v>1.017627864638353</v>
       </c>
     </row>
     <row r="430">
@@ -11593,13 +11593,13 @@
         </is>
       </c>
       <c r="D430" t="n">
-        <v>0.1012325450052867</v>
+        <v>0.07022969820619261</v>
       </c>
       <c r="E430" t="n">
-        <v>0.1012325450052867</v>
+        <v>0.07022969820619261</v>
       </c>
       <c r="F430" t="n">
-        <v>0.06678838911712029</v>
+        <v>0.04617529024006939</v>
       </c>
     </row>
     <row r="431">
@@ -11619,13 +11619,13 @@
         </is>
       </c>
       <c r="D431" t="n">
-        <v>-1.057872046383418</v>
+        <v>-1.035157676695043</v>
       </c>
       <c r="E431" t="n">
-        <v>1.057872046383418</v>
+        <v>1.035157676695043</v>
       </c>
       <c r="F431" t="n">
-        <v>0.6979333559804343</v>
+        <v>0.680605319209741</v>
       </c>
     </row>
     <row r="432">
@@ -11645,13 +11645,13 @@
         </is>
       </c>
       <c r="D432" t="n">
-        <v>1.849260145894057</v>
+        <v>1.857546363896672</v>
       </c>
       <c r="E432" t="n">
-        <v>1.849260145894057</v>
+        <v>1.857546363896672</v>
       </c>
       <c r="F432" t="n">
-        <v>1.220053355334541</v>
+        <v>1.221317258625942</v>
       </c>
     </row>
     <row r="433">
@@ -11671,13 +11671,13 @@
         </is>
       </c>
       <c r="D433" t="n">
-        <v>-2.124211644284504</v>
+        <v>-2.150087211646348</v>
       </c>
       <c r="E433" t="n">
-        <v>2.124211644284504</v>
+        <v>2.150087211646348</v>
       </c>
       <c r="F433" t="n">
-        <v>1.401453197271513</v>
+        <v>1.413659798846713</v>
       </c>
     </row>
     <row r="434">
@@ -11697,13 +11697,13 @@
         </is>
       </c>
       <c r="D434" t="n">
-        <v>0.9745952277802821</v>
+        <v>0.9843438707520884</v>
       </c>
       <c r="E434" t="n">
-        <v>0.9745952277802821</v>
+        <v>0.9843438707520884</v>
       </c>
       <c r="F434" t="n">
-        <v>0.6429912959441915</v>
+        <v>0.6471957745648294</v>
       </c>
     </row>
     <row r="435">
@@ -11723,13 +11723,13 @@
         </is>
       </c>
       <c r="D435" t="n">
-        <v>0.7887708875674755</v>
+        <v>0.8048987252111639</v>
       </c>
       <c r="E435" t="n">
-        <v>0.7887708875674755</v>
+        <v>0.8048987252111639</v>
       </c>
       <c r="F435" t="n">
-        <v>0.5203932881501868</v>
+        <v>0.5292124727827769</v>
       </c>
     </row>
     <row r="436">
@@ -11749,13 +11749,13 @@
         </is>
       </c>
       <c r="D436" t="n">
-        <v>1.428182753358794</v>
+        <v>1.455149351559341</v>
       </c>
       <c r="E436" t="n">
-        <v>1.428182753358794</v>
+        <v>1.455149351559341</v>
       </c>
       <c r="F436" t="n">
-        <v>0.9422466407093292</v>
+        <v>0.9567454419870565</v>
       </c>
     </row>
     <row r="437">
@@ -11775,13 +11775,13 @@
         </is>
       </c>
       <c r="D437" t="n">
-        <v>-1.664508953213004</v>
+        <v>-1.673027903597291</v>
       </c>
       <c r="E437" t="n">
-        <v>1.664508953213004</v>
+        <v>1.673027903597291</v>
       </c>
       <c r="F437" t="n">
-        <v>1.098163358930817</v>
+        <v>1.099998305581895</v>
       </c>
     </row>
     <row r="438">
@@ -11801,13 +11801,13 @@
         </is>
       </c>
       <c r="D438" t="n">
-        <v>-1.093550140833812</v>
+        <v>-1.111994422904012</v>
       </c>
       <c r="E438" t="n">
-        <v>1.093550140833812</v>
+        <v>1.111994422904012</v>
       </c>
       <c r="F438" t="n">
-        <v>0.7214720554667093</v>
+        <v>0.7311246742393612</v>
       </c>
     </row>
     <row r="439">
@@ -11827,13 +11827,13 @@
         </is>
       </c>
       <c r="D439" t="n">
-        <v>-0.8301916565189628</v>
+        <v>-0.8733188221746282</v>
       </c>
       <c r="E439" t="n">
-        <v>0.8301916565189628</v>
+        <v>0.8733188221746282</v>
       </c>
       <c r="F439" t="n">
-        <v>0.5477207294796307</v>
+        <v>0.574197969178703</v>
       </c>
     </row>
     <row r="440">
@@ -11853,13 +11853,13 @@
         </is>
       </c>
       <c r="D440" t="n">
-        <v>1.038745939621354</v>
+        <v>1.08137204963806</v>
       </c>
       <c r="E440" t="n">
-        <v>1.038745939621354</v>
+        <v>1.08137204963806</v>
       </c>
       <c r="F440" t="n">
-        <v>0.6853148659419426</v>
+        <v>0.7109907848804233</v>
       </c>
     </row>
     <row r="441">
@@ -11879,13 +11879,13 @@
         </is>
       </c>
       <c r="D441" t="n">
-        <v>0.3315814089031885</v>
+        <v>0.3320810975281505</v>
       </c>
       <c r="E441" t="n">
-        <v>0.3315814089031885</v>
+        <v>0.3320810975281505</v>
       </c>
       <c r="F441" t="n">
-        <v>0.2187615470960708</v>
+        <v>0.2183398398862982</v>
       </c>
     </row>
     <row r="442">
@@ -11905,13 +11905,13 @@
         </is>
       </c>
       <c r="D442" t="n">
-        <v>-0.2245733724781505</v>
+        <v>-0.2402597878780894</v>
       </c>
       <c r="E442" t="n">
-        <v>0.2245733724781505</v>
+        <v>0.2402597878780894</v>
       </c>
       <c r="F442" t="n">
-        <v>0.1481627651031733</v>
+        <v>0.1579682915013587</v>
       </c>
     </row>
     <row r="443">
@@ -11931,13 +11931,13 @@
         </is>
       </c>
       <c r="D443" t="n">
-        <v>0.09066238138493535</v>
+        <v>0.09782389413409803</v>
       </c>
       <c r="E443" t="n">
-        <v>0.09066238138493535</v>
+        <v>0.09782389413409803</v>
       </c>
       <c r="F443" t="n">
-        <v>0.05981470095319252</v>
+        <v>0.06431818474847868</v>
       </c>
     </row>
     <row r="444">
@@ -11957,13 +11957,13 @@
         </is>
       </c>
       <c r="D444" t="n">
-        <v>0.1339109910932155</v>
+        <v>0.1424358937439913</v>
       </c>
       <c r="E444" t="n">
-        <v>0.1339109910932155</v>
+        <v>0.1424358937439913</v>
       </c>
       <c r="F444" t="n">
-        <v>0.088348064149981</v>
+        <v>0.09365010675288002</v>
       </c>
     </row>
     <row r="445">
@@ -12099,7 +12099,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>9868</t>
+          <t>7896</t>
         </is>
       </c>
       <c r="D451" t="inlineStr"/>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>2468</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="D452" t="inlineStr"/>
@@ -12139,7 +12139,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>92.5583</t>
+          <t>91.8136</t>
         </is>
       </c>
       <c r="D453" t="inlineStr"/>
@@ -12159,7 +12159,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>96.9193</t>
+          <t>97.0745</t>
         </is>
       </c>
       <c r="D454" t="inlineStr"/>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>96.718</t>
+          <t>96.9333</t>
         </is>
       </c>
       <c r="D455" t="inlineStr"/>
@@ -12199,7 +12199,7 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>0.088384</t>
+          <t>0.085626</t>
         </is>
       </c>
       <c r="D456" t="inlineStr"/>
@@ -12219,7 +12219,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>0.094437</t>
+          <t>0.089905</t>
         </is>
       </c>
       <c r="D457" t="inlineStr"/>
